--- a/research/brics_universities/output/BRICS_universities_saudi_arabia.xlsx
+++ b/research/brics_universities/output/BRICS_universities_saudi_arabia.xlsx
@@ -4850,7 +4850,7 @@
       </c>
       <c r="AE18" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF18" s="4" t="inlineStr">
@@ -4859,7 +4859,8 @@
 • Op@imamu.edu.sa — e-mail для записи на приём к президенту (офис президента); телефоны офиса: 011 259 8762, 011 258 5214
 • Сайт в основном на JavaScript, часть страниц (contact-us) блокируется WAF; почтовый адрес (P.O. Box) на открытых страницах не найден
 • Есть Генеральное управление международного сотрудничества и коммуникаций (الإدارة العامة للتعاون والتواصل الدولي), но e-mail и руководитель на странице не отображаются
-• Спутников не найдено; в поиске упоминается проект KN-Sat1 (ResearchGate), связь с IMSIU и запуск не подтверждены</t>
+• Спутников не найдено; в поиске упоминается проект KN-Sat1 (ResearchGate), связь с IMSIU и запуск не подтверждены
+• Перепроверка: Повторный доступ к imamu.edu.sa блокируется WAF (страница «IMAMU Support», 04.10.2026) — обход не выполнялся; уровень повышен до medium на основании ранее подтверждённых данных (президент — SPA, июль 2026; e-mail офиса президента — официальный сайт), данные не изменены</t>
         </is>
       </c>
       <c r="AG18" s="4" t="inlineStr">
@@ -5086,10 +5087,10 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Prof. Dr. Mar'ei bin Hussein Al-Qahtani
-Президент университета
+          <t>Dr. Mohammad AbuRasain
+President
 Офис президента университета
-Обращение: Dear Prof. Al-Qahtani,</t>
+Обращение: Dear Dr. AbuRasain,</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr"/>
@@ -5110,7 +5111,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>Prof. Dr. Mar'ei bin Hussein Al-Qahtani</t>
+          <t>Dr. Mohammad AbuRasain (Mohammed bin Hassan AbuRasain)</t>
         </is>
       </c>
       <c r="Q20" s="4" t="inlineStr">
@@ -5154,9 +5155,11 @@
       </c>
       <c r="AF20" s="4" t="inlineStr">
         <is>
-          <t>• Сайт jazanu.edu.sa недоступен из нашей сети (HTTP 403/503, архив также недоступен) — ФИО президента, e-mail, телефон и адрес взяты из поисковой выдачи по официальным страницам, НЕ открытым напрямую; обязательно перепроверить
+          <t>• Сайт jazanu.edu.sa недоступен из нашей сети (HTTP 403 / сброс соединения) — e-mail president@jazanu.edu.sa, телефон и адрес взяты из поисковой выдачи по официальным страницам, НЕ открытым напрямую; обязательно перепроверить
+• Президент исправлен: Dr. Mohammad AbuRasain (Mohammed bin Hassan AbuRasain), с 17.05.2024 — подтверждено Saudi Press Agency 21.04.2026; ранее в строке ошибочно был указан Prof. Mar'ei bin Hussein Al-Qahtani (бывший президент)
 • E-mail международного отдела не найден; используется адрес офиса президента president@jazanu.edu.sa (в письме требуется указать полное имя и мобильный номер)
-• Спутников в nanosats.csv не найдено; отдельная проверка по космосу не проводилась из-за блокировки сайта</t>
+• Спутников в nanosats.csv не найдено; отдельная проверка по космосу не проводилась из-за блокировки сайта
+• Перепроверка: ИСПРАВЛЕНО: президент — д-р Мохаммад Абурасаин (SPA, 21.04.2026; в должности с 17.05.2024), а не Al-Qahtani; контакты по-прежнему не открыты (сайт 403)</t>
         </is>
       </c>
       <c r="AG20" s="4" t="inlineStr">
@@ -5164,7 +5167,8 @@
           <t>• Https://www.jazanu.edu.sa/en/administration/departments/jupresident/contactinfo (via search index
 • Site blocked)
 • Https://www.jazanu.edu.sa/en/administration/departments/university-president
-• Nanosats.csv</t>
+• Nanosats.csv
+• Https://spa.gov.sa/en/N2566500</t>
         </is>
       </c>
       <c r="AH20" s="4" t="inlineStr">
@@ -5606,7 +5610,8 @@
 • Ask_dar@ksau-hs.edu.sa — e-mail деканата приёма и регистрации (другого общего адреса не найдено)
 • Университет подчиняется Министерству национальной гвардии (не Минобразования); президент одновременно CEO медицинских служб нацгвардии (MNGHA); подтверждён по программе BIO 2026
 • Медицинский профиль; спутников не найдено (проверка только по nanosats.csv)
-• Имя руководителя по международным партнёрствам не найдено; есть портал соглашений и стратегических партнёрств</t>
+• Имя руководителя по международным партнёрствам не найдено; есть портал соглашений и стратегических партнёрств
+• Перепроверка: Сайт ksau-hs.edu.sa по-прежнему не открывается (устаревший TLS и неполная цепочка сертификатов); данные не изменены</t>
         </is>
       </c>
       <c r="AG23" s="4" t="inlineStr">
@@ -5727,7 +5732,8 @@
         <is>
           <t>• Сайт mu.edu.sa (и m.mu.edu.sa) недоступен из нашей сети (HTTP 403) — e-mail и адрес не проверены, не заполнены
 • ФИО президента — по Википедии (данные 2026 г.); учёное звание «Prof.» не подтверждено официальным сайтом; телефон — по поисковой выдаче (my.gov.sa), перепроверить
-• Спутников в nanosats.csv не найдено</t>
+• Спутников в nanosats.csv не найдено
+• Перепроверка: 04.10.2026: mu.edu.sa (в т.ч. /en через WebFetch) и каталог my.gov.sa по-прежнему отдают 403; данные не изменены</t>
         </is>
       </c>
       <c r="AG24" s="4" t="inlineStr">
@@ -6912,7 +6918,8 @@
           <t>• Сайт bu.edu.sa недоступен из нашей сети (HTTP 503/обрыв соединения) — e-mail contact@bu.edu.sa, телефон (+966 17 725 7700, доб. 15005; факс +966 17 725 7777) и ФИО взяты из поисковой выдачи по странице офиса президента и Википедии; перепроверить
 • По той же выдаче директор офиса президента — Mr. Abdullah Alzahrani
 • Главный кампус — в Аль-Акике (~25 км от г. Эль-Баха); почтовый адрес не проверен
-• Спутников в nanosats.csv не найдено</t>
+• Спутников в nanosats.csv не найдено
+• Перепроверка: Сайт bu.edu.sa по-прежнему недоступен (04.10.2026: сброс соединения, WebFetch — 503); данные не изменены</t>
         </is>
       </c>
       <c r="AG32" s="4" t="inlineStr">
@@ -7406,23 +7413,28 @@
       <c r="I36" s="4" t="inlineStr"/>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>ccm@ub.edu.sa</t>
+          <t>president_office@ub.edu.sa</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>ФИО не найдено
-Общий адрес университета (коммуникации)
-Обращение: Dear Sir or Madam,</t>
+          <t>Prof. Dr. Mohammed bin Mohsen Safhi
+President of the University
+Office of the President (president_office@ub.edu.sa); общий ящик коммуникаций — ccm@ub.edu.sa
+Обращение: Dear Professor Safhi,</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr"/>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>ccm@ub.edu.sa</t>
-        </is>
-      </c>
-      <c r="N36" s="4" t="inlineStr"/>
+          <t>president_office@ub.edu.sa</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>+966 17 623 8093 (President's Office)</t>
+        </is>
+      </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
           <t>https://www.ub.edu.sa</t>
@@ -7469,20 +7481,22 @@
       </c>
       <c r="AE36" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF36" s="4" t="inlineStr">
         <is>
-          <t>• Новый сайт ub.edu.sa — SPA; e-mail ccm@ub.edu.sa взят из подвала сайта (назначение ящика не указано, вероятно — коммуникации/обращения); телефон и почтовый адрес не найдены
+          <t>• Новый сайт ub.edu.sa — SPA; e-mail president_office@ub.edu.sa и телефон +966 17 623 8093 заданы в коде официальной страницы «Президент университета» (проверено 04.10.2026); ccm@ub.edu.sa — общий ящик из подвала сайта
 • Президент подтверждён новостью официального сайта за октябрь 2026 (أ.د. محمد بن محسن صفحي)
-• E-mail международного отдела не найден
-• Спутников не найдено (nanosats.csv, новости сайта)</t>
+• Почтовый адрес не найден (страница контактов подгружает данные динамически); e-mail международного отдела не найден
+• Спутников не найдено (nanosats.csv, новости сайта)
+• Перепроверка: Добавлены e-mail и телефон офиса президента с официальной страницы президента (04.10.2026); президент подтверждён новостями сайта 10.2026</t>
         </is>
       </c>
       <c r="AG36" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ub.edu.sa/
+• Https://www.ub.edu.sa/university-president (assets/university-president-Du7USWOi.js)
 • Https://ubapi.ub.edu.sa/api/cms/news
 • Nanosats.csv</t>
         </is>
@@ -8045,16 +8059,17 @@
       </c>
       <c r="AE40" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF40" s="4" t="inlineStr">
         <is>
           <t>• Саудовское отделение некоммерческого Арабского открытого университета (штаб-квартира в Кувейте), смешанное/дистанционное обучение; партнёр Open University (UK)
-• Глава указан на странице About как President; дата обновления страницы не видна (в футере © 2022) — актуальность на 2026 г. не подтверждена
 • Есть раздел Local and International Relations, но отдельного e-mail/руководителя нет — использовать info@arabou.edu.sa; второй телефон +966 11 274 2696
 • Филиалы: Даммам/Эль-Хаса (Dr. Mohammad Alsaif), Джидда (Dr. Osamah Alzaid), Медина (Dr. Abdullah AlGhamdi)
-• Инженерного/космического профиля нет; спутников не найдено (проверка только по nanosats.csv)</t>
+• Инженерного/космического профиля нет; спутников не найдено (проверка только по nanosats.csv)
+• 04.10.2026: страница About (сайт активно обновляется, новости до 30.09.2026) по-прежнему называет президентом Prof. Dr. Ali bin Mohammed Al-Shahrani; адрес, info@arabou.edu.sa и телефоны подтверждены. В новостях 2026 г. («رئيس الجامعة…», 26.08.2026) имя президента не указано — дата назначения не подтверждена
+• Перепроверка: Президент, адрес, e-mail и телефоны подтверждены на сайте arabou.edu.sa 04.10.2026 (страница без даты, сайт обновляется в 2026)</t>
         </is>
       </c>
       <c r="AG40" s="4" t="inlineStr">
@@ -8589,7 +8604,8 @@
           <t>• Сайт www.jic.edu.sa недоступен (DNS не разрешается/прокси отклоняет соединение), портал Королевской комиссии rcjy.edu.sa отвечает 503; лимит веб-поиска исчерпан — контакты и руководитель НЕ проверены
 • Колледж Королевской комиссии по Джубайлю и Янбу (не Минобразования); прикладной инженерно-технологический профиль; должность руководителя (Managing Director) не подтверждена
 • Спутников не найдено (проверка только по nanosats.csv)
-• Требуется ручная доработка перед рассылкой</t>
+• Требуется ручная доработка перед рассылкой
+• Перепроверка: Домен www.jic.edu.sa не разрешается, jic.edu.sa и rcjy.gov.sa недоступны (502 / сброс соединения) — данные не изменены (04.10.2026)</t>
         </is>
       </c>
       <c r="AG44" s="4" t="inlineStr">
@@ -8613,7 +8629,11 @@
           <t>Саудовская Аравия</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr"/>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Джидда</t>
+        </is>
+      </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
           <t>Prince Sultan Aviation Academy</t>
@@ -8639,7 +8659,11 @@
       <c r="L45" s="4" t="inlineStr"/>
       <c r="M45" s="4" t="inlineStr"/>
       <c r="N45" s="4" t="inlineStr"/>
-      <c r="O45" s="4" t="inlineStr"/>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>https://psaa.com.sa</t>
+        </is>
+      </c>
       <c r="P45" s="4" t="inlineStr"/>
       <c r="Q45" s="4" t="inlineStr"/>
       <c r="R45" s="4" t="inlineStr"/>
@@ -8670,15 +8694,18 @@
       </c>
       <c r="AF45" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт не открылся: psaa.edu.sa не резолвится (DNS), psaa.com.sa отвечает HTTP 403; лимит веб-поиска сессии исчерпан — контакты, руководитель, адрес НЕ проверены и не заполнены
-• В англ. Википедии статья перенаправляет на раздел истории авиакомпании Saudia — вероятно, академия входит в группу Saudia (не подтверждено официальной страницей)
+          <t>• Официальный сайт — https://psaa.com.sa (одностраничное приложение, в основном портал записи на курсы); psaa.edu.sa не резолвится
+• Сайт указывает расположение академии в Джидде и отдельную регистрацию для сотрудников Saudia — подтверждает принадлежность к группе Saudia
+• Руководитель, e-mail, телефон, почтовый адрес НЕ найдены на официальных страницах — требуется ручная доработка
 • Профиль main_fields — общий для авиационной академии, не проверен; спутников в nanosats.csv нет
-• Требуется ручная доработка всей строки</t>
+• Перепроверка: Официальный сайт psaa.com.sa (SPA) открыт 04.10.2026: из его кода подтверждены расположение в Джидде и связь с Saudia (отдельная регистрация для сотрудников Saudia); руководитель, e-mail, телефон и адрес на сайте не опубликованы</t>
         </is>
       </c>
       <c r="AG45" s="4" t="inlineStr">
         <is>
-          <t>• Https://en.wikipedia.org/wiki/Prince_Sultan_Aviation_Academy (redirect to Saudia#Early_years)
+          <t>• Https://psaa.com.sa/ (SPA
+• Текст из официального JS-бандла /static/js/main.ca029ecb.js)
+• Https://en.wikipedia.org/wiki/Prince_Sultan_Aviation_Academy (redirect to Saudia#Early_years)
 • Nanosats.csv</t>
         </is>
       </c>
@@ -9170,7 +9197,7 @@
       <c r="N49" s="4" t="inlineStr"/>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>http://www.rcyci.edu.sa/en/yic/</t>
+          <t>https://rcjy.edu.sa/en/colleges-and-institutes-in-yanbu/yanbu-industrial-college/home-yanbu-industrial-college/</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr"/>
@@ -9208,14 +9235,20 @@
       <c r="AF49" s="4" t="inlineStr">
         <is>
           <t>• Колледж Королевской комиссии по Джубайлю и Янбу (Royal Commission), основан в 1989 г., расположен в промышленном городе Янбу
-• Официальные сайты yic.edu.sa и rcyci.edu.sa не резолвятся / недоступны; лимит веб-поиска исчерпан — контакты и адрес не проверены
 • В Википедии руководителем указан Dr. Fahad Aloufi (без даты, вероятно устарело) — в head_name не внесено
-• Profile_type: технический колледж (не аэрокосмический); спутников нет</t>
+• Profile_type: технический колледж (не аэрокосмический); спутников нет
+• Актуальный официальный сайт — раздел портала Royal Commission Education (rcjy.edu.sa); yic.edu.sa и rcyci.edu.sa не открываются
+• Руководитель — Managing Director (по оргструктуре на rcjy.edu.sa), имя на открытых страницах не указано; по поиску — Dr. Ahmed Al-Ghamdi (не подтверждено)
+• Опубликованного e-mail нет: обращения через веб-форму https://rcjy.edu.sa/en/contact-us/ (выбор «Yanbu Industrial College»)
+• Перепроверка: 04.10.2026: найден официальный раздел колледжа на rcjy.edu.sa (сайт обновлён); имя руководителя и e-mail там не опубликованы — остаётся low</t>
         </is>
       </c>
       <c r="AG49" s="4" t="inlineStr">
         <is>
-          <t>• Https://en.wikipedia.org/wiki/Yanbu_Industrial_College
+          <t>• Https://rcjy.edu.sa/en/colleges-and-institutes-in-yanbu/yanbu-industrial-college/home-yanbu-industrial-college/
+• Https://rcjy.edu.sa/en/colleges-and-institutes-in-yanbu/yanbu-industrial-college/about-yanbu-industrial-college/organizational-structure-yanbu-industrial-college/
+• Https://rcjy.edu.sa/en/contact-us/
+• Https://en.wikipedia.org/wiki/Yanbu_Industrial_College
 • Nanosats.csv</t>
         </is>
       </c>

--- a/research/brics_universities/output/BRICS_universities_saudi_arabia.xlsx
+++ b/research/brics_universities/output/BRICS_universities_saudi_arabia.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Саудовская Аравия" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AI$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Саудовская Аравия'!$A$1:$AI$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AJ$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Саудовская Аравия'!$A$1:$AJ$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Дата формирования: 2026-10-04</t>
+          <t>Дата формирования: 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AJ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -666,30 +666,31 @@
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="45" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="45" customWidth="1" min="23" max="23"/>
     <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="40" customWidth="1" min="25" max="25"/>
-    <col width="45" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
-    <col width="55" customWidth="1" min="32" max="32"/>
-    <col width="60" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="24" customWidth="1" min="35" max="35"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="45" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="55" customWidth="1" min="33" max="33"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="24" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -750,120 +751,125 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Стыковка e-mail и адресата</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>E-mail (международный отдел)</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>E-mail (общий / ректорат)</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Телефон</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Ректор / президент</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Должность</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Рейтинг QS</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Рейтинг THE</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Национальный рейтинг</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Запущено КА (спутников)</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Названия запущенных КА (год)</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>КА в разработке</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Наземная станция</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>Космические подразделения</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>Партнёрства в космической сфере</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>Санкционные / ограничительные списки (США)</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>Космический индекс (0–100)</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AD1" s="3" t="inlineStr">
         <is>
           <t>Волна рассылки</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AE1" s="3" t="inlineStr">
         <is>
           <t>Проверка домена e-mail (MX)</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AF1" s="3" t="inlineStr">
         <is>
           <t>Достоверность</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AG1" s="3" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>Дата проверки</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>Секретарь парткома (справочно, Китай)</t>
         </is>
@@ -933,90 +939,95 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
           <t>icstd@ksu.edu.sa</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>po@ksu.edu.sa</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>+966 11 467 0000</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>https://ksu.edu.sa</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>Prof. Ali bin Mohammed Masmali</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>Acting President</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>QS2027: 107</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>THE2027: 216</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="n">
+      <c r="U2" s="4" t="inlineStr"/>
+      <c r="V2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>KSU CubeSat (2021)</t>
         </is>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>• KSU CubeSat-2 (second satellite approved in 2021
 • Current status unverified)</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>Satellite ground station at the College of Engineering (built during KSU CubeSat project)</t>
         </is>
       </c>
-      <c r="Y2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>College of Engineering – KSU CubeSat project team</t>
         </is>
       </c>
-      <c r="Z2" s="4" t="inlineStr"/>
       <c r="AA2" s="4" t="inlineStr"/>
-      <c r="AB2" s="4" t="n">
+      <c r="AB2" s="4" t="inlineStr"/>
+      <c r="AC2" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="AC2" s="5" t="inlineStr">
+      <c r="AD2" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD2" s="4" t="inlineStr">
+      <c r="AE2" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE2" s="4" t="inlineStr">
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>• Ректор — исполняющий обязанности (Acting President) с июня 2025 г.; упоминается в новостях KSU от 30.09.2026
 • KSU CubeSat (1U) запущен 22.03.2021 на «Союз-2» с Байконура — первый спутник саудовского университета; сошёл с орбиты
@@ -1024,7 +1035,7 @@
 • Дата последнего обновления страницы с руководителем GEO не указана</t>
         </is>
       </c>
-      <c r="AG2" s="4" t="inlineStr">
+      <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>• Https://ksu.edu.sa/en/contact-us
 • Https://ksu.edu.sa/en
@@ -1037,12 +1048,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI2" s="4" t="inlineStr"/>
+      <c r="AI2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -1105,39 +1116,44 @@
 Обращение: Dear Director of International Cooperation,</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>media@kacst.gov.sa</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>+966 11 488 3555</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>https://kacst.gov.sa</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>Dr. Munir M. Eldesouki</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="4" t="inlineStr"/>
       <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="n">
+      <c r="U3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>• SaudiSat-1A (2000)
 • SaudiSat-1B (2000)
@@ -1158,41 +1174,41 @@
 • Shaheen Sat (2021)</t>
         </is>
       </c>
-      <c r="W3" s="4" t="inlineStr"/>
       <c r="X3" s="4" t="inlineStr"/>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr"/>
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>• Space Research Institute (per Wikipedia
 • Current structure unverified)
 • National Satellite Technology Program</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>• Saudi Space Agency
 • CNSA (Chang'e-4 payload, 2018)</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="n">
+      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="AC3" s="5" t="inlineStr">
+      <c r="AD3" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD3" s="4" t="inlineStr">
+      <c r="AE3" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE3" s="4" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>• Сайт kacst.gov.sa недоступен (503/таймаут); адрес, телефон и media@kacst.gov.sa взяты из поисковой выдачи официальной страницы контактов
 • Президент в ранге министра; подтверждён в новости SPA от 11.02.2026
@@ -1201,7 +1217,7 @@
 • Член IAF; не университет — партнёрство через агентство/институт</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>• Https://saudipedia.com/en/list-of-the-kingdom%E2%80%99s-satellites
 • Https://en.wikipedia.org/wiki/King_Abdulaziz_City_for_Science_and_Technology
@@ -1212,12 +1228,12 @@
 • Https://www.iafastro.org/membership/all-members/king-abdulaziz-city-for-science-and-technology-kacst.html</t>
         </is>
       </c>
-      <c r="AH3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1283,85 +1299,90 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
           <t>icu@uqu.edu.sa</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>rect@uqu.edu.sa</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>+966 12 528 0347</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>https://uqu.edu.sa</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Prof. Moaddi bin Muhammad Aal Madh-hab</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>QS2027: 741–750</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>THE2027: 451–500</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="n">
+      <c r="U4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr">
         <is>
           <t>SARI-1 (Ufuq) (2025)</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr"/>
       <c r="X4" s="4" t="inlineStr"/>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr"/>
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>Student team 'Ufuq' (SARI competition)</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>Saudi Space Agency (SARI student satellite competition)</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="n">
+      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AC4" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="AC4" s="5" t="inlineStr">
+      <c r="AD4" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AE4" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>• Ректор назначен королевским указом в октябре 2020 г.; актуальность на 2026 г. подтверждена только CV на официальном сайте (дата обновления не видна)
 • SARI-1 (Ufuq, PocketQube 1p) — победитель конкурса SARI Саудовского космического агентства; запуск 28.11.2025 (Transporter-15, через Alba Orbital), статус на орбите неизвестен
@@ -1369,7 +1390,7 @@
 • Имя текущего руководителя подразделения международного сотрудничества не подтверждено</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>• Https://uqu.edu.sa/en/rect
 • Https://uqu.edu.sa/en/icu/App/Contact
@@ -1380,12 +1401,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1449,71 +1470,76 @@
 Обращение: Dear Head of Global Communications,</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>global.pr@kaust.edu.sa</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>https://www.kaust.edu.sa</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>Prof. Sir Edward Byrne AC</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>President &amp; Chief Academic Officer</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="4" t="inlineStr"/>
       <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="n">
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V5" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t>KAUSTSat (Lemur-2 ONREFLECTION, 6U, with Spire Global) (2023)</t>
         </is>
       </c>
-      <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr"/>
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>Climate and Livability Initiative / Hydrology, Agriculture and Land Observation group (Prof. Matthew McCabe) — KAUSTSat mission</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>Spire Global (KAUSTSat platform, launch on SpaceX Transporter-7)</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="n">
+      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AC5" s="5" t="inlineStr">
+      <c r="AD5" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD5" s="4" t="inlineStr">
+      <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr">
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>• Общий e-mail не опубликован; global.pr@kaust.edu.sa — ящик медиа/PR (Global PR and in-Kingdom inquiries), используется как единственный неадмиссионный адрес
 • Отдел партнёрств (Partnerships Office, &gt;40 международных соглашений) упомянут на сайте, но e-mail и руководитель не опубликованы
@@ -1522,7 +1548,7 @@
 • Телефон на официальной странице контактов не опубликован</t>
         </is>
       </c>
-      <c r="AG5" s="4" t="inlineStr">
+      <c r="AH5" s="4" t="inlineStr">
         <is>
           <t>• Https://www.kaust.edu.sa/en/about/administration/president
 • Https://www.kaust.edu.sa/en/contact
@@ -1532,12 +1558,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1603,92 +1629,97 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
           <t>global@kfupm.edu.sa</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>info@kfupm.edu.sa</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>+966 13 860 0000</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>https://www.kfupm.edu.sa</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>Dr. Muhammad M. Al-Saggaf</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr">
+      <c r="S6" s="4" t="inlineStr">
         <is>
           <t>QS2027: 63</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="T6" s="4" t="inlineStr">
         <is>
           <t>THE2027: =176</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="n">
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="4" t="inlineStr"/>
-      <c r="W6" s="4" t="inlineStr">
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr">
         <is>
           <t>• Opti-K 6U CubeSat with optical transmitter (with Astrolight)
 • Dual 8U Earth-observation satellite mission (GomSpace MoU, Sep 2026)
 • High-altitude balloon CubeSat platform</t>
         </is>
       </c>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="Y6" s="4" t="inlineStr">
         <is>
           <t>Student-built ground station (IRC-ASE); Optical Ground Station with 360° tracking (Opti-K, in development)</t>
         </is>
       </c>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>Interdisciplinary Research Center for Aviation &amp; Space Exploration (IRC-ASE), Director Dr. Ayman Abdallah, irc-ase@kfupm.edu.sa</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>• GomSpace (MoU, 2026)
 • Astrolight (Opti-K)</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="n">
+      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AC6" s="6" t="inlineStr">
+      <c r="AD6" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD6" s="4" t="inlineStr">
+      <c r="AE6" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>• Спутников на орбите нет; активная космическая программа через IRC-ASE (создан в 2022 г.)
 • Сентябрь 2026: MoU с GomSpace о двойной 8U миссии ДЗЗ — приоритетный кандидат для партнёрства по CubeSat
@@ -1696,7 +1727,7 @@
 • Для партнёрств по космосу дополнительно: irc-ase@kfupm.edu.sa, +966 13 860 5400</t>
         </is>
       </c>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AH6" s="4" t="inlineStr">
         <is>
           <t>• Https://www.kfupm.edu.sa/about-us/our-story/leadership
 • Https://www.kfupm.edu.sa/about-us/connect/contact-us
@@ -1707,12 +1738,12 @@
 • Https://gomspace.com/gomspace-and-kfupm-sign-mou-to-explore-strategic-cooperation-in-space-technology/</t>
         </is>
       </c>
-      <c r="AH6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1775,86 +1806,91 @@
 Обращение: Dear Sir or Madam,</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>info@psu.edu.sa</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>+966 11 494 8000</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>https://www.psu.edu.sa</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Dr. Ahmed S. Yamani</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>President (Rector)</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t>QS2027: 488</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>THE2027: 376–400</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="n">
+      <c r="U7" s="4" t="inlineStr"/>
+      <c r="V7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="4" t="inlineStr">
+      <c r="W7" s="4" t="inlineStr">
         <is>
           <t>Rawdat Scoop (SARI-2, PocketQube 1p) (2025)</t>
         </is>
       </c>
-      <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr"/>
       <c r="Y7" s="4" t="inlineStr"/>
-      <c r="Z7" s="4" t="inlineStr">
+      <c r="Z7" s="4" t="inlineStr"/>
+      <c r="AA7" s="4" t="inlineStr">
         <is>
           <t>Saudi Space Agency (SARI student small-satellite competition — PSU design selected for flight, launched Nov 2025)</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="n">
+      <c r="AB7" s="4" t="inlineStr"/>
+      <c r="AC7" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AC7" s="5" t="inlineStr">
+      <c r="AD7" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD7" s="4" t="inlineStr">
+      <c r="AE7" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr">
+      <c r="AF7" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт psu.edu.sa недоступен (HTTP 503 / ошибка TLS) — контакты взяты из справочника WIPO TISC, ФИО ректора — из Википедии; рекомендуется перепроверить
 • Спутник Rawdat Scoop (SARI-2) спроектирован студентами PSU в рамках конкурса SARI Саудовского космического агентства и запущен в ноябре 2025; статус на орбите неизвестен
 • E-mail международного отдела не найден</t>
         </is>
       </c>
-      <c r="AG7" s="4" t="inlineStr">
+      <c r="AH7" s="4" t="inlineStr">
         <is>
           <t>• Https://en.wikipedia.org/wiki/Prince_Sultan_University
 • Https://www.wipo.int/tisc/en/search/details.jsp?id=12475
@@ -1862,12 +1898,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1920,42 +1956,47 @@
       </c>
       <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>+966 11 244 3999</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>https://ssa.gov.sa</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>Dr. Mohammed bin Saud Al-Tamimi</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>Chief Executive Officer (Acting CEO per April 2026 SPA statement)</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="n">
+      <c r="U8" s="4" t="inlineStr"/>
+      <c r="V8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="4" t="inlineStr">
+      <c r="W8" s="4" t="inlineStr">
         <is>
           <t>Shams (Space Weather CubeSat-1, SWC-1, 12U) (2026)</t>
         </is>
       </c>
-      <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="4" t="inlineStr">
+      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="Z8" s="4" t="inlineStr">
         <is>
           <t>• Saudi Human Spaceflight (HSF) Program
 • Shams space-weather mission
@@ -1964,7 +2005,7 @@
 • Space Academy</t>
         </is>
       </c>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="AA8" s="4" t="inlineStr">
         <is>
           <t>• NASA (Artemis II — Shams launched as SLS secondary payload, April 2026
 • US–Saudi civil aeronautics and space cooperation agreement)
@@ -1972,22 +2013,22 @@
 • Umm Al-Qura University and Prince Sultan University (SARI satellites, 2025)</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="n">
+      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AC8" s="5" t="inlineStr">
+      <c r="AD8" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD8" s="4" t="inlineStr"/>
-      <c r="AE8" s="4" t="inlineStr">
+      <c r="AE8" s="4" t="inlineStr"/>
+      <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF8" s="4" t="inlineStr">
+      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t>• Это государственное агентство, а не университет (включено намеренно)
 • Сайт ssa.gov.sa рендерится через JS — контактный e-mail не удалось прочитать; по поисковой выдаче общий адрес Info@ssa.gov.sa (в справочнике Eye of Riyadh — устаревший Info@ssc.gov.sa) — НЕ подтверждено, проверить перед отправкой
@@ -1996,7 +2037,7 @@
 • Спутник Shams (SWC-1) разработан в КСА, выведен 01.04.2026 в рамках Artemis II на высокоэллиптическую орбиту ~500–70 000 км (не VLEO)</t>
         </is>
       </c>
-      <c r="AG8" s="4" t="inlineStr">
+      <c r="AH8" s="4" t="inlineStr">
         <is>
           <t>• Https://ssa.gov.sa/en/about-ssa/
 • Https://www.iafastro.org/membership/all-members/saudi-space-commission-ssc.html
@@ -2007,15 +2048,15 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ8" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI8"/>
+  <autoFilter ref="A1:AJ8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2026,7 +2067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI49"/>
+  <dimension ref="A1:AJ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2040,30 +2081,31 @@
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="45" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="45" customWidth="1" min="23" max="23"/>
     <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="40" customWidth="1" min="25" max="25"/>
-    <col width="45" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
-    <col width="55" customWidth="1" min="32" max="32"/>
-    <col width="60" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="24" customWidth="1" min="35" max="35"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="45" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="55" customWidth="1" min="33" max="33"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="24" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2124,120 +2166,125 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Стыковка e-mail и адресата</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>E-mail (международный отдел)</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>E-mail (общий / ректорат)</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Телефон</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Ректор / президент</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Должность</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Рейтинг QS</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Рейтинг THE</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Национальный рейтинг</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Запущено КА (спутников)</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Названия запущенных КА (год)</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>КА в разработке</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Наземная станция</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>Космические подразделения</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>Партнёрства в космической сфере</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>Санкционные / ограничительные списки (США)</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>Космический индекс (0–100)</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AD1" s="3" t="inlineStr">
         <is>
           <t>Волна рассылки</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AE1" s="3" t="inlineStr">
         <is>
           <t>Проверка домена e-mail (MX)</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AF1" s="3" t="inlineStr">
         <is>
           <t>Достоверность</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AG1" s="3" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>Дата проверки</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>Секретарь парткома (справочно, Китай)</t>
         </is>
@@ -2307,90 +2354,95 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
           <t>icstd@ksu.edu.sa</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>po@ksu.edu.sa</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>+966 11 467 0000</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>https://ksu.edu.sa</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>Prof. Ali bin Mohammed Masmali</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>Acting President</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>QS2027: 107</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>THE2027: 216</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="n">
+      <c r="U2" s="4" t="inlineStr"/>
+      <c r="V2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>KSU CubeSat (2021)</t>
         </is>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>• KSU CubeSat-2 (second satellite approved in 2021
 • Current status unverified)</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>Satellite ground station at the College of Engineering (built during KSU CubeSat project)</t>
         </is>
       </c>
-      <c r="Y2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>College of Engineering – KSU CubeSat project team</t>
         </is>
       </c>
-      <c r="Z2" s="4" t="inlineStr"/>
       <c r="AA2" s="4" t="inlineStr"/>
-      <c r="AB2" s="4" t="n">
+      <c r="AB2" s="4" t="inlineStr"/>
+      <c r="AC2" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="AC2" s="5" t="inlineStr">
+      <c r="AD2" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD2" s="4" t="inlineStr">
+      <c r="AE2" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE2" s="4" t="inlineStr">
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>• Ректор — исполняющий обязанности (Acting President) с июня 2025 г.; упоминается в новостях KSU от 30.09.2026
 • KSU CubeSat (1U) запущен 22.03.2021 на «Союз-2» с Байконура — первый спутник саудовского университета; сошёл с орбиты
@@ -2398,7 +2450,7 @@
 • Дата последнего обновления страницы с руководителем GEO не указана</t>
         </is>
       </c>
-      <c r="AG2" s="4" t="inlineStr">
+      <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>• Https://ksu.edu.sa/en/contact-us
 • Https://ksu.edu.sa/en
@@ -2411,12 +2463,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI2" s="4" t="inlineStr"/>
+      <c r="AI2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -2479,39 +2531,44 @@
 Обращение: Dear Director of International Cooperation,</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>media@kacst.gov.sa</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>+966 11 488 3555</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>https://kacst.gov.sa</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>Dr. Munir M. Eldesouki</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="4" t="inlineStr"/>
       <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="n">
+      <c r="U3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>• SaudiSat-1A (2000)
 • SaudiSat-1B (2000)
@@ -2532,41 +2589,41 @@
 • Shaheen Sat (2021)</t>
         </is>
       </c>
-      <c r="W3" s="4" t="inlineStr"/>
       <c r="X3" s="4" t="inlineStr"/>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr"/>
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>• Space Research Institute (per Wikipedia
 • Current structure unverified)
 • National Satellite Technology Program</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>• Saudi Space Agency
 • CNSA (Chang'e-4 payload, 2018)</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="n">
+      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="AC3" s="5" t="inlineStr">
+      <c r="AD3" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD3" s="4" t="inlineStr">
+      <c r="AE3" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE3" s="4" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>• Сайт kacst.gov.sa недоступен (503/таймаут); адрес, телефон и media@kacst.gov.sa взяты из поисковой выдачи официальной страницы контактов
 • Президент в ранге министра; подтверждён в новости SPA от 11.02.2026
@@ -2575,7 +2632,7 @@
 • Член IAF; не университет — партнёрство через агентство/институт</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>• Https://saudipedia.com/en/list-of-the-kingdom%E2%80%99s-satellites
 • Https://en.wikipedia.org/wiki/King_Abdulaziz_City_for_Science_and_Technology
@@ -2586,12 +2643,12 @@
 • Https://www.iafastro.org/membership/all-members/king-abdulaziz-city-for-science-and-technology-kacst.html</t>
         </is>
       </c>
-      <c r="AH3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -2657,85 +2714,90 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
           <t>icu@uqu.edu.sa</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>rect@uqu.edu.sa</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>+966 12 528 0347</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>https://uqu.edu.sa</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Prof. Moaddi bin Muhammad Aal Madh-hab</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>QS2027: 741–750</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>THE2027: 451–500</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="n">
+      <c r="U4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr">
         <is>
           <t>SARI-1 (Ufuq) (2025)</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr"/>
       <c r="X4" s="4" t="inlineStr"/>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr"/>
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>Student team 'Ufuq' (SARI competition)</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>Saudi Space Agency (SARI student satellite competition)</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="n">
+      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AC4" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="AC4" s="5" t="inlineStr">
+      <c r="AD4" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AE4" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>• Ректор назначен королевским указом в октябре 2020 г.; актуальность на 2026 г. подтверждена только CV на официальном сайте (дата обновления не видна)
 • SARI-1 (Ufuq, PocketQube 1p) — победитель конкурса SARI Саудовского космического агентства; запуск 28.11.2025 (Transporter-15, через Alba Orbital), статус на орбите неизвестен
@@ -2743,7 +2805,7 @@
 • Имя текущего руководителя подразделения международного сотрудничества не подтверждено</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>• Https://uqu.edu.sa/en/rect
 • Https://uqu.edu.sa/en/icu/App/Contact
@@ -2754,12 +2816,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -2823,71 +2885,76 @@
 Обращение: Dear Head of Global Communications,</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>global.pr@kaust.edu.sa</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>https://www.kaust.edu.sa</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>Prof. Sir Edward Byrne AC</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>President &amp; Chief Academic Officer</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="4" t="inlineStr"/>
       <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="n">
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V5" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t>KAUSTSat (Lemur-2 ONREFLECTION, 6U, with Spire Global) (2023)</t>
         </is>
       </c>
-      <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr"/>
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>Climate and Livability Initiative / Hydrology, Agriculture and Land Observation group (Prof. Matthew McCabe) — KAUSTSat mission</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>Spire Global (KAUSTSat platform, launch on SpaceX Transporter-7)</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="n">
+      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AC5" s="5" t="inlineStr">
+      <c r="AD5" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD5" s="4" t="inlineStr">
+      <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr">
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>• Общий e-mail не опубликован; global.pr@kaust.edu.sa — ящик медиа/PR (Global PR and in-Kingdom inquiries), используется как единственный неадмиссионный адрес
 • Отдел партнёрств (Partnerships Office, &gt;40 международных соглашений) упомянут на сайте, но e-mail и руководитель не опубликованы
@@ -2896,7 +2963,7 @@
 • Телефон на официальной странице контактов не опубликован</t>
         </is>
       </c>
-      <c r="AG5" s="4" t="inlineStr">
+      <c r="AH5" s="4" t="inlineStr">
         <is>
           <t>• Https://www.kaust.edu.sa/en/about/administration/president
 • Https://www.kaust.edu.sa/en/contact
@@ -2906,12 +2973,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -2977,92 +3044,97 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
           <t>global@kfupm.edu.sa</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>info@kfupm.edu.sa</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>+966 13 860 0000</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>https://www.kfupm.edu.sa</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>Dr. Muhammad M. Al-Saggaf</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr">
+      <c r="S6" s="4" t="inlineStr">
         <is>
           <t>QS2027: 63</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="T6" s="4" t="inlineStr">
         <is>
           <t>THE2027: =176</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="n">
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="4" t="inlineStr"/>
-      <c r="W6" s="4" t="inlineStr">
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr">
         <is>
           <t>• Opti-K 6U CubeSat with optical transmitter (with Astrolight)
 • Dual 8U Earth-observation satellite mission (GomSpace MoU, Sep 2026)
 • High-altitude balloon CubeSat platform</t>
         </is>
       </c>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="Y6" s="4" t="inlineStr">
         <is>
           <t>Student-built ground station (IRC-ASE); Optical Ground Station with 360° tracking (Opti-K, in development)</t>
         </is>
       </c>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>Interdisciplinary Research Center for Aviation &amp; Space Exploration (IRC-ASE), Director Dr. Ayman Abdallah, irc-ase@kfupm.edu.sa</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>• GomSpace (MoU, 2026)
 • Astrolight (Opti-K)</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="n">
+      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AC6" s="6" t="inlineStr">
+      <c r="AD6" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD6" s="4" t="inlineStr">
+      <c r="AE6" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>• Спутников на орбите нет; активная космическая программа через IRC-ASE (создан в 2022 г.)
 • Сентябрь 2026: MoU с GomSpace о двойной 8U миссии ДЗЗ — приоритетный кандидат для партнёрства по CubeSat
@@ -3070,7 +3142,7 @@
 • Для партнёрств по космосу дополнительно: irc-ase@kfupm.edu.sa, +966 13 860 5400</t>
         </is>
       </c>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AH6" s="4" t="inlineStr">
         <is>
           <t>• Https://www.kfupm.edu.sa/about-us/our-story/leadership
 • Https://www.kfupm.edu.sa/about-us/connect/contact-us
@@ -3081,12 +3153,12 @@
 • Https://gomspace.com/gomspace-and-kfupm-sign-mou-to-explore-strategic-cooperation-in-space-technology/</t>
         </is>
       </c>
-      <c r="AH6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -3149,86 +3221,91 @@
 Обращение: Dear Sir or Madam,</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>info@psu.edu.sa</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>+966 11 494 8000</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>https://www.psu.edu.sa</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Dr. Ahmed S. Yamani</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>President (Rector)</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t>QS2027: 488</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>THE2027: 376–400</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="n">
+      <c r="U7" s="4" t="inlineStr"/>
+      <c r="V7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="4" t="inlineStr">
+      <c r="W7" s="4" t="inlineStr">
         <is>
           <t>Rawdat Scoop (SARI-2, PocketQube 1p) (2025)</t>
         </is>
       </c>
-      <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr"/>
       <c r="Y7" s="4" t="inlineStr"/>
-      <c r="Z7" s="4" t="inlineStr">
+      <c r="Z7" s="4" t="inlineStr"/>
+      <c r="AA7" s="4" t="inlineStr">
         <is>
           <t>Saudi Space Agency (SARI student small-satellite competition — PSU design selected for flight, launched Nov 2025)</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="n">
+      <c r="AB7" s="4" t="inlineStr"/>
+      <c r="AC7" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AC7" s="5" t="inlineStr">
+      <c r="AD7" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD7" s="4" t="inlineStr">
+      <c r="AE7" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr">
+      <c r="AF7" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт psu.edu.sa недоступен (HTTP 503 / ошибка TLS) — контакты взяты из справочника WIPO TISC, ФИО ректора — из Википедии; рекомендуется перепроверить
 • Спутник Rawdat Scoop (SARI-2) спроектирован студентами PSU в рамках конкурса SARI Саудовского космического агентства и запущен в ноябре 2025; статус на орбите неизвестен
 • E-mail международного отдела не найден</t>
         </is>
       </c>
-      <c r="AG7" s="4" t="inlineStr">
+      <c r="AH7" s="4" t="inlineStr">
         <is>
           <t>• Https://en.wikipedia.org/wiki/Prince_Sultan_University
 • Https://www.wipo.int/tisc/en/search/details.jsp?id=12475
@@ -3236,12 +3313,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -3294,42 +3371,47 @@
       </c>
       <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>+966 11 244 3999</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>https://ssa.gov.sa</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>Dr. Mohammed bin Saud Al-Tamimi</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>Chief Executive Officer (Acting CEO per April 2026 SPA statement)</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="n">
+      <c r="U8" s="4" t="inlineStr"/>
+      <c r="V8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="4" t="inlineStr">
+      <c r="W8" s="4" t="inlineStr">
         <is>
           <t>Shams (Space Weather CubeSat-1, SWC-1, 12U) (2026)</t>
         </is>
       </c>
-      <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="4" t="inlineStr">
+      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="Z8" s="4" t="inlineStr">
         <is>
           <t>• Saudi Human Spaceflight (HSF) Program
 • Shams space-weather mission
@@ -3338,7 +3420,7 @@
 • Space Academy</t>
         </is>
       </c>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="AA8" s="4" t="inlineStr">
         <is>
           <t>• NASA (Artemis II — Shams launched as SLS secondary payload, April 2026
 • US–Saudi civil aeronautics and space cooperation agreement)
@@ -3346,22 +3428,22 @@
 • Umm Al-Qura University and Prince Sultan University (SARI satellites, 2025)</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="n">
+      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AC8" s="5" t="inlineStr">
+      <c r="AD8" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD8" s="4" t="inlineStr"/>
-      <c r="AE8" s="4" t="inlineStr">
+      <c r="AE8" s="4" t="inlineStr"/>
+      <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF8" s="4" t="inlineStr">
+      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t>• Это государственное агентство, а не университет (включено намеренно)
 • Сайт ssa.gov.sa рендерится через JS — контактный e-mail не удалось прочитать; по поисковой выдаче общий адрес Info@ssa.gov.sa (в справочнике Eye of Riyadh — устаревший Info@ssc.gov.sa) — НЕ подтверждено, проверить перед отправкой
@@ -3370,7 +3452,7 @@
 • Спутник Shams (SWC-1) разработан в КСА, выведен 01.04.2026 в рамках Artemis II на высокоэллиптическую орбиту ~500–70 000 км (не VLEO)</t>
         </is>
       </c>
-      <c r="AG8" s="4" t="inlineStr">
+      <c r="AH8" s="4" t="inlineStr">
         <is>
           <t>• Https://ssa.gov.sa/en/about-ssa/
 • Https://www.iafastro.org/membership/all-members/saudi-space-commission-ssc.html
@@ -3381,12 +3463,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -3450,80 +3532,85 @@
 Обращение: Dear Dr. Al Ansari,</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>President@pmu.edu.sa</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>+966 13 849 8880</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>https://www.pmu.edu.sa</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>Dr. Issa Al Ansari</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>President (Rector)</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr">
+      <c r="S9" s="4" t="inlineStr">
         <is>
           <t>QS2027: 421</t>
         </is>
       </c>
-      <c r="S9" s="4" t="inlineStr">
+      <c r="T9" s="4" t="inlineStr">
         <is>
           <t>THE2027: 401–450</t>
         </is>
       </c>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="n">
+      <c r="U9" s="4" t="inlineStr"/>
+      <c r="V9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="4" t="inlineStr"/>
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr"/>
-      <c r="Y9" s="4" t="inlineStr">
+      <c r="Y9" s="4" t="inlineStr"/>
+      <c r="Z9" s="4" t="inlineStr">
         <is>
           <t>Space Research Center (listed among PMU research centers)</t>
         </is>
       </c>
-      <c r="Z9" s="4" t="inlineStr">
+      <c r="AA9" s="4" t="inlineStr">
         <is>
           <t>• ICESCO (strategic partnership incl. space sciences
 • Proposed CanSat training workshop, Sept 2025)</t>
         </is>
       </c>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="n">
+      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="AC9" s="7" t="inlineStr">
+      <c r="AD9" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD9" s="4" t="inlineStr">
+      <c r="AE9" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE9" s="4" t="inlineStr">
+      <c r="AF9" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF9" s="4" t="inlineStr">
+      <c r="AG9" s="4" t="inlineStr">
         <is>
           <t>• E-mail международного отдела (Department of International Affairs) не опубликован; использован адрес офиса президента President@pmu.edu.sa (также есть Info@pmu.edu.sa)
 • На старой оргсхеме директором International Affairs указана Mrs. Rania Sinno, но в текущем справочнике она числится директором Institutional Planning and Research — не использовано
@@ -3531,7 +3618,7 @@
 • Рейтинг QS2027: 421 по одному источнику, 422 по другому</t>
         </is>
       </c>
-      <c r="AG9" s="4" t="inlineStr">
+      <c r="AH9" s="4" t="inlineStr">
         <is>
           <t>• Https://www.pmu.edu.sa/About/Contact_Us.aspx
 • Https://www.pmu.edu.sa/global-engagement/
@@ -3540,12 +3627,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -3610,77 +3697,82 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
           <t>ic@kau.edu.sa</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>cic@kau.edu.sa</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>+966 12 640 0000</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>https://www.kau.edu.sa</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr">
+      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>Dr. Tareef bin Yousuf Alaama</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="inlineStr">
+      <c r="R10" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R10" s="4" t="inlineStr">
+      <c r="S10" s="4" t="inlineStr">
         <is>
           <t>QS2027: 200</t>
         </is>
       </c>
-      <c r="S10" s="4" t="inlineStr">
+      <c r="T10" s="4" t="inlineStr">
         <is>
           <t>THE2027: 401–450</t>
         </is>
       </c>
-      <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="4" t="n">
+      <c r="U10" s="4" t="inlineStr"/>
+      <c r="V10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="4" t="inlineStr"/>
       <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr"/>
-      <c r="Y10" s="4" t="inlineStr">
+      <c r="Y10" s="4" t="inlineStr"/>
+      <c r="Z10" s="4" t="inlineStr">
         <is>
           <t>Astronomy programme (Faculty of Science) — KAU offers astronomy, meteorology and marine science courses</t>
         </is>
       </c>
-      <c r="Z10" s="4" t="inlineStr"/>
       <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="n">
+      <c r="AB10" s="4" t="inlineStr"/>
+      <c r="AC10" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="AC10" s="8" t="inlineStr">
+      <c r="AD10" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD10" s="4" t="inlineStr">
+      <c r="AE10" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE10" s="4" t="inlineStr">
+      <c r="AF10" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF10" s="4" t="inlineStr">
+      <c r="AG10" s="4" t="inlineStr">
         <is>
           <t>• Ректор (с февраля 2024) подтверждён по Википедии; на официальном сайте страница ректора не найдена (сайт на JS)
 • Ic@kau.edu.sa — Управление глобального и внешнего взаимодействия (Department of International Cooperation Agreements, подчиняется ректору); руководитель не указан
@@ -3688,7 +3780,7 @@
 • Спутников, построенных КАУ, не найдено</t>
         </is>
       </c>
-      <c r="AG10" s="4" t="inlineStr">
+      <c r="AH10" s="4" t="inlineStr">
         <is>
           <t>• Https://kau.edu.sa/en/page/contact-us
 • Https://kau.edu.sa/en/page/global-and-external-engagement
@@ -3698,12 +3790,12 @@
 • Https://en.wikipedia.org/wiki/King_Abdulaziz_University</t>
         </is>
       </c>
-      <c r="AH10" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI10" s="4" t="inlineStr"/>
+      <c r="AI10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -3766,71 +3858,76 @@
 Обращение: Dear Director of Communications,</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr"/>
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>cm.dir@iau.edu.sa</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>+966 13 333 0030</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>https://www.iau.edu.sa</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>Prof. Dr. Fahad bin Ahmed Alharbi</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr">
+      <c r="S11" s="4" t="inlineStr">
         <is>
           <t>QS2027: 474</t>
         </is>
       </c>
-      <c r="S11" s="4" t="inlineStr">
+      <c r="T11" s="4" t="inlineStr">
         <is>
           <t>THE2027: 651–700</t>
         </is>
       </c>
-      <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="4" t="n">
+      <c r="U11" s="4" t="inlineStr"/>
+      <c r="V11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="4" t="inlineStr"/>
       <c r="W11" s="4" t="inlineStr"/>
       <c r="X11" s="4" t="inlineStr"/>
       <c r="Y11" s="4" t="inlineStr"/>
       <c r="Z11" s="4" t="inlineStr"/>
       <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="n">
+      <c r="AB11" s="4" t="inlineStr"/>
+      <c r="AC11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC11" s="8" t="inlineStr">
+      <c r="AD11" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD11" s="4" t="inlineStr">
+      <c r="AE11" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE11" s="4" t="inlineStr">
+      <c r="AF11" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF11" s="4" t="inlineStr">
+      <c r="AG11" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт iau.edu.sa недоступен из-за геоблокировки (HTTP 503 / сброс соединения); контакты — из справочника WIPO TISC
 • Ректор проф. Фахад аль-Харби назначен королевским указом (новость IAU, июль 2025); в Википедии также упоминается прежний ректор Абдулла ар-Рубаиш — использовать аль-Харби
@@ -3838,19 +3935,19 @@
 • E-mail международного отдела не найден; космических проектов не найдено</t>
         </is>
       </c>
-      <c r="AG11" s="4" t="inlineStr">
+      <c r="AH11" s="4" t="inlineStr">
         <is>
           <t>• Https://www.wipo.int/tisc/en/search/details.jsp?id=11748
 • Https://en.wikipedia.org/wiki/Imam_Abdulrahman_Bin_Faisal_University
 • Https://www.iau.edu.sa/en/news/professor-dr-fahd-al-harbi-president-of-imam-abdulrahman-bin-faisal-university</t>
         </is>
       </c>
-      <c r="AH11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -3916,73 +4013,78 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
+          <t>ПРОВЕРИТЬ: Ящик личный, имя адресата не совпадает с владельцем — уточнить владельца ящика</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
           <t>msalshehri@kku.edu.sa</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>kkurector@kku.edu.sa</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>+966 17 241 8000</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>https://www.kku.edu.sa</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>Prof. Falleh R. M. Al-Solamy</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="inlineStr">
+      <c r="R12" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R12" s="4" t="inlineStr">
+      <c r="S12" s="4" t="inlineStr">
         <is>
           <t>QS2027: 514</t>
         </is>
       </c>
-      <c r="S12" s="4" t="inlineStr">
+      <c r="T12" s="4" t="inlineStr">
         <is>
           <t>THE2027: 301–325</t>
         </is>
       </c>
-      <c r="T12" s="4" t="inlineStr"/>
-      <c r="U12" s="4" t="n">
+      <c r="U12" s="4" t="inlineStr"/>
+      <c r="V12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="4" t="inlineStr"/>
       <c r="W12" s="4" t="inlineStr"/>
       <c r="X12" s="4" t="inlineStr"/>
       <c r="Y12" s="4" t="inlineStr"/>
       <c r="Z12" s="4" t="inlineStr"/>
       <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="n">
+      <c r="AB12" s="4" t="inlineStr"/>
+      <c r="AC12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC12" s="8" t="inlineStr">
+      <c r="AD12" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD12" s="4" t="inlineStr">
+      <c r="AE12" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE12" s="4" t="inlineStr">
+      <c r="AF12" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF12" s="4" t="inlineStr">
+      <c r="AG12" s="4" t="inlineStr">
         <is>
           <t>• Ректор занимает пост с июня 2016 г.; официальная страница (обновлена 2026) указывает «June 2016 – Present»
 • Спутников не найдено (nanosats.csv и один поиск)
@@ -3990,7 +4092,7 @@
 • QS2027 по таблице qianmu.org (вторичный источник)</t>
         </is>
       </c>
-      <c r="AG12" s="4" t="inlineStr">
+      <c r="AH12" s="4" t="inlineStr">
         <is>
           <t>• Https://www.kku.edu.sa/en
 • Https://www.kku.edu.sa/en/portfolio/The-university-president
@@ -4001,12 +4103,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI12" s="4" t="inlineStr"/>
+      <c r="AI12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -4072,76 +4174,81 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
           <t>DICCR@psau.edu.sa</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>rector.office@psau.edu.sa</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr"/>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr"/>
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>https://www.psau.edu.sa</t>
         </is>
       </c>
-      <c r="P13" s="4" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>Prof. Abdullah Abdulaziz Altameem</t>
         </is>
       </c>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="R13" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="S13" s="4" t="inlineStr">
         <is>
           <t>QS2027: 677</t>
         </is>
       </c>
-      <c r="S13" s="4" t="inlineStr">
+      <c r="T13" s="4" t="inlineStr">
         <is>
           <t>THE2027: 401–450</t>
         </is>
       </c>
-      <c r="T13" s="4" t="inlineStr"/>
-      <c r="U13" s="4" t="n">
+      <c r="U13" s="4" t="inlineStr"/>
+      <c r="V13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="4" t="inlineStr"/>
       <c r="W13" s="4" t="inlineStr"/>
       <c r="X13" s="4" t="inlineStr"/>
       <c r="Y13" s="4" t="inlineStr"/>
       <c r="Z13" s="4" t="inlineStr"/>
       <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="n">
+      <c r="AB13" s="4" t="inlineStr"/>
+      <c r="AC13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC13" s="8" t="inlineStr">
+      <c r="AD13" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD13" s="4" t="inlineStr">
+      <c r="AE13" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE13" s="4" t="inlineStr">
+      <c r="AF13" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF13" s="4" t="inlineStr">
+      <c r="AG13" s="4" t="inlineStr">
         <is>
           <t>• Общий номер телефона на сайте не найден (только телефонный справочник/добавочные); добавочный директора отдела — 4460
 • Спутников не найдено (nanosats.csv и один поиск)
 • Отдел международного сотрудничества: DICCR@psau.edu.sa; директор — s.alabdulaziz@psau.edu.sa (страница обновлена 24.08.2026)</t>
         </is>
       </c>
-      <c r="AG13" s="4" t="inlineStr">
+      <c r="AH13" s="4" t="inlineStr">
         <is>
           <t>• Https://www.psau.edu.sa/en
 • Https://www.psau.edu.sa/en/presidents-message
@@ -4152,12 +4259,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH13" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI13" s="4" t="inlineStr"/>
+      <c r="AI13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -4216,71 +4323,76 @@
 Обращение: Dear Sir or Madam,</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>info@pnu.edu.sa</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>+966 11 822 0000</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>https://www.pnu.edu.sa</t>
         </is>
       </c>
-      <c r="P14" s="4" t="inlineStr">
+      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>Prof. Einas bint Suleiman Al-Eisa</t>
         </is>
       </c>
-      <c r="Q14" s="4" t="inlineStr">
+      <c r="R14" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R14" s="4" t="inlineStr">
+      <c r="S14" s="4" t="inlineStr">
         <is>
           <t>QS2027: 801–850</t>
         </is>
       </c>
-      <c r="S14" s="4" t="inlineStr">
+      <c r="T14" s="4" t="inlineStr">
         <is>
           <t>THE2027: 451–500</t>
         </is>
       </c>
-      <c r="T14" s="4" t="inlineStr"/>
-      <c r="U14" s="4" t="n">
+      <c r="U14" s="4" t="inlineStr"/>
+      <c r="V14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="4" t="inlineStr"/>
       <c r="W14" s="4" t="inlineStr"/>
       <c r="X14" s="4" t="inlineStr"/>
       <c r="Y14" s="4" t="inlineStr"/>
       <c r="Z14" s="4" t="inlineStr"/>
       <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="4" t="n">
+      <c r="AB14" s="4" t="inlineStr"/>
+      <c r="AC14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC14" s="8" t="inlineStr">
+      <c r="AD14" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD14" s="4" t="inlineStr">
+      <c r="AE14" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE14" s="4" t="inlineStr">
+      <c r="AF14" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF14" s="4" t="inlineStr">
+      <c r="AG14" s="4" t="inlineStr">
         <is>
           <t>• Женский университет (крупнейший женский университет страны) — учитывать при приглашении
 • E-mail международного отдела не найден на сайте; используется общий info@pnu.edu.sa (также pnu-tawasul@pnu.edu.sa — канал обращений)
@@ -4288,7 +4400,7 @@
 • Спутников в nanosats.csv и в быстрой проверке не найдено</t>
         </is>
       </c>
-      <c r="AG14" s="4" t="inlineStr">
+      <c r="AH14" s="4" t="inlineStr">
         <is>
           <t>• Https://www.pnu.edu.sa/en/Pages/ContactUsForm.aspx
 • Https://pnu.edu.sa/en/AboutUniversity/pages/home.aspx
@@ -4297,12 +4409,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH14" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI14" s="4" t="inlineStr"/>
+      <c r="AI14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -4365,67 +4477,72 @@
 Обращение: Dear Sir or Madam,</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr"/>
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>info@um.edu.sa</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>+966 11 253 2828</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>https://www.um.edu.sa</t>
         </is>
       </c>
-      <c r="P15" s="4" t="inlineStr">
+      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>Prof. Abdulrahman Abdullah Alsughayir</t>
         </is>
       </c>
-      <c r="Q15" s="4" t="inlineStr">
+      <c r="R15" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R15" s="4" t="inlineStr"/>
-      <c r="S15" s="4" t="inlineStr">
+      <c r="S15" s="4" t="inlineStr"/>
+      <c r="T15" s="4" t="inlineStr">
         <is>
           <t>THE2027: 701–800</t>
         </is>
       </c>
-      <c r="T15" s="4" t="inlineStr"/>
-      <c r="U15" s="4" t="n">
+      <c r="U15" s="4" t="inlineStr"/>
+      <c r="V15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="4" t="inlineStr"/>
       <c r="W15" s="4" t="inlineStr"/>
       <c r="X15" s="4" t="inlineStr"/>
       <c r="Y15" s="4" t="inlineStr"/>
       <c r="Z15" s="4" t="inlineStr"/>
       <c r="AA15" s="4" t="inlineStr"/>
-      <c r="AB15" s="4" t="n">
+      <c r="AB15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC15" s="8" t="inlineStr">
+      <c r="AD15" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD15" s="4" t="inlineStr">
+      <c r="AE15" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE15" s="4" t="inlineStr">
+      <c r="AF15" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF15" s="4" t="inlineStr">
+      <c r="AG15" s="4" t="inlineStr">
         <is>
           <t>• Частный университет медицинского профиля — низкая релевантность для спутниковой программы
 • E-mail международного отдела не найден; общий info@um.edu.sa; единый номер 920011909
@@ -4433,19 +4550,19 @@
 • Спутников не найдено</t>
         </is>
       </c>
-      <c r="AG15" s="4" t="inlineStr">
+      <c r="AH15" s="4" t="inlineStr">
         <is>
           <t>• Https://www.um.edu.sa/en
 • Https://www.um.edu.sa/en/%D9%83%D9%84%D9%85%D8%A9-%D9%85%D8%B9%D8%A7%D9%84%D9%8A-%D8%B1%D8%A6%D9%8A%D8%B3-%D8%A7%D9%84%D8%AC%D8%A7%D9%85%D8%B9%D8%A9-2/
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH15" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI15" s="4" t="inlineStr"/>
+      <c r="AI15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -4511,73 +4628,78 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
           <t>advancement@alfaisal.edu</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>info@alfaisal.edu</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>+966 11 215 7777</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>https://www.alfaisal.edu</t>
         </is>
       </c>
-      <c r="P16" s="4" t="inlineStr">
+      <c r="Q16" s="4" t="inlineStr">
         <is>
           <t>H.E. Dr. Mohammed Al Hayaza</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="inlineStr">
+      <c r="R16" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R16" s="4" t="inlineStr">
+      <c r="S16" s="4" t="inlineStr">
         <is>
           <t>QS2027: 801–850</t>
         </is>
       </c>
-      <c r="S16" s="4" t="inlineStr">
+      <c r="T16" s="4" t="inlineStr">
         <is>
           <t>THE2027: 501–550</t>
         </is>
       </c>
-      <c r="T16" s="4" t="inlineStr"/>
-      <c r="U16" s="4" t="n">
+      <c r="U16" s="4" t="inlineStr"/>
+      <c r="V16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="4" t="inlineStr"/>
       <c r="W16" s="4" t="inlineStr"/>
       <c r="X16" s="4" t="inlineStr"/>
       <c r="Y16" s="4" t="inlineStr"/>
       <c r="Z16" s="4" t="inlineStr"/>
       <c r="AA16" s="4" t="inlineStr"/>
-      <c r="AB16" s="4" t="n">
+      <c r="AB16" s="4" t="inlineStr"/>
+      <c r="AC16" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC16" s="8" t="inlineStr">
+      <c r="AD16" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD16" s="4" t="inlineStr">
+      <c r="AE16" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE16" s="4" t="inlineStr">
+      <c r="AF16" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF16" s="4" t="inlineStr">
+      <c r="AG16" s="4" t="inlineStr">
         <is>
           <t>• Частный некоммерческий университет (основан фондом короля Фейсала)
 • Космической программы и спутников не найдено (одна проверка)
@@ -4585,7 +4707,7 @@
 • Office of International Students &amp; Exchange (oise.alfaisal.edu) ориентирован на студентов</t>
         </is>
       </c>
-      <c r="AG16" s="4" t="inlineStr">
+      <c r="AH16" s="4" t="inlineStr">
         <is>
           <t>• Https://www.alfaisal.edu
 • Https://www.alfaisal.edu/en/contact
@@ -4594,12 +4716,12 @@
 • Https://oise.alfaisal.edu/</t>
         </is>
       </c>
-      <c r="AH16" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI16" s="4" t="inlineStr"/>
+      <c r="AI16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -4652,66 +4774,71 @@
       </c>
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="4" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M17" s="4" t="inlineStr"/>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr"/>
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>920003331 (unified number)</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>https://www.effatuniversity.edu.sa</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr">
+      <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>Dr. Haifa Reda Jamal Al-Lail</t>
         </is>
       </c>
-      <c r="Q17" s="4" t="inlineStr">
+      <c r="R17" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R17" s="4" t="inlineStr"/>
-      <c r="S17" s="4" t="inlineStr">
+      <c r="S17" s="4" t="inlineStr"/>
+      <c r="T17" s="4" t="inlineStr">
         <is>
           <t>THE2027: 601–650</t>
         </is>
       </c>
-      <c r="T17" s="4" t="inlineStr"/>
-      <c r="U17" s="4" t="n">
+      <c r="U17" s="4" t="inlineStr"/>
+      <c r="V17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="4" t="inlineStr"/>
       <c r="W17" s="4" t="inlineStr"/>
       <c r="X17" s="4" t="inlineStr"/>
       <c r="Y17" s="4" t="inlineStr"/>
       <c r="Z17" s="4" t="inlineStr"/>
       <c r="AA17" s="4" t="inlineStr"/>
-      <c r="AB17" s="4" t="n">
+      <c r="AB17" s="4" t="inlineStr"/>
+      <c r="AC17" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC17" s="8" t="inlineStr">
+      <c r="AD17" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD17" s="4" t="inlineStr"/>
-      <c r="AE17" s="4" t="inlineStr">
+      <c r="AE17" s="4" t="inlineStr"/>
+      <c r="AF17" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF17" s="4" t="inlineStr">
+      <c r="AG17" s="4" t="inlineStr">
         <is>
           <t>• Частный женский университет (учредитель — King Faisal Foundation)
 • Общий e-mail и e-mail международного отдела на сайте не опубликованы (есть только Effat.PACCE@effatuniversity.edu.sa — непрерывное образование); связь через форму Tawasul или единый номер 920003331
 • Спутников не найдено; студенты участвовали в космическом лагере в Нью-Йорке (2024)</t>
         </is>
       </c>
-      <c r="AG17" s="4" t="inlineStr">
+      <c r="AH17" s="4" t="inlineStr">
         <is>
           <t>• Https://www.effatuniversity.edu.sa/English/Pages/default.aspx
 • Https://www.effatuniversity.edu.sa/English/About/Contact-Us/Pages/default.aspx
@@ -4720,12 +4847,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH17" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI17" s="4" t="inlineStr"/>
+      <c r="AI17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -4789,71 +4916,76 @@
 Обращение: Dear President Alaameri,</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr"/>
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>op@imamu.edu.sa</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>+966 11 258 5214</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>https://imamu.edu.sa</t>
         </is>
       </c>
-      <c r="P18" s="4" t="inlineStr">
+      <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>Ahmed Alaameri</t>
         </is>
       </c>
-      <c r="Q18" s="4" t="inlineStr">
+      <c r="R18" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr">
+      <c r="S18" s="4" t="inlineStr">
         <is>
           <t>QS2027: 791–800</t>
         </is>
       </c>
-      <c r="S18" s="4" t="inlineStr">
+      <c r="T18" s="4" t="inlineStr">
         <is>
           <t>THE2027: 601–650</t>
         </is>
       </c>
-      <c r="T18" s="4" t="inlineStr"/>
-      <c r="U18" s="4" t="n">
+      <c r="U18" s="4" t="inlineStr"/>
+      <c r="V18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="4" t="inlineStr"/>
       <c r="W18" s="4" t="inlineStr"/>
       <c r="X18" s="4" t="inlineStr"/>
       <c r="Y18" s="4" t="inlineStr"/>
       <c r="Z18" s="4" t="inlineStr"/>
       <c r="AA18" s="4" t="inlineStr"/>
-      <c r="AB18" s="4" t="n">
+      <c r="AB18" s="4" t="inlineStr"/>
+      <c r="AC18" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC18" s="8" t="inlineStr">
+      <c r="AD18" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD18" s="4" t="inlineStr">
+      <c r="AE18" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE18" s="4" t="inlineStr">
+      <c r="AF18" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF18" s="4" t="inlineStr">
+      <c r="AG18" s="4" t="inlineStr">
         <is>
           <t>• Президент подтверждён по новости SPA (июль 2026 г.); учёное звание в источнике не указано
 • Op@imamu.edu.sa — e-mail для записи на приём к президенту (офис президента); телефоны офиса: 011 259 8762, 011 258 5214
@@ -4863,7 +4995,7 @@
 • Перепроверка: Повторный доступ к imamu.edu.sa блокируется WAF (страница «IMAMU Support», 04.10.2026) — обход не выполнялся; уровень повышен до medium на основании ранее подтверждённых данных (президент — SPA, июль 2026; e-mail офиса президента — официальный сайт), данные не изменены</t>
         </is>
       </c>
-      <c r="AG18" s="4" t="inlineStr">
+      <c r="AH18" s="4" t="inlineStr">
         <is>
           <t>• Https://imamu.edu.sa/en
 • Https://imamu.edu.sa/en/about-university/president-office
@@ -4873,12 +5005,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH18" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI18" s="4" t="inlineStr"/>
+      <c r="AI18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -4942,71 +5074,76 @@
 Обращение: Dear Director of the Partnerships and Knowledge Exchange Center,</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>care@iu.edu.sa</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>920022042</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>https://iu.edu.sa</t>
         </is>
       </c>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>Dr. Saleh bin Ali Al-Oqla (د. صالح بن علي العقلا)</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="R19" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R19" s="4" t="inlineStr">
+      <c r="S19" s="4" t="inlineStr">
         <is>
           <t>QS2027: 1001–1200</t>
         </is>
       </c>
-      <c r="S19" s="4" t="inlineStr">
+      <c r="T19" s="4" t="inlineStr">
         <is>
           <t>THE2027: 701–800</t>
         </is>
       </c>
-      <c r="T19" s="4" t="inlineStr"/>
-      <c r="U19" s="4" t="n">
+      <c r="U19" s="4" t="inlineStr"/>
+      <c r="V19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V19" s="4" t="inlineStr"/>
       <c r="W19" s="4" t="inlineStr"/>
       <c r="X19" s="4" t="inlineStr"/>
       <c r="Y19" s="4" t="inlineStr"/>
       <c r="Z19" s="4" t="inlineStr"/>
       <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="n">
+      <c r="AB19" s="4" t="inlineStr"/>
+      <c r="AC19" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC19" s="8" t="inlineStr">
+      <c r="AD19" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD19" s="4" t="inlineStr">
+      <c r="AE19" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE19" s="4" t="inlineStr">
+      <c r="AF19" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF19" s="4" t="inlineStr">
+      <c r="AG19" s="4" t="inlineStr">
         <is>
           <t>• Президент с мая 2024 г. (официальная CV на сайте); латинская транслитерация фамилии (العقلا) — наша, на сайте только по-арабски
 • Care@iu.edu.sa — служба по работе с обращениями (единственный опубликованный общий e-mail); телефон 920022042 — единый номер внутри КСА
@@ -5014,7 +5151,7 @@
 • Профиль преимущественно исламские/гуманитарные науки; спутников не найдено</t>
         </is>
       </c>
-      <c r="AG19" s="4" t="inlineStr">
+      <c r="AH19" s="4" t="inlineStr">
         <is>
           <t>• Https://iu.edu.sa
 • Https://iu.edu.sa/university
@@ -5024,12 +5161,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH19" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI19" s="4" t="inlineStr"/>
+      <c r="AI19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -5093,67 +5230,72 @@
 Обращение: Dear Dr. AbuRasain,</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr"/>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>president@jazanu.edu.sa</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>+966 17 329 5000</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>https://www.jazanu.edu.sa</t>
         </is>
       </c>
-      <c r="P20" s="4" t="inlineStr">
+      <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>Dr. Mohammad AbuRasain (Mohammed bin Hassan AbuRasain)</t>
         </is>
       </c>
-      <c r="Q20" s="4" t="inlineStr">
+      <c r="R20" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="4" t="inlineStr">
+      <c r="S20" s="4" t="inlineStr"/>
+      <c r="T20" s="4" t="inlineStr">
         <is>
           <t>THE2027: 701–800</t>
         </is>
       </c>
-      <c r="T20" s="4" t="inlineStr"/>
-      <c r="U20" s="4" t="n">
+      <c r="U20" s="4" t="inlineStr"/>
+      <c r="V20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="4" t="inlineStr"/>
       <c r="W20" s="4" t="inlineStr"/>
       <c r="X20" s="4" t="inlineStr"/>
       <c r="Y20" s="4" t="inlineStr"/>
       <c r="Z20" s="4" t="inlineStr"/>
       <c r="AA20" s="4" t="inlineStr"/>
-      <c r="AB20" s="4" t="n">
+      <c r="AB20" s="4" t="inlineStr"/>
+      <c r="AC20" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC20" s="8" t="inlineStr">
+      <c r="AD20" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD20" s="4" t="inlineStr">
+      <c r="AE20" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE20" s="4" t="inlineStr">
+      <c r="AF20" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF20" s="4" t="inlineStr">
+      <c r="AG20" s="4" t="inlineStr">
         <is>
           <t>• Сайт jazanu.edu.sa недоступен из нашей сети (HTTP 403 / сброс соединения) — e-mail president@jazanu.edu.sa, телефон и адрес взяты из поисковой выдачи по официальным страницам, НЕ открытым напрямую; обязательно перепроверить
 • Президент исправлен: Dr. Mohammad AbuRasain (Mohammed bin Hassan AbuRasain), с 17.05.2024 — подтверждено Saudi Press Agency 21.04.2026; ранее в строке ошибочно был указан Prof. Mar'ei bin Hussein Al-Qahtani (бывший президент)
@@ -5162,7 +5304,7 @@
 • Перепроверка: ИСПРАВЛЕНО: президент — д-р Мохаммад Абурасаин (SPA, 21.04.2026; в должности с 17.05.2024), а не Al-Qahtani; контакты по-прежнему не открыты (сайт 403)</t>
         </is>
       </c>
-      <c r="AG20" s="4" t="inlineStr">
+      <c r="AH20" s="4" t="inlineStr">
         <is>
           <t>• Https://www.jazanu.edu.sa/en/administration/departments/jupresident/contactinfo (via search index
 • Site blocked)
@@ -5171,12 +5313,12 @@
 • Https://spa.gov.sa/en/N2566500</t>
         </is>
       </c>
-      <c r="AH20" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI20" s="4" t="inlineStr"/>
+      <c r="AI20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -5239,78 +5381,83 @@
 Обращение: Dear Sir or Madam,</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr"/>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>contact@ju.edu.sa</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>+966 14 654 4444</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>https://www.ju.edu.sa</t>
         </is>
       </c>
-      <c r="P21" s="4" t="inlineStr">
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>Prof. Mohammed bin Abdullah Al-Shaya</t>
         </is>
       </c>
-      <c r="Q21" s="4" t="inlineStr">
+      <c r="R21" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R21" s="4" t="inlineStr">
+      <c r="S21" s="4" t="inlineStr">
         <is>
           <t>QS2027: 951–1000</t>
         </is>
       </c>
-      <c r="S21" s="4" t="inlineStr">
+      <c r="T21" s="4" t="inlineStr">
         <is>
           <t>THE2027: 651–700</t>
         </is>
       </c>
-      <c r="T21" s="4" t="inlineStr"/>
-      <c r="U21" s="4" t="n">
+      <c r="U21" s="4" t="inlineStr"/>
+      <c r="V21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="4" t="inlineStr"/>
       <c r="W21" s="4" t="inlineStr"/>
       <c r="X21" s="4" t="inlineStr"/>
       <c r="Y21" s="4" t="inlineStr"/>
       <c r="Z21" s="4" t="inlineStr"/>
       <c r="AA21" s="4" t="inlineStr"/>
-      <c r="AB21" s="4" t="n">
+      <c r="AB21" s="4" t="inlineStr"/>
+      <c r="AC21" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC21" s="8" t="inlineStr">
+      <c r="AD21" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD21" s="4" t="inlineStr">
+      <c r="AE21" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE21" s="4" t="inlineStr">
+      <c r="AF21" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF21" s="4" t="inlineStr">
+      <c r="AG21" s="4" t="inlineStr">
         <is>
           <t>• E-mail международного отдела не найден; используется общий contact@ju.edu.sa (колл-центр 014 654 4444)
 • Почтовый индекс/а/я не опубликованы на главной странице — адрес неполный
 • Спутников не найдено (nanosats.csv, сайт)</t>
         </is>
       </c>
-      <c r="AG21" s="4" t="inlineStr">
+      <c r="AH21" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ju.edu.sa/en
 • Https://www.ju.edu.sa/en/He-President-Jouf-University-launches-ai-course
@@ -5319,12 +5466,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH21" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI21" s="4" t="inlineStr"/>
+      <c r="AI21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -5390,73 +5537,78 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
           <t>ickea.info@kfu.edu.sa</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>info@kfu.edu.sa</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>920002366</t>
         </is>
       </c>
-      <c r="O22" s="4" t="inlineStr">
+      <c r="P22" s="4" t="inlineStr">
         <is>
           <t>https://www.kfu.edu.sa</t>
         </is>
       </c>
-      <c r="P22" s="4" t="inlineStr">
+      <c r="Q22" s="4" t="inlineStr">
         <is>
           <t>Prof. Adel bin Mohammed Abuzenadah</t>
         </is>
       </c>
-      <c r="Q22" s="4" t="inlineStr">
+      <c r="R22" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R22" s="4" t="inlineStr">
+      <c r="S22" s="4" t="inlineStr">
         <is>
           <t>QS2027: =567</t>
         </is>
       </c>
-      <c r="S22" s="4" t="inlineStr">
+      <c r="T22" s="4" t="inlineStr">
         <is>
           <t>THE2027: 551–600</t>
         </is>
       </c>
-      <c r="T22" s="4" t="inlineStr"/>
-      <c r="U22" s="4" t="n">
+      <c r="U22" s="4" t="inlineStr"/>
+      <c r="V22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="4" t="inlineStr"/>
       <c r="W22" s="4" t="inlineStr"/>
       <c r="X22" s="4" t="inlineStr"/>
       <c r="Y22" s="4" t="inlineStr"/>
       <c r="Z22" s="4" t="inlineStr"/>
       <c r="AA22" s="4" t="inlineStr"/>
-      <c r="AB22" s="4" t="n">
+      <c r="AB22" s="4" t="inlineStr"/>
+      <c r="AC22" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC22" s="8" t="inlineStr">
+      <c r="AD22" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD22" s="4" t="inlineStr">
+      <c r="AE22" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE22" s="4" t="inlineStr">
+      <c r="AF22" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF22" s="4" t="inlineStr">
+      <c r="AG22" s="4" t="inlineStr">
         <is>
           <t>• Президент (с октября 2024 г.) подтверждён по газете Al-Jazirah от 21.09.2026, на сайте университета страница ректора не открылась (меню на JavaScript)
 • Телефон 920002366 — единый номер (внутри КСА); отдел международного сотрудничества: +966 13 589 5298
@@ -5465,7 +5617,7 @@
 • Профиль: исторически аграрно-ветеринарный университет, ныне многопрофильный</t>
         </is>
       </c>
-      <c r="AG22" s="4" t="inlineStr">
+      <c r="AH22" s="4" t="inlineStr">
         <is>
           <t>• Https://www.kfu.edu.sa/en
 • Https://www.kfu.edu.sa/en/Departments/knowledgeExchange/Pages/Home-new.aspx
@@ -5475,12 +5627,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH22" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI22" s="4" t="inlineStr"/>
+      <c r="AI22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -5544,67 +5696,72 @@
 Обращение: Dear Director of International Affairs,</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr"/>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>ask_dar@ksau-hs.edu.sa</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>+966 11 429 9999</t>
         </is>
       </c>
-      <c r="O23" s="4" t="inlineStr">
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>https://www.ksau-hs.edu.sa</t>
         </is>
       </c>
-      <c r="P23" s="4" t="inlineStr">
+      <c r="Q23" s="4" t="inlineStr">
         <is>
           <t>Prof. Bandar Al-Knawy</t>
         </is>
       </c>
-      <c r="Q23" s="4" t="inlineStr">
+      <c r="R23" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R23" s="4" t="inlineStr"/>
-      <c r="S23" s="4" t="inlineStr">
+      <c r="S23" s="4" t="inlineStr"/>
+      <c r="T23" s="4" t="inlineStr">
         <is>
           <t>THE2027: 701–800</t>
         </is>
       </c>
-      <c r="T23" s="4" t="inlineStr"/>
-      <c r="U23" s="4" t="n">
+      <c r="U23" s="4" t="inlineStr"/>
+      <c r="V23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="4" t="inlineStr"/>
       <c r="W23" s="4" t="inlineStr"/>
       <c r="X23" s="4" t="inlineStr"/>
       <c r="Y23" s="4" t="inlineStr"/>
       <c r="Z23" s="4" t="inlineStr"/>
       <c r="AA23" s="4" t="inlineStr"/>
-      <c r="AB23" s="4" t="n">
+      <c r="AB23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC23" s="8" t="inlineStr">
+      <c r="AD23" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD23" s="4" t="inlineStr">
+      <c r="AE23" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE23" s="4" t="inlineStr">
+      <c r="AF23" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF23" s="4" t="inlineStr">
+      <c r="AG23" s="4" t="inlineStr">
         <is>
           <t>• Сайт ksau-hs.edu.sa не открывается (устаревший TLS — unsafe legacy renegotiation); адрес, телефон и e-mail взяты из поисковой выдачи официальной страницы контактов, не проверены вручную
 • Ask_dar@ksau-hs.edu.sa — e-mail деканата приёма и регистрации (другого общего адреса не найдено)
@@ -5614,7 +5771,7 @@
 • Перепроверка: Сайт ksau-hs.edu.sa по-прежнему не открывается (устаревший TLS и неполная цепочка сертификатов); данные не изменены</t>
         </is>
       </c>
-      <c r="AG23" s="4" t="inlineStr">
+      <c r="AH23" s="4" t="inlineStr">
         <is>
           <t>• Https://convention.bio.org/2026-sessions-and-courses/king-saud-bin-abdulaziz-university-for-health-sciences
 • Https://www.ksau-hs.edu.sa/English/About-Us/Pages/ContactKSAU.aspx
@@ -5622,12 +5779,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI23" s="4" t="inlineStr"/>
+      <c r="AI23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -5676,59 +5833,64 @@
       <c r="I24" s="4" t="inlineStr"/>
       <c r="J24" s="4" t="inlineStr"/>
       <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="4" t="inlineStr"/>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="N24" s="4" t="inlineStr"/>
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>+966 16 404 4444</t>
         </is>
       </c>
-      <c r="O24" s="4" t="inlineStr">
+      <c r="P24" s="4" t="inlineStr">
         <is>
           <t>https://www.mu.edu.sa</t>
         </is>
       </c>
-      <c r="P24" s="4" t="inlineStr">
+      <c r="Q24" s="4" t="inlineStr">
         <is>
           <t>Prof. Khaled bin Saad Al-Muqrin</t>
         </is>
       </c>
-      <c r="Q24" s="4" t="inlineStr">
+      <c r="R24" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R24" s="4" t="inlineStr"/>
-      <c r="S24" s="4" t="inlineStr">
+      <c r="S24" s="4" t="inlineStr"/>
+      <c r="T24" s="4" t="inlineStr">
         <is>
           <t>THE2027: 701–800</t>
         </is>
       </c>
-      <c r="T24" s="4" t="inlineStr"/>
-      <c r="U24" s="4" t="n">
+      <c r="U24" s="4" t="inlineStr"/>
+      <c r="V24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="4" t="inlineStr"/>
       <c r="W24" s="4" t="inlineStr"/>
       <c r="X24" s="4" t="inlineStr"/>
       <c r="Y24" s="4" t="inlineStr"/>
       <c r="Z24" s="4" t="inlineStr"/>
       <c r="AA24" s="4" t="inlineStr"/>
-      <c r="AB24" s="4" t="n">
+      <c r="AB24" s="4" t="inlineStr"/>
+      <c r="AC24" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC24" s="8" t="inlineStr">
+      <c r="AD24" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD24" s="4" t="inlineStr"/>
-      <c r="AE24" s="4" t="inlineStr">
+      <c r="AE24" s="4" t="inlineStr"/>
+      <c r="AF24" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF24" s="4" t="inlineStr">
+      <c r="AG24" s="4" t="inlineStr">
         <is>
           <t>• Сайт mu.edu.sa (и m.mu.edu.sa) недоступен из нашей сети (HTTP 403) — e-mail и адрес не проверены, не заполнены
 • ФИО президента — по Википедии (данные 2026 г.); учёное звание «Prof.» не подтверждено официальным сайтом; телефон — по поисковой выдаче (my.gov.sa), перепроверить
@@ -5736,19 +5898,19 @@
 • Перепроверка: 04.10.2026: mu.edu.sa (в т.ч. /en через WebFetch) и каталог my.gov.sa по-прежнему отдают 403; данные не изменены</t>
         </is>
       </c>
-      <c r="AG24" s="4" t="inlineStr">
+      <c r="AH24" s="4" t="inlineStr">
         <is>
           <t>• Https://en.wikipedia.org/wiki/Majmaah_University
 • Https://my.gov.sa/en/agencies/17441 (via search index)
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH24" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI24" s="4" t="inlineStr"/>
+      <c r="AI24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -5812,67 +5974,72 @@
 Обращение: Dear Director of International Affairs,</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr"/>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>care@nu.edu.sa</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>+966 17 542 8888</t>
         </is>
       </c>
-      <c r="O25" s="4" t="inlineStr">
+      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>https://www.nu.edu.sa</t>
         </is>
       </c>
-      <c r="P25" s="4" t="inlineStr">
+      <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>Dr. Abdulrahman bin Ibrahim Al-Khodairi</t>
         </is>
       </c>
-      <c r="Q25" s="4" t="inlineStr">
+      <c r="R25" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R25" s="4" t="inlineStr"/>
-      <c r="S25" s="4" t="inlineStr">
+      <c r="S25" s="4" t="inlineStr"/>
+      <c r="T25" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="T25" s="4" t="inlineStr"/>
-      <c r="U25" s="4" t="n">
+      <c r="U25" s="4" t="inlineStr"/>
+      <c r="V25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="4" t="inlineStr"/>
       <c r="W25" s="4" t="inlineStr"/>
       <c r="X25" s="4" t="inlineStr"/>
       <c r="Y25" s="4" t="inlineStr"/>
       <c r="Z25" s="4" t="inlineStr"/>
       <c r="AA25" s="4" t="inlineStr"/>
-      <c r="AB25" s="4" t="n">
+      <c r="AB25" s="4" t="inlineStr"/>
+      <c r="AC25" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC25" s="8" t="inlineStr">
+      <c r="AD25" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD25" s="4" t="inlineStr">
+      <c r="AE25" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE25" s="4" t="inlineStr">
+      <c r="AF25" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF25" s="4" t="inlineStr">
+      <c r="AG25" s="4" t="inlineStr">
         <is>
           <t>• Президент подтверждён новостью сайта к Нацдню (сентябрь 2026)
 • Care@nu.edu.sa — центр обслуживания обращений (официальная страница «Связаться с нами»); info@nu.edu.sa, адрес и телефон — из вторичного каталога LabOasis
@@ -5880,7 +6047,7 @@
 • Международный отдел и его руководитель на сайте не найдены; спутников не найдено</t>
         </is>
       </c>
-      <c r="AG25" s="4" t="inlineStr">
+      <c r="AH25" s="4" t="inlineStr">
         <is>
           <t>• Https://www.nu.edu.sa/en
 • Https://portal.nu.edu.sa/contact-us
@@ -5890,12 +6057,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH25" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI25" s="4" t="inlineStr"/>
+      <c r="AI25" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -5959,78 +6126,83 @@
 Обращение: Dear Prof. Al-Rumaih,</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr"/>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>opu@nbu.edu.sa</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>+966 14 661 4005</t>
         </is>
       </c>
-      <c r="O26" s="4" t="inlineStr">
+      <c r="P26" s="4" t="inlineStr">
         <is>
           <t>https://www.nbu.edu.sa</t>
         </is>
       </c>
-      <c r="P26" s="4" t="inlineStr">
+      <c r="Q26" s="4" t="inlineStr">
         <is>
           <t>Prof. Dr. Ahmed bin Ali Al-Rumaih</t>
         </is>
       </c>
-      <c r="Q26" s="4" t="inlineStr">
+      <c r="R26" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R26" s="4" t="inlineStr">
+      <c r="S26" s="4" t="inlineStr">
         <is>
           <t>QS2027: 1001–1200</t>
         </is>
       </c>
-      <c r="S26" s="4" t="inlineStr">
+      <c r="T26" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="T26" s="4" t="inlineStr"/>
-      <c r="U26" s="4" t="n">
+      <c r="U26" s="4" t="inlineStr"/>
+      <c r="V26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="4" t="inlineStr"/>
       <c r="X26" s="4" t="inlineStr"/>
       <c r="Y26" s="4" t="inlineStr"/>
       <c r="Z26" s="4" t="inlineStr"/>
       <c r="AA26" s="4" t="inlineStr"/>
-      <c r="AB26" s="4" t="n">
+      <c r="AB26" s="4" t="inlineStr"/>
+      <c r="AC26" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC26" s="8" t="inlineStr">
+      <c r="AD26" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD26" s="4" t="inlineStr">
+      <c r="AE26" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE26" s="4" t="inlineStr">
+      <c r="AF26" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF26" s="4" t="inlineStr">
+      <c r="AG26" s="4" t="inlineStr">
         <is>
           <t>• ФИО президента на сайте только по-арабски (الأستاذ الدكتور أحمد بن علي الرميح) — латинская транслитерация наша
 • E-mail международного отдела не найден; используется адрес офиса президента opu@nbu.edu.sa (факс +966 14 662 0771)
 • Спутников не найдено (nanosats.csv, сайт)</t>
         </is>
       </c>
-      <c r="AG26" s="4" t="inlineStr">
+      <c r="AH26" s="4" t="inlineStr">
         <is>
           <t>• Https://www.nbu.edu.sa/
 • Https://www.nbu.edu.sa/university-administration/university-manager
@@ -6039,12 +6211,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH26" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI26" s="4" t="inlineStr"/>
+      <c r="AI26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -6110,80 +6282,85 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
           <t>cir@qu.edu.sa</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>info@qu.edu.sa</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>+966 16 301 1111</t>
         </is>
       </c>
-      <c r="O27" s="4" t="inlineStr">
+      <c r="P27" s="4" t="inlineStr">
         <is>
           <t>https://www.qu.edu.sa</t>
         </is>
       </c>
-      <c r="P27" s="4" t="inlineStr">
+      <c r="Q27" s="4" t="inlineStr">
         <is>
           <t>Prof. Mohammed bin Fahd Al Sharikh</t>
         </is>
       </c>
-      <c r="Q27" s="4" t="inlineStr">
+      <c r="R27" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R27" s="4" t="inlineStr">
+      <c r="S27" s="4" t="inlineStr">
         <is>
           <t>QS2027: 781–790</t>
         </is>
       </c>
-      <c r="S27" s="4" t="inlineStr">
+      <c r="T27" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="T27" s="4" t="inlineStr"/>
-      <c r="U27" s="4" t="n">
+      <c r="U27" s="4" t="inlineStr"/>
+      <c r="V27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="4" t="inlineStr"/>
       <c r="W27" s="4" t="inlineStr"/>
       <c r="X27" s="4" t="inlineStr"/>
       <c r="Y27" s="4" t="inlineStr"/>
       <c r="Z27" s="4" t="inlineStr"/>
       <c r="AA27" s="4" t="inlineStr"/>
-      <c r="AB27" s="4" t="n">
+      <c r="AB27" s="4" t="inlineStr"/>
+      <c r="AC27" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC27" s="8" t="inlineStr">
+      <c r="AD27" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD27" s="4" t="inlineStr">
+      <c r="AE27" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE27" s="4" t="inlineStr">
+      <c r="AF27" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF27" s="4" t="inlineStr">
+      <c r="AG27" s="4" t="inlineStr">
         <is>
           <t>• Президент — профессор электротехники (PhD, Ohio University); страница CV на официальном сайте, дата назначения не указана
 • Cir@qu.edu.sa (тел. +966 16 302 0768) в официальном справочнике значится за «Управлением обмена знаниями и научных мероприятий» (إدارة التبادل المعرفي والفعاليات العلمية); по поисковой выдаче — Центр международного сотрудничества и обмена знаниями; имя руководителя не найдено
 • Спутников не найдено (nanosats.csv и один поиск)</t>
         </is>
       </c>
-      <c r="AG27" s="4" t="inlineStr">
+      <c r="AH27" s="4" t="inlineStr">
         <is>
           <t>• Https://qu.edu.sa/en
 • Https://www.qu.edu.sa/en/university-president/cv/
@@ -6193,12 +6370,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH27" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI27" s="4" t="inlineStr"/>
+      <c r="AI27" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -6261,67 +6438,72 @@
 Обращение: Dear Sir or Madam,</t>
         </is>
       </c>
-      <c r="L28" s="4" t="inlineStr"/>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr"/>
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>info@su.edu.sa</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>+966 11 647 5075</t>
         </is>
       </c>
-      <c r="O28" s="4" t="inlineStr">
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>https://www.su.edu.sa</t>
         </is>
       </c>
-      <c r="P28" s="4" t="inlineStr">
+      <c r="Q28" s="4" t="inlineStr">
         <is>
           <t>Prof. Dr. Badr Saleh Elmehemed</t>
         </is>
       </c>
-      <c r="Q28" s="4" t="inlineStr">
+      <c r="R28" s="4" t="inlineStr">
         <is>
           <t>Acting President</t>
         </is>
       </c>
-      <c r="R28" s="4" t="inlineStr"/>
-      <c r="S28" s="4" t="inlineStr">
+      <c r="S28" s="4" t="inlineStr"/>
+      <c r="T28" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="T28" s="4" t="inlineStr"/>
-      <c r="U28" s="4" t="n">
+      <c r="U28" s="4" t="inlineStr"/>
+      <c r="V28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="4" t="inlineStr"/>
       <c r="W28" s="4" t="inlineStr"/>
       <c r="X28" s="4" t="inlineStr"/>
       <c r="Y28" s="4" t="inlineStr"/>
       <c r="Z28" s="4" t="inlineStr"/>
       <c r="AA28" s="4" t="inlineStr"/>
-      <c r="AB28" s="4" t="n">
+      <c r="AB28" s="4" t="inlineStr"/>
+      <c r="AC28" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC28" s="8" t="inlineStr">
+      <c r="AD28" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD28" s="4" t="inlineStr">
+      <c r="AE28" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE28" s="4" t="inlineStr">
+      <c r="AF28" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF28" s="4" t="inlineStr">
+      <c r="AG28" s="4" t="inlineStr">
         <is>
           <t>• Руководитель — исполняющий обязанности президента (Acting President) — должность может смениться
 • E-mail международного отдела не найден; общий info@su.edu.sa (факс +966 11 647 7762)
@@ -6329,7 +6511,7 @@
 • Спутников не найдено (nanosats.csv, сайт)</t>
         </is>
       </c>
-      <c r="AG28" s="4" t="inlineStr">
+      <c r="AH28" s="4" t="inlineStr">
         <is>
           <t>• Https://www.su.edu.sa/en
 • Https://www.su.edu.sa/en/contact/form
@@ -6337,12 +6519,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH28" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI28" s="4" t="inlineStr"/>
+      <c r="AI28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -6406,71 +6588,76 @@
 Обращение: Dear Dr. Al-Shahri,</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr"/>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>websupport@tu.edu.sa</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>+966 12 727 2020</t>
         </is>
       </c>
-      <c r="O29" s="4" t="inlineStr">
+      <c r="P29" s="4" t="inlineStr">
         <is>
           <t>https://www.tu.edu.sa</t>
         </is>
       </c>
-      <c r="P29" s="4" t="inlineStr">
+      <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>Prof. Yousef bin Abdu Asiri</t>
         </is>
       </c>
-      <c r="Q29" s="4" t="inlineStr">
+      <c r="R29" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R29" s="4" t="inlineStr">
+      <c r="S29" s="4" t="inlineStr">
         <is>
           <t>QS2027: 851–900</t>
         </is>
       </c>
-      <c r="S29" s="4" t="inlineStr">
+      <c r="T29" s="4" t="inlineStr">
         <is>
           <t>THE2027: 701–800</t>
         </is>
       </c>
-      <c r="T29" s="4" t="inlineStr"/>
-      <c r="U29" s="4" t="n">
+      <c r="U29" s="4" t="inlineStr"/>
+      <c r="V29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="4" t="inlineStr"/>
       <c r="W29" s="4" t="inlineStr"/>
       <c r="X29" s="4" t="inlineStr"/>
       <c r="Y29" s="4" t="inlineStr"/>
       <c r="Z29" s="4" t="inlineStr"/>
       <c r="AA29" s="4" t="inlineStr"/>
-      <c r="AB29" s="4" t="n">
+      <c r="AB29" s="4" t="inlineStr"/>
+      <c r="AC29" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC29" s="8" t="inlineStr">
+      <c r="AD29" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD29" s="4" t="inlineStr">
+      <c r="AE29" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE29" s="4" t="inlineStr">
+      <c r="AF29" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF29" s="4" t="inlineStr">
+      <c r="AG29" s="4" t="inlineStr">
         <is>
           <t>• Президент подтверждён новостью сайта от 20.09.2026
 • Единственный опубликованный e-mail — websupport@tu.edu.sa (техподдержка сайта); лучше использовать платформу партнёрств webapps1.tu.edu.sa/partnership
@@ -6478,7 +6665,7 @@
 • Спутников не найдено; кафедра компьютерной инженерии вела работы по CubeSat-прототипу для управления толпой (испытание на высоте 15 м, 2022)</t>
         </is>
       </c>
-      <c r="AG29" s="4" t="inlineStr">
+      <c r="AH29" s="4" t="inlineStr">
         <is>
           <t>• Https://www.tu.edu.sa/En
 • Https://www.tu.edu.sa/En/University/Pages/20291/Contact-Us
@@ -6490,12 +6677,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH29" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI29" s="4" t="inlineStr"/>
+      <c r="AI29" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -6558,71 +6745,76 @@
 Обращение: Dear Sir or Madam,</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr"/>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr"/>
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>info@uoh.edu.sa</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>+966 16 510 9200</t>
         </is>
       </c>
-      <c r="O30" s="4" t="inlineStr">
+      <c r="P30" s="4" t="inlineStr">
         <is>
           <t>https://www.uoh.edu.sa</t>
         </is>
       </c>
-      <c r="P30" s="4" t="inlineStr">
+      <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>Dr. Badr bin Shujaa Al-Harbi</t>
         </is>
       </c>
-      <c r="Q30" s="4" t="inlineStr">
+      <c r="R30" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R30" s="4" t="inlineStr">
+      <c r="S30" s="4" t="inlineStr">
         <is>
           <t>QS2027: 1001–1200</t>
         </is>
       </c>
-      <c r="S30" s="4" t="inlineStr">
+      <c r="T30" s="4" t="inlineStr">
         <is>
           <t>THE2027: 701–800</t>
         </is>
       </c>
-      <c r="T30" s="4" t="inlineStr"/>
-      <c r="U30" s="4" t="n">
+      <c r="U30" s="4" t="inlineStr"/>
+      <c r="V30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="4" t="inlineStr"/>
       <c r="W30" s="4" t="inlineStr"/>
       <c r="X30" s="4" t="inlineStr"/>
       <c r="Y30" s="4" t="inlineStr"/>
       <c r="Z30" s="4" t="inlineStr"/>
       <c r="AA30" s="4" t="inlineStr"/>
-      <c r="AB30" s="4" t="n">
+      <c r="AB30" s="4" t="inlineStr"/>
+      <c r="AC30" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC30" s="8" t="inlineStr">
+      <c r="AD30" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD30" s="4" t="inlineStr">
+      <c r="AE30" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE30" s="4" t="inlineStr">
+      <c r="AF30" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF30" s="4" t="inlineStr">
+      <c r="AG30" s="4" t="inlineStr">
         <is>
           <t>• E-mail международного отдела не найден; общий info@uoh.edu.sa
 • На сайте телефон указан с опечаткой «+996 165109200» — исправлено на +966
@@ -6630,7 +6822,7 @@
 • Спутников не найдено (nanosats.csv, сайт)</t>
         </is>
       </c>
-      <c r="AG30" s="4" t="inlineStr">
+      <c r="AH30" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uoh.edu.sa/
 • Https://www.uoh.edu.sa/Ar/Pages/Contacts.aspx
@@ -6639,12 +6831,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH30" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI30" s="4" t="inlineStr"/>
+      <c r="AI30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -6708,78 +6900,83 @@
 Обращение: Dear Head of International Partnerships and Cooperation,</t>
         </is>
       </c>
-      <c r="L31" s="4" t="inlineStr"/>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr"/>
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>ut@ut.edu.sa</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>+966 14 456 8000</t>
         </is>
       </c>
-      <c r="O31" s="4" t="inlineStr">
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>https://www.ut.edu.sa</t>
         </is>
       </c>
-      <c r="P31" s="4" t="inlineStr">
+      <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>Prof. Dr. Abdulaziz bin Salem Al-Ghamdi</t>
         </is>
       </c>
-      <c r="Q31" s="4" t="inlineStr">
+      <c r="R31" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R31" s="4" t="inlineStr">
+      <c r="S31" s="4" t="inlineStr">
         <is>
           <t>QS2027: 1001–1200</t>
         </is>
       </c>
-      <c r="S31" s="4" t="inlineStr">
+      <c r="T31" s="4" t="inlineStr">
         <is>
           <t>THE2027: 651–700</t>
         </is>
       </c>
-      <c r="T31" s="4" t="inlineStr"/>
-      <c r="U31" s="4" t="n">
+      <c r="U31" s="4" t="inlineStr"/>
+      <c r="V31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="4" t="inlineStr"/>
       <c r="W31" s="4" t="inlineStr"/>
       <c r="X31" s="4" t="inlineStr"/>
       <c r="Y31" s="4" t="inlineStr"/>
       <c r="Z31" s="4" t="inlineStr"/>
       <c r="AA31" s="4" t="inlineStr"/>
-      <c r="AB31" s="4" t="n">
+      <c r="AB31" s="4" t="inlineStr"/>
+      <c r="AC31" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC31" s="8" t="inlineStr">
+      <c r="AD31" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD31" s="4" t="inlineStr">
+      <c r="AE31" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE31" s="4" t="inlineStr">
+      <c r="AF31" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF31" s="4" t="inlineStr">
+      <c r="AG31" s="4" t="inlineStr">
         <is>
           <t>• Почтовый адрес (P.O. Box) на сайте не указан — только «Kingdom of Saudi Arabia - Tabuk»
 • Есть International Partnerships and Cooperation Unit (при проректорате по аспирантуре и науке), но контакты и руководитель на странице не опубликованы — письмо направлять на ut@ut.edu.sa
 • Спутников не найдено; сотрудники кафедры электротехники публикуют работы по системам питания CubeSat (Scientific Reports, 2026)</t>
         </is>
       </c>
-      <c r="AG31" s="4" t="inlineStr">
+      <c r="AH31" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ut.edu.sa/en
 • Https://www.ut.edu.sa/en/contact-us/contact-university
@@ -6789,12 +6986,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH31" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI31" s="4" t="inlineStr"/>
+      <c r="AI31" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -6853,67 +7050,72 @@
 Обращение: Dear Sir or Madam,</t>
         </is>
       </c>
-      <c r="L32" s="4" t="inlineStr"/>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr"/>
+      <c r="N32" s="4" t="inlineStr">
         <is>
           <t>contact@bu.edu.sa</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>+966 17 725 7700</t>
         </is>
       </c>
-      <c r="O32" s="4" t="inlineStr">
+      <c r="P32" s="4" t="inlineStr">
         <is>
           <t>https://www.bu.edu.sa</t>
         </is>
       </c>
-      <c r="P32" s="4" t="inlineStr">
+      <c r="Q32" s="4" t="inlineStr">
         <is>
           <t>Prof. Dr. Abdullah Alhussain</t>
         </is>
       </c>
-      <c r="Q32" s="4" t="inlineStr">
+      <c r="R32" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R32" s="4" t="inlineStr"/>
-      <c r="S32" s="4" t="inlineStr">
+      <c r="S32" s="4" t="inlineStr"/>
+      <c r="T32" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr"/>
-      <c r="U32" s="4" t="n">
+      <c r="U32" s="4" t="inlineStr"/>
+      <c r="V32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="4" t="inlineStr"/>
       <c r="W32" s="4" t="inlineStr"/>
       <c r="X32" s="4" t="inlineStr"/>
       <c r="Y32" s="4" t="inlineStr"/>
       <c r="Z32" s="4" t="inlineStr"/>
       <c r="AA32" s="4" t="inlineStr"/>
-      <c r="AB32" s="4" t="n">
+      <c r="AB32" s="4" t="inlineStr"/>
+      <c r="AC32" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC32" s="8" t="inlineStr">
+      <c r="AD32" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD32" s="4" t="inlineStr">
+      <c r="AE32" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE32" s="4" t="inlineStr">
+      <c r="AF32" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF32" s="4" t="inlineStr">
+      <c r="AG32" s="4" t="inlineStr">
         <is>
           <t>• Сайт bu.edu.sa недоступен из нашей сети (HTTP 503/обрыв соединения) — e-mail contact@bu.edu.sa, телефон (+966 17 725 7700, доб. 15005; факс +966 17 725 7777) и ФИО взяты из поисковой выдачи по странице офиса президента и Википедии; перепроверить
 • По той же выдаче директор офиса президента — Mr. Abdullah Alzahrani
@@ -6922,7 +7124,7 @@
 • Перепроверка: Сайт bu.edu.sa по-прежнему недоступен (04.10.2026: сброс соединения, WebFetch — 503); данные не изменены</t>
         </is>
       </c>
-      <c r="AG32" s="4" t="inlineStr">
+      <c r="AH32" s="4" t="inlineStr">
         <is>
           <t>• Https://bu.edu.sa/en/web/office-of-the-president (via search index
 • Site blocked)
@@ -6930,12 +7132,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH32" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI32" s="4" t="inlineStr"/>
+      <c r="AI32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -7001,69 +7203,74 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
           <t>bd@bmc.edu.sa</t>
         </is>
       </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>info@bmc.edu.sa</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>920033923</t>
         </is>
       </c>
-      <c r="O33" s="4" t="inlineStr">
+      <c r="P33" s="4" t="inlineStr">
         <is>
           <t>https://bmc.edu.sa</t>
         </is>
       </c>
-      <c r="P33" s="4" t="inlineStr">
+      <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>Prof. Mohammed Shaikh</t>
         </is>
       </c>
-      <c r="Q33" s="4" t="inlineStr">
+      <c r="R33" s="4" t="inlineStr">
         <is>
           <t>Dean</t>
         </is>
       </c>
-      <c r="R33" s="4" t="inlineStr"/>
-      <c r="S33" s="4" t="inlineStr">
+      <c r="S33" s="4" t="inlineStr"/>
+      <c r="T33" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="T33" s="4" t="inlineStr"/>
-      <c r="U33" s="4" t="n">
+      <c r="U33" s="4" t="inlineStr"/>
+      <c r="V33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="4" t="inlineStr"/>
       <c r="W33" s="4" t="inlineStr"/>
       <c r="X33" s="4" t="inlineStr"/>
       <c r="Y33" s="4" t="inlineStr"/>
       <c r="Z33" s="4" t="inlineStr"/>
       <c r="AA33" s="4" t="inlineStr"/>
-      <c r="AB33" s="4" t="n">
+      <c r="AB33" s="4" t="inlineStr"/>
+      <c r="AC33" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC33" s="8" t="inlineStr">
+      <c r="AD33" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD33" s="4" t="inlineStr">
+      <c r="AE33" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE33" s="4" t="inlineStr">
+      <c r="AF33" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF33" s="4" t="inlineStr">
+      <c r="AG33" s="4" t="inlineStr">
         <is>
           <t>• Частный медицинский колледж (кампусы в Джидде, Асире и Даммаме); руководитель — декан (Dean), а не президент
 • Bd@bmc.edu.sa — отдел развития бизнеса/партнёрств; International Student Office ориентирован на студентов
@@ -7071,7 +7278,7 @@
 • Медицинский профиль; спутников не найдено (проверка только по nanosats.csv)</t>
         </is>
       </c>
-      <c r="AG33" s="4" t="inlineStr">
+      <c r="AH33" s="4" t="inlineStr">
         <is>
           <t>• Https://bmc.edu.sa/en/
 • Https://bmc.edu.sa/en/About-BMC/Message-from-the-Dean
@@ -7080,12 +7287,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH33" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI33" s="4" t="inlineStr"/>
+      <c r="AI33" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -7137,59 +7344,64 @@
       </c>
       <c r="J34" s="4" t="inlineStr"/>
       <c r="K34" s="4" t="inlineStr"/>
-      <c r="L34" s="4" t="inlineStr"/>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M34" s="4" t="inlineStr"/>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="N34" s="4" t="inlineStr"/>
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>+966 11 500 0333</t>
         </is>
       </c>
-      <c r="O34" s="4" t="inlineStr">
+      <c r="P34" s="4" t="inlineStr">
         <is>
           <t>https://seu.edu.sa</t>
         </is>
       </c>
-      <c r="P34" s="4" t="inlineStr">
+      <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>Prof. Mohammed Yahya Mardi</t>
         </is>
       </c>
-      <c r="Q34" s="4" t="inlineStr">
+      <c r="R34" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R34" s="4" t="inlineStr"/>
-      <c r="S34" s="4" t="inlineStr">
+      <c r="S34" s="4" t="inlineStr"/>
+      <c r="T34" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="T34" s="4" t="inlineStr"/>
-      <c r="U34" s="4" t="n">
+      <c r="U34" s="4" t="inlineStr"/>
+      <c r="V34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="4" t="inlineStr"/>
       <c r="W34" s="4" t="inlineStr"/>
       <c r="X34" s="4" t="inlineStr"/>
       <c r="Y34" s="4" t="inlineStr"/>
       <c r="Z34" s="4" t="inlineStr"/>
       <c r="AA34" s="4" t="inlineStr"/>
-      <c r="AB34" s="4" t="n">
+      <c r="AB34" s="4" t="inlineStr"/>
+      <c r="AC34" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC34" s="8" t="inlineStr">
+      <c r="AD34" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD34" s="4" t="inlineStr"/>
-      <c r="AE34" s="4" t="inlineStr">
+      <c r="AE34" s="4" t="inlineStr"/>
+      <c r="AF34" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF34" s="4" t="inlineStr">
+      <c r="AG34" s="4" t="inlineStr">
         <is>
           <t>• Электронный (дистанционно-смешанный) университет с филиалами в 17 городах; инженерного/космического профиля нет
 • Общий e-mail на сайте не опубликован — обращения через форму «Contact Us» (seu.edu.sa/external) и X @SEU_Care
@@ -7197,7 +7409,7 @@
 • Спутников не найдено (проверка только по nanosats.csv — лимит веб-поиска исчерпан)</t>
         </is>
       </c>
-      <c r="AG34" s="4" t="inlineStr">
+      <c r="AH34" s="4" t="inlineStr">
         <is>
           <t>• Https://seu.edu.sa/en/
 • Https://seu.edu.sa/en/university-presidency/
@@ -7207,12 +7419,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH34" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI34" s="4" t="inlineStr"/>
+      <c r="AI34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -7276,71 +7488,76 @@
 Обращение: Dear Director of International Affairs,</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr"/>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>tu@taibahu.edu.sa</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="O35" s="4" t="inlineStr">
         <is>
           <t>+966 14 861 8888</t>
         </is>
       </c>
-      <c r="O35" s="4" t="inlineStr">
+      <c r="P35" s="4" t="inlineStr">
         <is>
           <t>https://www.taibahu.edu.sa</t>
         </is>
       </c>
-      <c r="P35" s="4" t="inlineStr">
+      <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>Dr. Nawal bint Mohammed Al-Rasheed</t>
         </is>
       </c>
-      <c r="Q35" s="4" t="inlineStr">
+      <c r="R35" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R35" s="4" t="inlineStr">
+      <c r="S35" s="4" t="inlineStr">
         <is>
           <t>QS2027: 1201–1400</t>
         </is>
       </c>
-      <c r="S35" s="4" t="inlineStr">
+      <c r="T35" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="T35" s="4" t="inlineStr"/>
-      <c r="U35" s="4" t="n">
+      <c r="U35" s="4" t="inlineStr"/>
+      <c r="V35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="4" t="inlineStr"/>
       <c r="W35" s="4" t="inlineStr"/>
       <c r="X35" s="4" t="inlineStr"/>
       <c r="Y35" s="4" t="inlineStr"/>
       <c r="Z35" s="4" t="inlineStr"/>
       <c r="AA35" s="4" t="inlineStr"/>
-      <c r="AB35" s="4" t="n">
+      <c r="AB35" s="4" t="inlineStr"/>
+      <c r="AC35" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC35" s="8" t="inlineStr">
+      <c r="AD35" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD35" s="4" t="inlineStr">
+      <c r="AE35" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE35" s="4" t="inlineStr">
+      <c r="AF35" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF35" s="4" t="inlineStr">
+      <c r="AG35" s="4" t="inlineStr">
         <is>
           <t>• Президент — первая женщина-ректор саудовского университета (с ноября 2023 г.); подтверждена новостью сайта от 07.04.2026
 • Tu@taibahu.edu.sa — официальный адрес для официальной переписки; tawasul@taibahu.edu.sa — общие запросы
@@ -7349,7 +7566,7 @@
 • Спутников не найдено (проверка только по nanosats.csv — лимит веб-поиска исчерпан)</t>
         </is>
       </c>
-      <c r="AG35" s="4" t="inlineStr">
+      <c r="AH35" s="4" t="inlineStr">
         <is>
           <t>• Https://www.taibahu.edu.sa/en/contact-us
 • Https://www.taibahu.edu.sa/en/administration-of-media-and-communication/media-center/news-53
@@ -7359,12 +7576,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH35" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI35" s="4" t="inlineStr"/>
+      <c r="AI35" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -7424,67 +7641,72 @@
 Обращение: Dear Professor Safhi,</t>
         </is>
       </c>
-      <c r="L36" s="4" t="inlineStr"/>
-      <c r="M36" s="4" t="inlineStr">
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr"/>
+      <c r="N36" s="4" t="inlineStr">
         <is>
           <t>president_office@ub.edu.sa</t>
         </is>
       </c>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <t>+966 17 623 8093 (President's Office)</t>
         </is>
       </c>
-      <c r="O36" s="4" t="inlineStr">
+      <c r="P36" s="4" t="inlineStr">
         <is>
           <t>https://www.ub.edu.sa</t>
         </is>
       </c>
-      <c r="P36" s="4" t="inlineStr">
+      <c r="Q36" s="4" t="inlineStr">
         <is>
           <t>Prof. Dr. Mohammed bin Mohsen Safhi</t>
         </is>
       </c>
-      <c r="Q36" s="4" t="inlineStr">
+      <c r="R36" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R36" s="4" t="inlineStr"/>
-      <c r="S36" s="4" t="inlineStr">
+      <c r="S36" s="4" t="inlineStr"/>
+      <c r="T36" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="T36" s="4" t="inlineStr"/>
-      <c r="U36" s="4" t="n">
+      <c r="U36" s="4" t="inlineStr"/>
+      <c r="V36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="4" t="inlineStr"/>
       <c r="W36" s="4" t="inlineStr"/>
       <c r="X36" s="4" t="inlineStr"/>
       <c r="Y36" s="4" t="inlineStr"/>
       <c r="Z36" s="4" t="inlineStr"/>
       <c r="AA36" s="4" t="inlineStr"/>
-      <c r="AB36" s="4" t="n">
+      <c r="AB36" s="4" t="inlineStr"/>
+      <c r="AC36" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC36" s="8" t="inlineStr">
+      <c r="AD36" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD36" s="4" t="inlineStr">
+      <c r="AE36" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE36" s="4" t="inlineStr">
+      <c r="AF36" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF36" s="4" t="inlineStr">
+      <c r="AG36" s="4" t="inlineStr">
         <is>
           <t>• Новый сайт ub.edu.sa — SPA; e-mail president_office@ub.edu.sa и телефон +966 17 623 8093 заданы в коде официальной страницы «Президент университета» (проверено 04.10.2026); ccm@ub.edu.sa — общий ящик из подвала сайта
 • Президент подтверждён новостью официального сайта за октябрь 2026 (أ.د. محمد بن محسن صفحي)
@@ -7493,7 +7715,7 @@
 • Перепроверка: Добавлены e-mail и телефон офиса президента с официальной страницы президента (04.10.2026); президент подтверждён новостями сайта 10.2026</t>
         </is>
       </c>
-      <c r="AG36" s="4" t="inlineStr">
+      <c r="AH36" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ub.edu.sa/
 • Https://www.ub.edu.sa/university-president (assets/university-president-Du7USWOi.js)
@@ -7501,12 +7723,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH36" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI36" s="4" t="inlineStr"/>
+      <c r="AI36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -7569,74 +7791,79 @@
 Обращение: Dear Sir or Madam,</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr"/>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr"/>
+      <c r="N37" s="4" t="inlineStr">
         <is>
           <t>info@uhb.edu.sa</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="O37" s="4" t="inlineStr">
         <is>
           <t>+966 13 720 4828</t>
         </is>
       </c>
-      <c r="O37" s="4" t="inlineStr">
+      <c r="P37" s="4" t="inlineStr">
         <is>
           <t>https://www.uhb.edu.sa</t>
         </is>
       </c>
-      <c r="P37" s="4" t="inlineStr">
+      <c r="Q37" s="4" t="inlineStr">
         <is>
           <t>Prof. Dr. Khalid bin Bani Al-Harbi</t>
         </is>
       </c>
-      <c r="Q37" s="4" t="inlineStr">
+      <c r="R37" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R37" s="4" t="inlineStr"/>
-      <c r="S37" s="4" t="inlineStr">
+      <c r="S37" s="4" t="inlineStr"/>
+      <c r="T37" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="T37" s="4" t="inlineStr"/>
-      <c r="U37" s="4" t="n">
+      <c r="U37" s="4" t="inlineStr"/>
+      <c r="V37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="4" t="inlineStr"/>
       <c r="W37" s="4" t="inlineStr"/>
       <c r="X37" s="4" t="inlineStr"/>
       <c r="Y37" s="4" t="inlineStr"/>
       <c r="Z37" s="4" t="inlineStr"/>
       <c r="AA37" s="4" t="inlineStr"/>
-      <c r="AB37" s="4" t="n">
+      <c r="AB37" s="4" t="inlineStr"/>
+      <c r="AC37" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC37" s="8" t="inlineStr">
+      <c r="AD37" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD37" s="4" t="inlineStr">
+      <c r="AE37" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE37" s="4" t="inlineStr">
+      <c r="AF37" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF37" s="4" t="inlineStr">
+      <c r="AG37" s="4" t="inlineStr">
         <is>
           <t>• ФИО президента взято из новости на арабской главной странице (أ.د. خالد بن باني الحربي, начало 1448 г.х. / 2026) — латиница наша
 • E-mail международного отдела не найден; общий info@uhb.edu.sa (факс +966 13 720 4931)
 • Спутников не найдено (nanosats.csv, сайт)</t>
         </is>
       </c>
-      <c r="AG37" s="4" t="inlineStr">
+      <c r="AH37" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uhb.edu.sa/en
 • Https://www.uhb.edu.sa/ar
@@ -7644,12 +7871,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH37" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI37" s="4" t="inlineStr"/>
+      <c r="AI37" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -7715,76 +7942,81 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
           <t>dgs@uj.edu.sa</t>
         </is>
       </c>
-      <c r="M38" s="4" t="inlineStr">
+      <c r="N38" s="4" t="inlineStr">
         <is>
           <t>info@uj.edu.sa</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>+966 12 233 4443</t>
         </is>
       </c>
-      <c r="O38" s="4" t="inlineStr">
+      <c r="P38" s="4" t="inlineStr">
         <is>
           <t>https://www.uj.edu.sa</t>
         </is>
       </c>
-      <c r="P38" s="4" t="inlineStr">
+      <c r="Q38" s="4" t="inlineStr">
         <is>
           <t>Prof. Obaid bin Ali Atiyan Al-Mudhaff</t>
         </is>
       </c>
-      <c r="Q38" s="4" t="inlineStr">
+      <c r="R38" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R38" s="4" t="inlineStr"/>
-      <c r="S38" s="4" t="inlineStr">
+      <c r="S38" s="4" t="inlineStr"/>
+      <c r="T38" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="T38" s="4" t="inlineStr"/>
-      <c r="U38" s="4" t="n">
+      <c r="U38" s="4" t="inlineStr"/>
+      <c r="V38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V38" s="4" t="inlineStr"/>
       <c r="W38" s="4" t="inlineStr"/>
       <c r="X38" s="4" t="inlineStr"/>
       <c r="Y38" s="4" t="inlineStr"/>
       <c r="Z38" s="4" t="inlineStr"/>
       <c r="AA38" s="4" t="inlineStr"/>
-      <c r="AB38" s="4" t="n">
+      <c r="AB38" s="4" t="inlineStr"/>
+      <c r="AC38" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC38" s="8" t="inlineStr">
+      <c r="AD38" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD38" s="4" t="inlineStr">
+      <c r="AE38" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE38" s="4" t="inlineStr">
+      <c r="AF38" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF38" s="4" t="inlineStr">
+      <c r="AG38" s="4" t="inlineStr">
         <is>
           <t>• Международное сотрудничество ведёт Деканат аспирантуры и международного сотрудничества (dgs@uj.edu.sa); есть также вице-декан по стипендиям/обучению dgs-vdean.sic@uj.edu.sa
 • Декан — Dr. Faten bint Mohammed Ali Zainalabdeen Zaini (по новости на сайте деканата, дата публикации не указана); вице-декан женского отделения и межд. сотрудничества — Dr. Samar Al-Jahdali
 • Спутников не найдено (проверка только по nanosats.csv — лимит веб-поиска исчерпан)</t>
         </is>
       </c>
-      <c r="AG38" s="4" t="inlineStr">
+      <c r="AH38" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uj.edu.sa/en
 • Https://www.uj.edu.sa/en/senior-leadership
@@ -7794,12 +8026,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH38" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI38" s="4" t="inlineStr"/>
+      <c r="AI38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -7864,65 +8096,70 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
+          <t>личный, совпало</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
           <t>m_mourad@yu.edu.sa</t>
         </is>
       </c>
-      <c r="M39" s="4" t="inlineStr">
+      <c r="N39" s="4" t="inlineStr">
         <is>
           <t>info@yu.edu.sa</t>
         </is>
       </c>
-      <c r="N39" s="4" t="inlineStr">
+      <c r="O39" s="4" t="inlineStr">
         <is>
           <t>+966 11 224 2222</t>
         </is>
       </c>
-      <c r="O39" s="4" t="inlineStr">
+      <c r="P39" s="4" t="inlineStr">
         <is>
           <t>https://yu.edu.sa</t>
         </is>
       </c>
-      <c r="P39" s="4" t="inlineStr">
+      <c r="Q39" s="4" t="inlineStr">
         <is>
           <t>Dr. Yazeed Al-Suhaibani</t>
         </is>
       </c>
-      <c r="Q39" s="4" t="inlineStr">
+      <c r="R39" s="4" t="inlineStr">
         <is>
           <t>Acting President</t>
         </is>
       </c>
-      <c r="R39" s="4" t="inlineStr"/>
       <c r="S39" s="4" t="inlineStr"/>
       <c r="T39" s="4" t="inlineStr"/>
-      <c r="U39" s="4" t="n">
+      <c r="U39" s="4" t="inlineStr"/>
+      <c r="V39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V39" s="4" t="inlineStr"/>
       <c r="W39" s="4" t="inlineStr"/>
       <c r="X39" s="4" t="inlineStr"/>
       <c r="Y39" s="4" t="inlineStr"/>
       <c r="Z39" s="4" t="inlineStr"/>
       <c r="AA39" s="4" t="inlineStr"/>
-      <c r="AB39" s="4" t="n">
+      <c r="AB39" s="4" t="inlineStr"/>
+      <c r="AC39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC39" s="8" t="inlineStr">
+      <c r="AD39" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD39" s="4" t="inlineStr">
+      <c r="AE39" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE39" s="4" t="inlineStr">
+      <c r="AF39" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF39" s="4" t="inlineStr">
+      <c r="AG39" s="4" t="inlineStr">
         <is>
           <t>• Частный университет (бизнес, инженерия, право); есть кампус в Эль-Хобаре
 • Global Engagement Office: директор Dr. Mashhour Mourad (m_mourad@yu.edu.sa, доб. 3001); менеджер по международным партнёрствам Ms. Raghad Balkhi (r_balkhi@yu.edu.sa, доб. 3043)
@@ -7930,7 +8167,7 @@
 • Не входит в THE2027/QS2027; спутников не найдено</t>
         </is>
       </c>
-      <c r="AG39" s="4" t="inlineStr">
+      <c r="AH39" s="4" t="inlineStr">
         <is>
           <t>• Https://yu.edu.sa/global-engagement-office/
 • Https://yu.edu.sa/about/about-yu/locate-us/
@@ -7938,12 +8175,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH39" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI39" s="4" t="inlineStr"/>
+      <c r="AI39" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -8006,63 +8243,68 @@
 Обращение: Dear Director of International Relations,</t>
         </is>
       </c>
-      <c r="L40" s="4" t="inlineStr"/>
-      <c r="M40" s="4" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr"/>
+      <c r="N40" s="4" t="inlineStr">
         <is>
           <t>info@arabou.edu.sa</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>+966 11 401 7878</t>
         </is>
       </c>
-      <c r="O40" s="4" t="inlineStr">
+      <c r="P40" s="4" t="inlineStr">
         <is>
           <t>https://www.arabou.edu.sa</t>
         </is>
       </c>
-      <c r="P40" s="4" t="inlineStr">
+      <c r="Q40" s="4" t="inlineStr">
         <is>
           <t>Prof. Dr. Ali bin Mohammed Al-Shahrani</t>
         </is>
       </c>
-      <c r="Q40" s="4" t="inlineStr">
+      <c r="R40" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R40" s="4" t="inlineStr"/>
       <c r="S40" s="4" t="inlineStr"/>
       <c r="T40" s="4" t="inlineStr"/>
-      <c r="U40" s="4" t="n">
+      <c r="U40" s="4" t="inlineStr"/>
+      <c r="V40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V40" s="4" t="inlineStr"/>
       <c r="W40" s="4" t="inlineStr"/>
       <c r="X40" s="4" t="inlineStr"/>
       <c r="Y40" s="4" t="inlineStr"/>
       <c r="Z40" s="4" t="inlineStr"/>
       <c r="AA40" s="4" t="inlineStr"/>
-      <c r="AB40" s="4" t="n">
+      <c r="AB40" s="4" t="inlineStr"/>
+      <c r="AC40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC40" s="8" t="inlineStr">
+      <c r="AD40" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD40" s="4" t="inlineStr">
+      <c r="AE40" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE40" s="4" t="inlineStr">
+      <c r="AF40" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF40" s="4" t="inlineStr">
+      <c r="AG40" s="4" t="inlineStr">
         <is>
           <t>• Саудовское отделение некоммерческого Арабского открытого университета (штаб-квартира в Кувейте), смешанное/дистанционное обучение; партнёр Open University (UK)
 • Есть раздел Local and International Relations, но отдельного e-mail/руководителя нет — использовать info@arabou.edu.sa; второй телефон +966 11 274 2696
@@ -8072,7 +8314,7 @@
 • Перепроверка: Президент, адрес, e-mail и телефоны подтверждены на сайте arabou.edu.sa 04.10.2026 (страница без даты, сайт обновляется в 2026)</t>
         </is>
       </c>
-      <c r="AG40" s="4" t="inlineStr">
+      <c r="AH40" s="4" t="inlineStr">
         <is>
           <t>• Https://www.arabou.edu.sa/
 • Https://www.arabou.edu.sa/about
@@ -8081,12 +8323,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH40" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI40" s="4" t="inlineStr"/>
+      <c r="AI40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -8149,63 +8391,68 @@
 Обращение: Dear Sir or Madam,</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr"/>
-      <c r="M41" s="4" t="inlineStr">
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr"/>
+      <c r="N41" s="4" t="inlineStr">
         <is>
           <t>info@dau.edu.sa</t>
         </is>
       </c>
-      <c r="N41" s="4" t="inlineStr">
+      <c r="O41" s="4" t="inlineStr">
         <is>
           <t>+966 11 494 9000</t>
         </is>
       </c>
-      <c r="O41" s="4" t="inlineStr">
+      <c r="P41" s="4" t="inlineStr">
         <is>
           <t>https://dau.edu.sa</t>
         </is>
       </c>
-      <c r="P41" s="4" t="inlineStr">
+      <c r="Q41" s="4" t="inlineStr">
         <is>
           <t>Prof. Dr. Hossam bin Mohammed Ramadan</t>
         </is>
       </c>
-      <c r="Q41" s="4" t="inlineStr">
+      <c r="R41" s="4" t="inlineStr">
         <is>
           <t>Acting President</t>
         </is>
       </c>
-      <c r="R41" s="4" t="inlineStr"/>
       <c r="S41" s="4" t="inlineStr"/>
       <c r="T41" s="4" t="inlineStr"/>
-      <c r="U41" s="4" t="n">
+      <c r="U41" s="4" t="inlineStr"/>
+      <c r="V41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V41" s="4" t="inlineStr"/>
       <c r="W41" s="4" t="inlineStr"/>
       <c r="X41" s="4" t="inlineStr"/>
       <c r="Y41" s="4" t="inlineStr"/>
       <c r="Z41" s="4" t="inlineStr"/>
       <c r="AA41" s="4" t="inlineStr"/>
-      <c r="AB41" s="4" t="n">
+      <c r="AB41" s="4" t="inlineStr"/>
+      <c r="AC41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC41" s="8" t="inlineStr">
+      <c r="AD41" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD41" s="4" t="inlineStr">
+      <c r="AE41" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE41" s="4" t="inlineStr">
+      <c r="AF41" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF41" s="4" t="inlineStr">
+      <c r="AG41" s="4" t="inlineStr">
         <is>
           <t>• Частный университет (медицина, стоматология, инженерия, право, бизнес)
 • Руководитель — исполняющий обязанности президента (رئيس الجامعة المكلف) с сентября 2026: أ.د. حسام بن محمد رمضان (латиница наша); до этого президентом был Prof. Dr. Khalid bin Abdulrahman Al-Hamoudi
@@ -8213,7 +8460,7 @@
 • Спутников не найдено</t>
         </is>
       </c>
-      <c r="AG41" s="4" t="inlineStr">
+      <c r="AH41" s="4" t="inlineStr">
         <is>
           <t>• Https://dau.edu.sa/
 • Https://dau.edu.sa/عن-الجامعة/اتصل-بنا-2/
@@ -8221,12 +8468,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH41" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI41" s="4" t="inlineStr"/>
+      <c r="AI41" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -8292,65 +8539,70 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
+          <t>ПРОВЕРИТЬ: Ящик личный, имя адресата не совпадает с владельцем — уточнить владельца ящика</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
           <t>BusinessDevelopment@dah.edu.sa</t>
         </is>
       </c>
-      <c r="M42" s="4" t="inlineStr">
+      <c r="N42" s="4" t="inlineStr">
         <is>
           <t>communications@dah.edu.sa</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>+966 12 630 3333</t>
         </is>
       </c>
-      <c r="O42" s="4" t="inlineStr">
+      <c r="P42" s="4" t="inlineStr">
         <is>
           <t>https://www.dah.edu.sa</t>
         </is>
       </c>
-      <c r="P42" s="4" t="inlineStr">
+      <c r="Q42" s="4" t="inlineStr">
         <is>
           <t>Dr. Abeer Abdulaziz Aldoghaither</t>
         </is>
       </c>
-      <c r="Q42" s="4" t="inlineStr">
+      <c r="R42" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R42" s="4" t="inlineStr"/>
       <c r="S42" s="4" t="inlineStr"/>
       <c r="T42" s="4" t="inlineStr"/>
-      <c r="U42" s="4" t="n">
+      <c r="U42" s="4" t="inlineStr"/>
+      <c r="V42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="4" t="inlineStr"/>
       <c r="W42" s="4" t="inlineStr"/>
       <c r="X42" s="4" t="inlineStr"/>
       <c r="Y42" s="4" t="inlineStr"/>
       <c r="Z42" s="4" t="inlineStr"/>
       <c r="AA42" s="4" t="inlineStr"/>
-      <c r="AB42" s="4" t="n">
+      <c r="AB42" s="4" t="inlineStr"/>
+      <c r="AC42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC42" s="8" t="inlineStr">
+      <c r="AD42" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD42" s="4" t="inlineStr">
+      <c r="AE42" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE42" s="4" t="inlineStr">
+      <c r="AF42" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF42" s="4" t="inlineStr">
+      <c r="AG42" s="4" t="inlineStr">
         <is>
           <t>• Частный некоммерческий женский университет (Джидда)
 • Communications@dah.edu.sa — отдел маркетинга и коммуникаций (отдельного общего/ректорского адреса нет); единый номер +966 9200 16965
@@ -8358,7 +8610,7 @@
 • Космического профиля нет; спутников не найдено (проверка только по nanosats.csv)</t>
         </is>
       </c>
-      <c r="AG42" s="4" t="inlineStr">
+      <c r="AH42" s="4" t="inlineStr">
         <is>
           <t>• Https://www.dah.edu.sa/en
 • Https://www.dah.edu.sa/en/about/Pages/President.aspx
@@ -8367,12 +8619,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH42" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI42" s="4" t="inlineStr"/>
+      <c r="AI42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -8434,63 +8686,68 @@
 Обращение: Dear Sir or Madam,</t>
         </is>
       </c>
-      <c r="L43" s="4" t="inlineStr"/>
-      <c r="M43" s="4" t="inlineStr">
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr"/>
+      <c r="N43" s="4" t="inlineStr">
         <is>
           <t>info@fbsu.edu.sa</t>
         </is>
       </c>
-      <c r="N43" s="4" t="inlineStr">
+      <c r="O43" s="4" t="inlineStr">
         <is>
           <t>+966 14 425 2500</t>
         </is>
       </c>
-      <c r="O43" s="4" t="inlineStr">
+      <c r="P43" s="4" t="inlineStr">
         <is>
           <t>https://www.fbsu.edu.sa</t>
         </is>
       </c>
-      <c r="P43" s="4" t="inlineStr">
+      <c r="Q43" s="4" t="inlineStr">
         <is>
           <t>Prof. Abdallah I. Husein Malkawi</t>
         </is>
       </c>
-      <c r="Q43" s="4" t="inlineStr">
+      <c r="R43" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R43" s="4" t="inlineStr"/>
       <c r="S43" s="4" t="inlineStr"/>
       <c r="T43" s="4" t="inlineStr"/>
-      <c r="U43" s="4" t="n">
+      <c r="U43" s="4" t="inlineStr"/>
+      <c r="V43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="4" t="inlineStr"/>
       <c r="W43" s="4" t="inlineStr"/>
       <c r="X43" s="4" t="inlineStr"/>
       <c r="Y43" s="4" t="inlineStr"/>
       <c r="Z43" s="4" t="inlineStr"/>
       <c r="AA43" s="4" t="inlineStr"/>
-      <c r="AB43" s="4" t="n">
+      <c r="AB43" s="4" t="inlineStr"/>
+      <c r="AC43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC43" s="8" t="inlineStr">
+      <c r="AD43" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD43" s="4" t="inlineStr">
+      <c r="AE43" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE43" s="4" t="inlineStr">
+      <c r="AF43" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF43" s="4" t="inlineStr">
+      <c r="AG43" s="4" t="inlineStr">
         <is>
           <t>• Частный университет в Табуке (с 2004 г.); 4 инженерные программы аккредитованы ABET
 • E-mail международного отдела не найден; общий info@fbsu.edu.sa
@@ -8498,7 +8755,7 @@
 • Спутников не найдено</t>
         </is>
       </c>
-      <c r="AG43" s="4" t="inlineStr">
+      <c r="AH43" s="4" t="inlineStr">
         <is>
           <t>• Https://www.fbsu.edu.sa/
 • Https://fbsu.edu.sa/Contacts
@@ -8506,12 +8763,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH43" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI43" s="4" t="inlineStr"/>
+      <c r="AI43" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -8559,47 +8816,52 @@
       <c r="I44" s="4" t="inlineStr"/>
       <c r="J44" s="4" t="inlineStr"/>
       <c r="K44" s="4" t="inlineStr"/>
-      <c r="L44" s="4" t="inlineStr"/>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M44" s="4" t="inlineStr"/>
       <c r="N44" s="4" t="inlineStr"/>
-      <c r="O44" s="4" t="inlineStr">
+      <c r="O44" s="4" t="inlineStr"/>
+      <c r="P44" s="4" t="inlineStr">
         <is>
           <t>https://www.jic.edu.sa</t>
         </is>
       </c>
-      <c r="P44" s="4" t="inlineStr"/>
-      <c r="Q44" s="4" t="inlineStr">
+      <c r="Q44" s="4" t="inlineStr"/>
+      <c r="R44" s="4" t="inlineStr">
         <is>
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="R44" s="4" t="inlineStr"/>
       <c r="S44" s="4" t="inlineStr"/>
       <c r="T44" s="4" t="inlineStr"/>
-      <c r="U44" s="4" t="n">
+      <c r="U44" s="4" t="inlineStr"/>
+      <c r="V44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V44" s="4" t="inlineStr"/>
       <c r="W44" s="4" t="inlineStr"/>
       <c r="X44" s="4" t="inlineStr"/>
       <c r="Y44" s="4" t="inlineStr"/>
       <c r="Z44" s="4" t="inlineStr"/>
       <c r="AA44" s="4" t="inlineStr"/>
-      <c r="AB44" s="4" t="n">
+      <c r="AB44" s="4" t="inlineStr"/>
+      <c r="AC44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC44" s="8" t="inlineStr">
+      <c r="AD44" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD44" s="4" t="inlineStr"/>
-      <c r="AE44" s="4" t="inlineStr">
+      <c r="AE44" s="4" t="inlineStr"/>
+      <c r="AF44" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF44" s="4" t="inlineStr">
+      <c r="AG44" s="4" t="inlineStr">
         <is>
           <t>• Сайт www.jic.edu.sa недоступен (DNS не разрешается/прокси отклоняет соединение), портал Королевской комиссии rcjy.edu.sa отвечает 503; лимит веб-поиска исчерпан — контакты и руководитель НЕ проверены
 • Колледж Королевской комиссии по Джубайлю и Янбу (не Минобразования); прикладной инженерно-технологический профиль; должность руководителя (Managing Director) не подтверждена
@@ -8608,17 +8870,17 @@
 • Перепроверка: Домен www.jic.edu.sa не разрешается, jic.edu.sa и rcjy.gov.sa недоступны (502 / сброс соединения) — данные не изменены (04.10.2026)</t>
         </is>
       </c>
-      <c r="AG44" s="4" t="inlineStr">
+      <c r="AH44" s="4" t="inlineStr">
         <is>
           <t>Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH44" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI44" s="4" t="inlineStr"/>
+      <c r="AI44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -8656,43 +8918,48 @@
       <c r="I45" s="4" t="inlineStr"/>
       <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr"/>
-      <c r="L45" s="4" t="inlineStr"/>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M45" s="4" t="inlineStr"/>
       <c r="N45" s="4" t="inlineStr"/>
-      <c r="O45" s="4" t="inlineStr">
+      <c r="O45" s="4" t="inlineStr"/>
+      <c r="P45" s="4" t="inlineStr">
         <is>
           <t>https://psaa.com.sa</t>
         </is>
       </c>
-      <c r="P45" s="4" t="inlineStr"/>
       <c r="Q45" s="4" t="inlineStr"/>
       <c r="R45" s="4" t="inlineStr"/>
       <c r="S45" s="4" t="inlineStr"/>
       <c r="T45" s="4" t="inlineStr"/>
-      <c r="U45" s="4" t="n">
+      <c r="U45" s="4" t="inlineStr"/>
+      <c r="V45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="4" t="inlineStr"/>
       <c r="W45" s="4" t="inlineStr"/>
       <c r="X45" s="4" t="inlineStr"/>
       <c r="Y45" s="4" t="inlineStr"/>
       <c r="Z45" s="4" t="inlineStr"/>
       <c r="AA45" s="4" t="inlineStr"/>
-      <c r="AB45" s="4" t="n">
+      <c r="AB45" s="4" t="inlineStr"/>
+      <c r="AC45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC45" s="8" t="inlineStr">
+      <c r="AD45" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD45" s="4" t="inlineStr"/>
-      <c r="AE45" s="4" t="inlineStr">
+      <c r="AE45" s="4" t="inlineStr"/>
+      <c r="AF45" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF45" s="4" t="inlineStr">
+      <c r="AG45" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт — https://psaa.com.sa (одностраничное приложение, в основном портал записи на курсы); psaa.edu.sa не резолвится
 • Сайт указывает расположение академии в Джидде и отдельную регистрацию для сотрудников Saudia — подтверждает принадлежность к группе Saudia
@@ -8701,7 +8968,7 @@
 • Перепроверка: Официальный сайт psaa.com.sa (SPA) открыт 04.10.2026: из его кода подтверждены расположение в Джидде и связь с Saudia (отдельная регистрация для сотрудников Saudia); руководитель, e-mail, телефон и адрес на сайте не опубликованы</t>
         </is>
       </c>
-      <c r="AG45" s="4" t="inlineStr">
+      <c r="AH45" s="4" t="inlineStr">
         <is>
           <t>• Https://psaa.com.sa/ (SPA
 • Текст из официального JS-бандла /static/js/main.ca029ecb.js)
@@ -8709,12 +8976,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH45" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI45" s="4" t="inlineStr"/>
+      <c r="AI45" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -8778,63 +9045,68 @@
 Обращение: Dear Director of International Affairs,</t>
         </is>
       </c>
-      <c r="L46" s="4" t="inlineStr"/>
-      <c r="M46" s="4" t="inlineStr">
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr"/>
+      <c r="N46" s="4" t="inlineStr">
         <is>
           <t>info@riyadh.edu.sa</t>
         </is>
       </c>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>+966 11 210 0000</t>
         </is>
       </c>
-      <c r="O46" s="4" t="inlineStr">
+      <c r="P46" s="4" t="inlineStr">
         <is>
           <t>https://www.riyadh.edu.sa</t>
         </is>
       </c>
-      <c r="P46" s="4" t="inlineStr">
+      <c r="Q46" s="4" t="inlineStr">
         <is>
           <t>Dr. Mohammed bin Abdullah Al-Rafei (د. محمد بن عبد الله الرافعي)</t>
         </is>
       </c>
-      <c r="Q46" s="4" t="inlineStr">
+      <c r="R46" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R46" s="4" t="inlineStr"/>
       <c r="S46" s="4" t="inlineStr"/>
       <c r="T46" s="4" t="inlineStr"/>
-      <c r="U46" s="4" t="n">
+      <c r="U46" s="4" t="inlineStr"/>
+      <c r="V46" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="4" t="inlineStr"/>
       <c r="W46" s="4" t="inlineStr"/>
       <c r="X46" s="4" t="inlineStr"/>
       <c r="Y46" s="4" t="inlineStr"/>
       <c r="Z46" s="4" t="inlineStr"/>
       <c r="AA46" s="4" t="inlineStr"/>
-      <c r="AB46" s="4" t="n">
+      <c r="AB46" s="4" t="inlineStr"/>
+      <c r="AC46" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC46" s="8" t="inlineStr">
+      <c r="AD46" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD46" s="4" t="inlineStr">
+      <c r="AE46" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE46" s="4" t="inlineStr">
+      <c r="AF46" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF46" s="4" t="inlineStr">
+      <c r="AG46" s="4" t="inlineStr">
         <is>
           <t>• Частный университет медико-стоматологического профиля (бывш. Riyadh Colleges of Dentistry and Pharmacy)
 • Президент указан на сайте по-арабски (фото загружено 29.10.2025); латинская транслитерация — наша
@@ -8842,7 +9114,7 @@
 • Космического профиля нет; спутников не найдено (проверка только по nanosats.csv)</t>
         </is>
       </c>
-      <c r="AG46" s="4" t="inlineStr">
+      <c r="AH46" s="4" t="inlineStr">
         <is>
           <t>• Https://www.riyadh.edu.sa/en
 • Https://www.riyadh.edu.sa/about
@@ -8850,12 +9122,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH46" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI46" s="4" t="inlineStr"/>
+      <c r="AI46" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -8917,67 +9189,72 @@
 Обращение: Dear Sir or Madam,</t>
         </is>
       </c>
-      <c r="L47" s="4" t="inlineStr"/>
-      <c r="M47" s="4" t="inlineStr">
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr"/>
+      <c r="N47" s="4" t="inlineStr">
         <is>
           <t>info@ubt.edu.sa</t>
         </is>
       </c>
-      <c r="N47" s="4" t="inlineStr">
+      <c r="O47" s="4" t="inlineStr">
         <is>
           <t>+966 920000490</t>
         </is>
       </c>
-      <c r="O47" s="4" t="inlineStr">
+      <c r="P47" s="4" t="inlineStr">
         <is>
           <t>https://www.ubt.edu.sa</t>
         </is>
       </c>
-      <c r="P47" s="4" t="inlineStr">
+      <c r="Q47" s="4" t="inlineStr">
         <is>
           <t>Dr. Weam Husni Tunsi</t>
         </is>
       </c>
-      <c r="Q47" s="4" t="inlineStr">
+      <c r="R47" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R47" s="4" t="inlineStr"/>
-      <c r="S47" s="4" t="inlineStr">
+      <c r="S47" s="4" t="inlineStr"/>
+      <c r="T47" s="4" t="inlineStr">
         <is>
           <t>THE2027: Reporter (unranked)</t>
         </is>
       </c>
-      <c r="T47" s="4" t="inlineStr"/>
-      <c r="U47" s="4" t="n">
+      <c r="U47" s="4" t="inlineStr"/>
+      <c r="V47" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="4" t="inlineStr"/>
       <c r="W47" s="4" t="inlineStr"/>
       <c r="X47" s="4" t="inlineStr"/>
       <c r="Y47" s="4" t="inlineStr"/>
       <c r="Z47" s="4" t="inlineStr"/>
       <c r="AA47" s="4" t="inlineStr"/>
-      <c r="AB47" s="4" t="n">
+      <c r="AB47" s="4" t="inlineStr"/>
+      <c r="AC47" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC47" s="8" t="inlineStr">
+      <c r="AD47" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD47" s="4" t="inlineStr">
+      <c r="AE47" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE47" s="4" t="inlineStr">
+      <c r="AF47" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF47" s="4" t="inlineStr">
+      <c r="AG47" s="4" t="inlineStr">
         <is>
           <t>• Частный университет бизнес-профиля (есть инженерный колледж и программы ИИ); низкая релевантность для спутниковой программы
 • В вузе есть подразделение International Partnership Affairs, но его e-mail/руководитель не опубликованы; используется общий info@ubt.edu.sa
@@ -8985,7 +9262,7 @@
 • В THE 2027 — только статус Reporter (без места); спутников не найдено</t>
         </is>
       </c>
-      <c r="AG47" s="4" t="inlineStr">
+      <c r="AH47" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ubt.edu.sa/
 • Https://www.ubt.edu.sa/about/ubtpresident
@@ -8993,12 +9270,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH47" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI47" s="4" t="inlineStr"/>
+      <c r="AI47" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -9062,65 +9339,70 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
           <t>vrbd@upm.edu.sa</t>
         </is>
       </c>
-      <c r="M48" s="4" t="inlineStr">
+      <c r="N48" s="4" t="inlineStr">
         <is>
           <t>President.Office@upm.edu.sa</t>
         </is>
       </c>
-      <c r="N48" s="4" t="inlineStr">
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>+966 920000238</t>
         </is>
       </c>
-      <c r="O48" s="4" t="inlineStr">
+      <c r="P48" s="4" t="inlineStr">
         <is>
           <t>https://www.upm.edu.sa</t>
         </is>
       </c>
-      <c r="P48" s="4" t="inlineStr">
+      <c r="Q48" s="4" t="inlineStr">
         <is>
           <t>Dr. Bandar bin Mohammed Hajjar</t>
         </is>
       </c>
-      <c r="Q48" s="4" t="inlineStr">
+      <c r="R48" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R48" s="4" t="inlineStr"/>
       <c r="S48" s="4" t="inlineStr"/>
       <c r="T48" s="4" t="inlineStr"/>
-      <c r="U48" s="4" t="n">
+      <c r="U48" s="4" t="inlineStr"/>
+      <c r="V48" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="4" t="inlineStr"/>
       <c r="W48" s="4" t="inlineStr"/>
       <c r="X48" s="4" t="inlineStr"/>
       <c r="Y48" s="4" t="inlineStr"/>
       <c r="Z48" s="4" t="inlineStr"/>
       <c r="AA48" s="4" t="inlineStr"/>
-      <c r="AB48" s="4" t="n">
+      <c r="AB48" s="4" t="inlineStr"/>
+      <c r="AC48" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC48" s="8" t="inlineStr">
+      <c r="AD48" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD48" s="4" t="inlineStr">
+      <c r="AE48" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE48" s="4" t="inlineStr">
+      <c r="AF48" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF48" s="4" t="inlineStr">
+      <c r="AG48" s="4" t="inlineStr">
         <is>
           <t>• Частный некоммерческий университет (Медина); президент назначен 18/1/1444 г.х. (август 2022); упоминается как президент в новости о TEDxUPM от 12.02.2026
 • Профиль — компьютерные науки, кибербезопасность, инженерия (выбран technical, не аэрокосмический в узком смысле)
@@ -9129,7 +9411,7 @@
 • Спутников не найдено (проверка только по nanosats.csv)</t>
         </is>
       </c>
-      <c r="AG48" s="4" t="inlineStr">
+      <c r="AH48" s="4" t="inlineStr">
         <is>
           <t>• Https://www.upm.edu.sa/en
 • Https://www.upm.edu.sa/en/about-upm#president-corner
@@ -9138,12 +9420,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH48" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI48" s="4" t="inlineStr"/>
+      <c r="AI48" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -9192,47 +9474,52 @@
       <c r="I49" s="4" t="inlineStr"/>
       <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr"/>
-      <c r="L49" s="4" t="inlineStr"/>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M49" s="4" t="inlineStr"/>
       <c r="N49" s="4" t="inlineStr"/>
-      <c r="O49" s="4" t="inlineStr">
-        <is>
-          <t>https://rcjy.edu.sa/en/colleges-and-institutes-in-yanbu/yanbu-industrial-college/home-yanbu-industrial-college/</t>
-        </is>
-      </c>
-      <c r="P49" s="4" t="inlineStr"/>
-      <c r="Q49" s="4" t="inlineStr">
+      <c r="O49" s="4" t="inlineStr"/>
+      <c r="P49" s="4" t="inlineStr">
+        <is>
+          <t>https://rcjy.edu.sa/en/colleges-and-institutes-in-yanbu/yanbu-industrial-college/home-yanbu-industrial-college</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="inlineStr"/>
+      <c r="R49" s="4" t="inlineStr">
         <is>
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="R49" s="4" t="inlineStr"/>
       <c r="S49" s="4" t="inlineStr"/>
       <c r="T49" s="4" t="inlineStr"/>
-      <c r="U49" s="4" t="n">
+      <c r="U49" s="4" t="inlineStr"/>
+      <c r="V49" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V49" s="4" t="inlineStr"/>
       <c r="W49" s="4" t="inlineStr"/>
       <c r="X49" s="4" t="inlineStr"/>
       <c r="Y49" s="4" t="inlineStr"/>
       <c r="Z49" s="4" t="inlineStr"/>
       <c r="AA49" s="4" t="inlineStr"/>
-      <c r="AB49" s="4" t="n">
+      <c r="AB49" s="4" t="inlineStr"/>
+      <c r="AC49" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC49" s="8" t="inlineStr">
+      <c r="AD49" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD49" s="4" t="inlineStr"/>
-      <c r="AE49" s="4" t="inlineStr">
+      <c r="AE49" s="4" t="inlineStr"/>
+      <c r="AF49" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF49" s="4" t="inlineStr">
+      <c r="AG49" s="4" t="inlineStr">
         <is>
           <t>• Колледж Королевской комиссии по Джубайлю и Янбу (Royal Commission), основан в 1989 г., расположен в промышленном городе Янбу
 • В Википедии руководителем указан Dr. Fahad Aloufi (без даты, вероятно устарело) — в head_name не внесено
@@ -9243,7 +9530,7 @@
 • Перепроверка: 04.10.2026: найден официальный раздел колледжа на rcjy.edu.sa (сайт обновлён); имя руководителя и e-mail там не опубликованы — остаётся low</t>
         </is>
       </c>
-      <c r="AG49" s="4" t="inlineStr">
+      <c r="AH49" s="4" t="inlineStr">
         <is>
           <t>• Https://rcjy.edu.sa/en/colleges-and-institutes-in-yanbu/yanbu-industrial-college/home-yanbu-industrial-college/
 • Https://rcjy.edu.sa/en/colleges-and-institutes-in-yanbu/yanbu-industrial-college/about-yanbu-industrial-college/organizational-structure-yanbu-industrial-college/
@@ -9252,15 +9539,15 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH49" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI49" s="4" t="inlineStr"/>
+      <c r="AI49" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ49" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI49"/>
+  <autoFilter ref="A1:AJ49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/research/brics_universities/output/BRICS_universities_saudi_arabia.xlsx
+++ b/research/brics_universities/output/BRICS_universities_saudi_arabia.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Саудовская Аравия" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AJ$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Саудовская Аравия'!$A$1:$AJ$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AK$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Саудовская Аравия'!$A$1:$AK$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ8"/>
+  <dimension ref="A1:AK8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -676,21 +676,22 @@
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="45" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="45" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="40" customWidth="1" min="26" max="26"/>
-    <col width="45" customWidth="1" min="27" max="27"/>
-    <col width="22" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="9" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="55" customWidth="1" min="33" max="33"/>
-    <col width="60" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="24" customWidth="1" min="36" max="36"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="40" customWidth="1" min="27" max="27"/>
+    <col width="45" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="55" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="24" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -801,75 +802,80 @@
       </c>
       <c r="V1" s="3" t="inlineStr">
         <is>
+          <t>Рейтинг Webometrics (мир)</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
           <t>Запущено КА (спутников)</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Названия запущенных КА (год)</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>КА в разработке</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>Наземная станция</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>Космические подразделения</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>Партнёрства в космической сфере</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>Санкционные / ограничительные списки (США)</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AD1" s="3" t="inlineStr">
         <is>
           <t>Космический индекс (0–100)</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AE1" s="3" t="inlineStr">
         <is>
           <t>Волна рассылки</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AF1" s="3" t="inlineStr">
         <is>
           <t>Проверка домена e-mail (MX)</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AG1" s="3" t="inlineStr">
         <is>
           <t>Достоверность</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>Дата проверки</t>
         </is>
       </c>
-      <c r="AJ1" s="3" t="inlineStr">
+      <c r="AK1" s="3" t="inlineStr">
         <is>
           <t>Секретарь парткома (справочно, Китай)</t>
         </is>
@@ -982,60 +988,70 @@
           <t>THE2027: 216</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
+      <c r="U2" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>KSU CubeSat (2021)</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>• KSU CubeSat-2 (second satellite approved in 2021
 • Current status unverified)</t>
         </is>
       </c>
-      <c r="Y2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>Satellite ground station at the College of Engineering (built during KSU CubeSat project)</t>
         </is>
       </c>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>College of Engineering – KSU CubeSat project team</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr"/>
       <c r="AB2" s="4" t="inlineStr"/>
-      <c r="AC2" s="4" t="n">
+      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AD2" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="AD2" s="5" t="inlineStr">
+      <c r="AE2" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE2" s="4" t="inlineStr">
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG2" s="4" t="inlineStr">
+      <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>• Ректор — исполняющий обязанности (Acting President) с июня 2025 г.; упоминается в новостях KSU от 30.09.2026
 • KSU CubeSat (1U) запущен 22.03.2021 на «Союз-2» с Байконура — первый спутник саудовского университета; сошёл с орбиты
 • Почта po@ksu.edu.sa — офис ректора; icstd@ksu.edu.sa — Global Engagement Office (مكتب الشراكات العالمية), тел. +966 11 469 7398
-• Дата последнего обновления страницы с руководителем GEO не указана</t>
-        </is>
-      </c>
-      <c r="AH2" s="4" t="inlineStr">
+• Дата последнего обновления страницы с руководителем GEO не указана
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI2" s="4" t="inlineStr">
         <is>
           <t>• Https://ksu.edu.sa/en/contact-us
 • Https://ksu.edu.sa/en
@@ -1045,15 +1061,18 @@
 • Https://chairs.ksu.edu.sa/en/node/113
 • Https://www.arabnews.com/node/1836141/saudi-arabia
 • Https://saudigazette.com.sa/article/604671
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI2" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ2" s="4" t="inlineStr"/>
+      <c r="AK2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -1147,13 +1166,22 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="n">
+      <c r="V3" s="4" t="inlineStr"/>
+      <c r="W3" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>• SaudiSat-1A (2000)
 • SaudiSat-1B (2000)
@@ -1174,50 +1202,51 @@
 • Shaheen Sat (2021)</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr"/>
       <c r="Y3" s="4" t="inlineStr"/>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="Z3" s="4" t="inlineStr"/>
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>• Space Research Institute (per Wikipedia
 • Current structure unverified)
 • National Satellite Technology Program</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr">
+      <c r="AB3" s="4" t="inlineStr">
         <is>
           <t>• Saudi Space Agency
 • CNSA (Chang'e-4 payload, 2018)</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="n">
+      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AD3" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="AD3" s="5" t="inlineStr">
+      <c r="AE3" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE3" s="4" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>• Сайт kacst.gov.sa недоступен (503/таймаут); адрес, телефон и media@kacst.gov.sa взяты из поисковой выдачи официальной страницы контактов
 • Президент в ранге министра; подтверждён в новости SPA от 11.02.2026
 • 17 спутников за 2000–2021 гг. (Saudipedia); SGS-1 (2019) — геостационарный спутник связи, изготовлен совместно с Lockheed Martin
 • Международный e-mail int_coop@kacst.edu.sa (страница IAF) — на устаревшем домене kacst.edu.sa, не подтверждён
-• Член IAF; не университет — партнёрство через агентство/институт</t>
-        </is>
-      </c>
-      <c r="AH3" s="4" t="inlineStr">
+• Член IAF; не университет — партнёрство через агентство/институт
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI3" s="4" t="inlineStr">
         <is>
           <t>• Https://saudipedia.com/en/list-of-the-kingdom%E2%80%99s-satellites
 • Https://en.wikipedia.org/wiki/King_Abdulaziz_City_for_Science_and_Technology
@@ -1228,12 +1257,12 @@
 • Https://www.iafastro.org/membership/all-members/king-abdulaziz-city-for-science-and-technology-kacst.html</t>
         </is>
       </c>
-      <c r="AI3" s="4" t="inlineStr">
+      <c r="AJ3" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1342,55 +1371,65 @@
           <t>THE2027: 451–500</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>SARI-1 (Ufuq) (2025)</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr"/>
       <c r="Y4" s="4" t="inlineStr"/>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr"/>
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>Student team 'Ufuq' (SARI competition)</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AB4" s="4" t="inlineStr">
         <is>
           <t>Saudi Space Agency (SARI student satellite competition)</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="n">
+      <c r="AC4" s="4" t="inlineStr"/>
+      <c r="AD4" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="AD4" s="5" t="inlineStr">
+      <c r="AE4" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>• Ректор назначен королевским указом в октябре 2020 г.; актуальность на 2026 г. подтверждена только CV на официальном сайте (дата обновления не видна)
 • SARI-1 (Ufuq, PocketQube 1p) — победитель конкурса SARI Саудовского космического агентства; запуск 28.11.2025 (Transporter-15, через Alba Orbital), статус на орбите неизвестен
 • E-mail на сайте показаны картинками: rect@uqu.edu.sa (офис ректора), icu@uqu.edu.sa (Unit of International Cooperation)
-• Имя текущего руководителя подразделения международного сотрудничества не подтверждено</t>
-        </is>
-      </c>
-      <c r="AH4" s="4" t="inlineStr">
+• Имя текущего руководителя подразделения международного сотрудничества не подтверждено
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI4" s="4" t="inlineStr">
         <is>
           <t>• Https://uqu.edu.sa/en/rect
 • Https://uqu.edu.sa/en/icu/App/Contact
@@ -1398,15 +1437,18 @@
 • Https://uqu.edu.sa/en/rect/92736
 • Https://spa.gov.sa/en/N2455914
 • Https://www.nanosats.eu/sat/sari-1
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI4" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ4" s="4" t="inlineStr"/>
+      <c r="AK4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1497,73 +1539,93 @@
           <t>President &amp; Chief Academic Officer</t>
         </is>
       </c>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="n">
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W5" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>KAUSTSat (Lemur-2 ONREFLECTION, 6U, with Spire Global) (2023)</t>
         </is>
       </c>
-      <c r="X5" s="4" t="inlineStr"/>
       <c r="Y5" s="4" t="inlineStr"/>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr"/>
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>Climate and Livability Initiative / Hydrology, Agriculture and Land Observation group (Prof. Matthew McCabe) — KAUSTSat mission</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr">
+      <c r="AB5" s="4" t="inlineStr">
         <is>
           <t>Spire Global (KAUSTSat platform, launch on SpaceX Transporter-7)</t>
         </is>
       </c>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="n">
+      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AD5" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AD5" s="5" t="inlineStr">
+      <c r="AE5" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr">
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG5" s="4" t="inlineStr">
+      <c r="AH5" s="4" t="inlineStr">
         <is>
           <t>• Общий e-mail не опубликован; global.pr@kaust.edu.sa — ящик медиа/PR (Global PR and in-Kingdom inquiries), используется как единственный неадмиссионный адрес
 • Отдел партнёрств (Partnerships Office, &gt;40 международных соглашений) упомянут на сайте, но e-mail и руководитель не опубликованы
 • THE2027: статус Reporter (не ранжирован); в QS2027 (топ-500) не найден — KAUST как магистерско-докторский вуз в QS не участвует
 • KAUSTSat построен на платформе Spire Global (подписочная модель), полезная нагрузка — гиперспектральная камера KAUST; работал ~14 месяцев, сошёл с орбиты
-• Телефон на официальной странице контактов не опубликован</t>
-        </is>
-      </c>
-      <c r="AH5" s="4" t="inlineStr">
+• Телефон на официальной странице контактов не опубликован
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI5" s="4" t="inlineStr">
         <is>
           <t>• Https://www.kaust.edu.sa/en/about/administration/president
 • Https://www.kaust.edu.sa/en/contact
 • Https://www.kaust.edu.sa/en/news/kaust-satellite-to-deliver-earth-observation-data
 • Https://admissions.kaust.edu.sa/info-and-contact/partnerships
 • Https://agupubs.onlinelibrary.wiley.com/doi/10.1029/2025EA004729
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI5" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1672,62 +1734,72 @@
           <t>THE2027: =176</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="X6" s="4" t="inlineStr"/>
+      <c r="Y6" s="4" t="inlineStr">
         <is>
           <t>• Opti-K 6U CubeSat with optical transmitter (with Astrolight)
 • Dual 8U Earth-observation satellite mission (GomSpace MoU, Sep 2026)
 • High-altitude balloon CubeSat platform</t>
         </is>
       </c>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>Student-built ground station (IRC-ASE); Optical Ground Station with 360° tracking (Opti-K, in development)</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>Interdisciplinary Research Center for Aviation &amp; Space Exploration (IRC-ASE), Director Dr. Ayman Abdallah, irc-ase@kfupm.edu.sa</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr">
+      <c r="AB6" s="4" t="inlineStr">
         <is>
           <t>• GomSpace (MoU, 2026)
 • Astrolight (Opti-K)</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="n">
+      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AD6" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AD6" s="6" t="inlineStr">
+      <c r="AE6" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AH6" s="4" t="inlineStr">
         <is>
           <t>• Спутников на орбите нет; активная космическая программа через IRC-ASE (создан в 2022 г.)
 • Сентябрь 2026: MoU с GomSpace о двойной 8U миссии ДЗЗ — приоритетный кандидат для партнёрства по CubeSat
 • Global Engagement (создан в 2024 г.) возглавляет советник ректора; учёная степень адресата на сайте не указана — в обращении используется полное имя
-• Для партнёрств по космосу дополнительно: irc-ase@kfupm.edu.sa, +966 13 860 5400</t>
-        </is>
-      </c>
-      <c r="AH6" s="4" t="inlineStr">
+• Для партнёрств по космосу дополнительно: irc-ase@kfupm.edu.sa, +966 13 860 5400
+• Рейтинги: QS: в таблице как «KFUPM»; THE: в таблице как «KFUPM»; Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI6" s="4" t="inlineStr">
         <is>
           <t>• Https://www.kfupm.edu.sa/about-us/our-story/leadership
 • Https://www.kfupm.edu.sa/about-us/connect/contact-us
@@ -1735,15 +1807,18 @@
 • Https://global.kfupm.edu.sa/about-us/advisors-message/
 • Https://ri.kfupm.edu.sa/irc-ase/contact-us
 • Https://ri.kfupm.edu.sa/research-highlights/pioneering-the-future-of-space-communication
-• Https://gomspace.com/gomspace-and-kfupm-sign-mou-to-explore-strategic-cooperation-in-space-technology/</t>
-        </is>
-      </c>
-      <c r="AI6" s="4" t="inlineStr">
+• Https://gomspace.com/gomspace-and-kfupm-sign-mou-to-explore-strategic-cooperation-in-space-technology/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ6" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1839,7 +1914,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 488</t>
+          <t>QS2027: =488</t>
         </is>
       </c>
       <c r="T7" s="4" t="inlineStr">
@@ -1847,63 +1922,75 @@
           <t>THE2027: 376–400</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="n">
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W7" s="4" t="inlineStr">
+      <c r="X7" s="4" t="inlineStr">
         <is>
           <t>Rawdat Scoop (SARI-2, PocketQube 1p) (2025)</t>
         </is>
       </c>
-      <c r="X7" s="4" t="inlineStr"/>
       <c r="Y7" s="4" t="inlineStr"/>
       <c r="Z7" s="4" t="inlineStr"/>
-      <c r="AA7" s="4" t="inlineStr">
+      <c r="AA7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr">
         <is>
           <t>Saudi Space Agency (SARI student small-satellite competition — PSU design selected for flight, launched Nov 2025)</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="n">
+      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AD7" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AD7" s="5" t="inlineStr">
+      <c r="AE7" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr">
+      <c r="AF7" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG7" s="4" t="inlineStr">
+      <c r="AH7" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт psu.edu.sa недоступен (HTTP 503 / ошибка TLS) — контакты взяты из справочника WIPO TISC, ФИО ректора — из Википедии; рекомендуется перепроверить
 • Спутник Rawdat Scoop (SARI-2) спроектирован студентами PSU в рамках конкурса SARI Саудовского космического агентства и запущен в ноябре 2025; статус на орбите неизвестен
-• E-mail международного отдела не найден</t>
-        </is>
-      </c>
-      <c r="AH7" s="4" t="inlineStr">
+• E-mail международного отдела не найден
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI7" s="4" t="inlineStr">
         <is>
           <t>• Https://en.wikipedia.org/wiki/Prince_Sultan_University
 • Https://www.wipo.int/tisc/en/search/details.jsp?id=12475
 • Https://www.arabnews.com/node/2624459/saudi-arabia
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI7" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1983,20 +2070,37 @@
           <t>Chief Executive Officer (Acting CEO per April 2026 SPA statement)</t>
         </is>
       </c>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="n">
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W8" s="4" t="inlineStr">
+      <c r="X8" s="4" t="inlineStr">
         <is>
           <t>Shams (Space Weather CubeSat-1, SWC-1, 12U) (2026)</t>
         </is>
       </c>
-      <c r="X8" s="4" t="inlineStr"/>
       <c r="Y8" s="4" t="inlineStr"/>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="Z8" s="4" t="inlineStr"/>
+      <c r="AA8" s="4" t="inlineStr">
         <is>
           <t>• Saudi Human Spaceflight (HSF) Program
 • Shams space-weather mission
@@ -2005,7 +2109,7 @@
 • Space Academy</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="inlineStr">
+      <c r="AB8" s="4" t="inlineStr">
         <is>
           <t>• NASA (Artemis II — Shams launched as SLS secondary payload, April 2026
 • US–Saudi civil aeronautics and space cooperation agreement)
@@ -2013,31 +2117,32 @@
 • Umm Al-Qura University and Prince Sultan University (SARI satellites, 2025)</t>
         </is>
       </c>
-      <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="n">
+      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AD8" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AD8" s="5" t="inlineStr">
+      <c r="AE8" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE8" s="4" t="inlineStr"/>
-      <c r="AF8" s="4" t="inlineStr">
+      <c r="AF8" s="4" t="inlineStr"/>
+      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG8" s="4" t="inlineStr">
+      <c r="AH8" s="4" t="inlineStr">
         <is>
           <t>• Это государственное агентство, а не университет (включено намеренно)
 • Сайт ssa.gov.sa рендерится через JS — контактный e-mail не удалось прочитать; по поисковой выдаче общий адрес Info@ssa.gov.sa (в справочнике Eye of Riyadh — устаревший Info@ssc.gov.sa) — НЕ подтверждено, проверить перед отправкой
 • Адрес и телефон — из карточки члена IAF
 • Д-р Мохаммед ат-Тамими в апреле 2026 назван исполняющим обязанности CEO; с мая 2025 он также губернатор Национального агентства по ЧС
-• Спутник Shams (SWC-1) разработан в КСА, выведен 01.04.2026 в рамках Artemis II на высокоэллиптическую орбиту ~500–70 000 км (не VLEO)</t>
-        </is>
-      </c>
-      <c r="AH8" s="4" t="inlineStr">
+• Спутник Shams (SWC-1) разработан в КСА, выведен 01.04.2026 в рамках Artemis II на высокоэллиптическую орбиту ~500–70 000 км (не VLEO)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI8" s="4" t="inlineStr">
         <is>
           <t>• Https://ssa.gov.sa/en/about-ssa/
 • Https://www.iafastro.org/membership/all-members/saudi-space-commission-ssc.html
@@ -2048,15 +2153,15 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI8" s="4" t="inlineStr">
+      <c r="AJ8" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ8"/>
+  <autoFilter ref="A1:AK8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2067,7 +2172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ49"/>
+  <dimension ref="A1:AK49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2091,21 +2196,22 @@
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="45" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="45" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="40" customWidth="1" min="26" max="26"/>
-    <col width="45" customWidth="1" min="27" max="27"/>
-    <col width="22" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="9" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="55" customWidth="1" min="33" max="33"/>
-    <col width="60" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="24" customWidth="1" min="36" max="36"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="40" customWidth="1" min="27" max="27"/>
+    <col width="45" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="55" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="24" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2216,75 +2322,80 @@
       </c>
       <c r="V1" s="3" t="inlineStr">
         <is>
+          <t>Рейтинг Webometrics (мир)</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
           <t>Запущено КА (спутников)</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Названия запущенных КА (год)</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>КА в разработке</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>Наземная станция</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>Космические подразделения</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>Партнёрства в космической сфере</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>Санкционные / ограничительные списки (США)</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AD1" s="3" t="inlineStr">
         <is>
           <t>Космический индекс (0–100)</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AE1" s="3" t="inlineStr">
         <is>
           <t>Волна рассылки</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AF1" s="3" t="inlineStr">
         <is>
           <t>Проверка домена e-mail (MX)</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AG1" s="3" t="inlineStr">
         <is>
           <t>Достоверность</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>Дата проверки</t>
         </is>
       </c>
-      <c r="AJ1" s="3" t="inlineStr">
+      <c r="AK1" s="3" t="inlineStr">
         <is>
           <t>Секретарь парткома (справочно, Китай)</t>
         </is>
@@ -2397,60 +2508,70 @@
           <t>THE2027: 216</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
+      <c r="U2" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>KSU CubeSat (2021)</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>• KSU CubeSat-2 (second satellite approved in 2021
 • Current status unverified)</t>
         </is>
       </c>
-      <c r="Y2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>Satellite ground station at the College of Engineering (built during KSU CubeSat project)</t>
         </is>
       </c>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>College of Engineering – KSU CubeSat project team</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr"/>
       <c r="AB2" s="4" t="inlineStr"/>
-      <c r="AC2" s="4" t="n">
+      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AD2" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="AD2" s="5" t="inlineStr">
+      <c r="AE2" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE2" s="4" t="inlineStr">
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG2" s="4" t="inlineStr">
+      <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>• Ректор — исполняющий обязанности (Acting President) с июня 2025 г.; упоминается в новостях KSU от 30.09.2026
 • KSU CubeSat (1U) запущен 22.03.2021 на «Союз-2» с Байконура — первый спутник саудовского университета; сошёл с орбиты
 • Почта po@ksu.edu.sa — офис ректора; icstd@ksu.edu.sa — Global Engagement Office (مكتب الشراكات العالمية), тел. +966 11 469 7398
-• Дата последнего обновления страницы с руководителем GEO не указана</t>
-        </is>
-      </c>
-      <c r="AH2" s="4" t="inlineStr">
+• Дата последнего обновления страницы с руководителем GEO не указана
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI2" s="4" t="inlineStr">
         <is>
           <t>• Https://ksu.edu.sa/en/contact-us
 • Https://ksu.edu.sa/en
@@ -2460,15 +2581,18 @@
 • Https://chairs.ksu.edu.sa/en/node/113
 • Https://www.arabnews.com/node/1836141/saudi-arabia
 • Https://saudigazette.com.sa/article/604671
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI2" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ2" s="4" t="inlineStr"/>
+      <c r="AK2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -2562,13 +2686,22 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="n">
+      <c r="V3" s="4" t="inlineStr"/>
+      <c r="W3" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>• SaudiSat-1A (2000)
 • SaudiSat-1B (2000)
@@ -2589,50 +2722,51 @@
 • Shaheen Sat (2021)</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr"/>
       <c r="Y3" s="4" t="inlineStr"/>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="Z3" s="4" t="inlineStr"/>
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>• Space Research Institute (per Wikipedia
 • Current structure unverified)
 • National Satellite Technology Program</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr">
+      <c r="AB3" s="4" t="inlineStr">
         <is>
           <t>• Saudi Space Agency
 • CNSA (Chang'e-4 payload, 2018)</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="n">
+      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AD3" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="AD3" s="5" t="inlineStr">
+      <c r="AE3" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE3" s="4" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>• Сайт kacst.gov.sa недоступен (503/таймаут); адрес, телефон и media@kacst.gov.sa взяты из поисковой выдачи официальной страницы контактов
 • Президент в ранге министра; подтверждён в новости SPA от 11.02.2026
 • 17 спутников за 2000–2021 гг. (Saudipedia); SGS-1 (2019) — геостационарный спутник связи, изготовлен совместно с Lockheed Martin
 • Международный e-mail int_coop@kacst.edu.sa (страница IAF) — на устаревшем домене kacst.edu.sa, не подтверждён
-• Член IAF; не университет — партнёрство через агентство/институт</t>
-        </is>
-      </c>
-      <c r="AH3" s="4" t="inlineStr">
+• Член IAF; не университет — партнёрство через агентство/институт
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI3" s="4" t="inlineStr">
         <is>
           <t>• Https://saudipedia.com/en/list-of-the-kingdom%E2%80%99s-satellites
 • Https://en.wikipedia.org/wiki/King_Abdulaziz_City_for_Science_and_Technology
@@ -2643,12 +2777,12 @@
 • Https://www.iafastro.org/membership/all-members/king-abdulaziz-city-for-science-and-technology-kacst.html</t>
         </is>
       </c>
-      <c r="AI3" s="4" t="inlineStr">
+      <c r="AJ3" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -2757,55 +2891,65 @@
           <t>THE2027: 451–500</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>SARI-1 (Ufuq) (2025)</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr"/>
       <c r="Y4" s="4" t="inlineStr"/>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr"/>
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>Student team 'Ufuq' (SARI competition)</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AB4" s="4" t="inlineStr">
         <is>
           <t>Saudi Space Agency (SARI student satellite competition)</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="n">
+      <c r="AC4" s="4" t="inlineStr"/>
+      <c r="AD4" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="AD4" s="5" t="inlineStr">
+      <c r="AE4" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>• Ректор назначен королевским указом в октябре 2020 г.; актуальность на 2026 г. подтверждена только CV на официальном сайте (дата обновления не видна)
 • SARI-1 (Ufuq, PocketQube 1p) — победитель конкурса SARI Саудовского космического агентства; запуск 28.11.2025 (Transporter-15, через Alba Orbital), статус на орбите неизвестен
 • E-mail на сайте показаны картинками: rect@uqu.edu.sa (офис ректора), icu@uqu.edu.sa (Unit of International Cooperation)
-• Имя текущего руководителя подразделения международного сотрудничества не подтверждено</t>
-        </is>
-      </c>
-      <c r="AH4" s="4" t="inlineStr">
+• Имя текущего руководителя подразделения международного сотрудничества не подтверждено
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI4" s="4" t="inlineStr">
         <is>
           <t>• Https://uqu.edu.sa/en/rect
 • Https://uqu.edu.sa/en/icu/App/Contact
@@ -2813,15 +2957,18 @@
 • Https://uqu.edu.sa/en/rect/92736
 • Https://spa.gov.sa/en/N2455914
 • Https://www.nanosats.eu/sat/sari-1
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI4" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ4" s="4" t="inlineStr"/>
+      <c r="AK4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -2912,73 +3059,93 @@
           <t>President &amp; Chief Academic Officer</t>
         </is>
       </c>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="n">
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W5" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>KAUSTSat (Lemur-2 ONREFLECTION, 6U, with Spire Global) (2023)</t>
         </is>
       </c>
-      <c r="X5" s="4" t="inlineStr"/>
       <c r="Y5" s="4" t="inlineStr"/>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr"/>
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>Climate and Livability Initiative / Hydrology, Agriculture and Land Observation group (Prof. Matthew McCabe) — KAUSTSat mission</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr">
+      <c r="AB5" s="4" t="inlineStr">
         <is>
           <t>Spire Global (KAUSTSat platform, launch on SpaceX Transporter-7)</t>
         </is>
       </c>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="n">
+      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AD5" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AD5" s="5" t="inlineStr">
+      <c r="AE5" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr">
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG5" s="4" t="inlineStr">
+      <c r="AH5" s="4" t="inlineStr">
         <is>
           <t>• Общий e-mail не опубликован; global.pr@kaust.edu.sa — ящик медиа/PR (Global PR and in-Kingdom inquiries), используется как единственный неадмиссионный адрес
 • Отдел партнёрств (Partnerships Office, &gt;40 международных соглашений) упомянут на сайте, но e-mail и руководитель не опубликованы
 • THE2027: статус Reporter (не ранжирован); в QS2027 (топ-500) не найден — KAUST как магистерско-докторский вуз в QS не участвует
 • KAUSTSat построен на платформе Spire Global (подписочная модель), полезная нагрузка — гиперспектральная камера KAUST; работал ~14 месяцев, сошёл с орбиты
-• Телефон на официальной странице контактов не опубликован</t>
-        </is>
-      </c>
-      <c r="AH5" s="4" t="inlineStr">
+• Телефон на официальной странице контактов не опубликован
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI5" s="4" t="inlineStr">
         <is>
           <t>• Https://www.kaust.edu.sa/en/about/administration/president
 • Https://www.kaust.edu.sa/en/contact
 • Https://www.kaust.edu.sa/en/news/kaust-satellite-to-deliver-earth-observation-data
 • Https://admissions.kaust.edu.sa/info-and-contact/partnerships
 • Https://agupubs.onlinelibrary.wiley.com/doi/10.1029/2025EA004729
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI5" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -3087,62 +3254,72 @@
           <t>THE2027: =176</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="X6" s="4" t="inlineStr"/>
+      <c r="Y6" s="4" t="inlineStr">
         <is>
           <t>• Opti-K 6U CubeSat with optical transmitter (with Astrolight)
 • Dual 8U Earth-observation satellite mission (GomSpace MoU, Sep 2026)
 • High-altitude balloon CubeSat platform</t>
         </is>
       </c>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>Student-built ground station (IRC-ASE); Optical Ground Station with 360° tracking (Opti-K, in development)</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>Interdisciplinary Research Center for Aviation &amp; Space Exploration (IRC-ASE), Director Dr. Ayman Abdallah, irc-ase@kfupm.edu.sa</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr">
+      <c r="AB6" s="4" t="inlineStr">
         <is>
           <t>• GomSpace (MoU, 2026)
 • Astrolight (Opti-K)</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="n">
+      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AD6" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AD6" s="6" t="inlineStr">
+      <c r="AE6" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AH6" s="4" t="inlineStr">
         <is>
           <t>• Спутников на орбите нет; активная космическая программа через IRC-ASE (создан в 2022 г.)
 • Сентябрь 2026: MoU с GomSpace о двойной 8U миссии ДЗЗ — приоритетный кандидат для партнёрства по CubeSat
 • Global Engagement (создан в 2024 г.) возглавляет советник ректора; учёная степень адресата на сайте не указана — в обращении используется полное имя
-• Для партнёрств по космосу дополнительно: irc-ase@kfupm.edu.sa, +966 13 860 5400</t>
-        </is>
-      </c>
-      <c r="AH6" s="4" t="inlineStr">
+• Для партнёрств по космосу дополнительно: irc-ase@kfupm.edu.sa, +966 13 860 5400
+• Рейтинги: QS: в таблице как «KFUPM»; THE: в таблице как «KFUPM»; Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI6" s="4" t="inlineStr">
         <is>
           <t>• Https://www.kfupm.edu.sa/about-us/our-story/leadership
 • Https://www.kfupm.edu.sa/about-us/connect/contact-us
@@ -3150,15 +3327,18 @@
 • Https://global.kfupm.edu.sa/about-us/advisors-message/
 • Https://ri.kfupm.edu.sa/irc-ase/contact-us
 • Https://ri.kfupm.edu.sa/research-highlights/pioneering-the-future-of-space-communication
-• Https://gomspace.com/gomspace-and-kfupm-sign-mou-to-explore-strategic-cooperation-in-space-technology/</t>
-        </is>
-      </c>
-      <c r="AI6" s="4" t="inlineStr">
+• Https://gomspace.com/gomspace-and-kfupm-sign-mou-to-explore-strategic-cooperation-in-space-technology/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ6" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -3254,7 +3434,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 488</t>
+          <t>QS2027: =488</t>
         </is>
       </c>
       <c r="T7" s="4" t="inlineStr">
@@ -3262,63 +3442,75 @@
           <t>THE2027: 376–400</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="n">
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W7" s="4" t="inlineStr">
+      <c r="X7" s="4" t="inlineStr">
         <is>
           <t>Rawdat Scoop (SARI-2, PocketQube 1p) (2025)</t>
         </is>
       </c>
-      <c r="X7" s="4" t="inlineStr"/>
       <c r="Y7" s="4" t="inlineStr"/>
       <c r="Z7" s="4" t="inlineStr"/>
-      <c r="AA7" s="4" t="inlineStr">
+      <c r="AA7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr">
         <is>
           <t>Saudi Space Agency (SARI student small-satellite competition — PSU design selected for flight, launched Nov 2025)</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="n">
+      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AD7" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AD7" s="5" t="inlineStr">
+      <c r="AE7" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr">
+      <c r="AF7" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG7" s="4" t="inlineStr">
+      <c r="AH7" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт psu.edu.sa недоступен (HTTP 503 / ошибка TLS) — контакты взяты из справочника WIPO TISC, ФИО ректора — из Википедии; рекомендуется перепроверить
 • Спутник Rawdat Scoop (SARI-2) спроектирован студентами PSU в рамках конкурса SARI Саудовского космического агентства и запущен в ноябре 2025; статус на орбите неизвестен
-• E-mail международного отдела не найден</t>
-        </is>
-      </c>
-      <c r="AH7" s="4" t="inlineStr">
+• E-mail международного отдела не найден
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI7" s="4" t="inlineStr">
         <is>
           <t>• Https://en.wikipedia.org/wiki/Prince_Sultan_University
 • Https://www.wipo.int/tisc/en/search/details.jsp?id=12475
 • Https://www.arabnews.com/node/2624459/saudi-arabia
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI7" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -3398,20 +3590,37 @@
           <t>Chief Executive Officer (Acting CEO per April 2026 SPA statement)</t>
         </is>
       </c>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="n">
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W8" s="4" t="inlineStr">
+      <c r="X8" s="4" t="inlineStr">
         <is>
           <t>Shams (Space Weather CubeSat-1, SWC-1, 12U) (2026)</t>
         </is>
       </c>
-      <c r="X8" s="4" t="inlineStr"/>
       <c r="Y8" s="4" t="inlineStr"/>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="Z8" s="4" t="inlineStr"/>
+      <c r="AA8" s="4" t="inlineStr">
         <is>
           <t>• Saudi Human Spaceflight (HSF) Program
 • Shams space-weather mission
@@ -3420,7 +3629,7 @@
 • Space Academy</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="inlineStr">
+      <c r="AB8" s="4" t="inlineStr">
         <is>
           <t>• NASA (Artemis II — Shams launched as SLS secondary payload, April 2026
 • US–Saudi civil aeronautics and space cooperation agreement)
@@ -3428,31 +3637,32 @@
 • Umm Al-Qura University and Prince Sultan University (SARI satellites, 2025)</t>
         </is>
       </c>
-      <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="n">
+      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AD8" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AD8" s="5" t="inlineStr">
+      <c r="AE8" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE8" s="4" t="inlineStr"/>
-      <c r="AF8" s="4" t="inlineStr">
+      <c r="AF8" s="4" t="inlineStr"/>
+      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG8" s="4" t="inlineStr">
+      <c r="AH8" s="4" t="inlineStr">
         <is>
           <t>• Это государственное агентство, а не университет (включено намеренно)
 • Сайт ssa.gov.sa рендерится через JS — контактный e-mail не удалось прочитать; по поисковой выдаче общий адрес Info@ssa.gov.sa (в справочнике Eye of Riyadh — устаревший Info@ssc.gov.sa) — НЕ подтверждено, проверить перед отправкой
 • Адрес и телефон — из карточки члена IAF
 • Д-р Мохаммед ат-Тамими в апреле 2026 назван исполняющим обязанности CEO; с мая 2025 он также губернатор Национального агентства по ЧС
-• Спутник Shams (SWC-1) разработан в КСА, выведен 01.04.2026 в рамках Artemis II на высокоэллиптическую орбиту ~500–70 000 км (не VLEO)</t>
-        </is>
-      </c>
-      <c r="AH8" s="4" t="inlineStr">
+• Спутник Shams (SWC-1) разработан в КСА, выведен 01.04.2026 в рамках Artemis II на высокоэллиптическую орбиту ~500–70 000 км (не VLEO)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI8" s="4" t="inlineStr">
         <is>
           <t>• Https://ssa.gov.sa/en/about-ssa/
 • Https://www.iafastro.org/membership/all-members/saudi-space-commission-ssc.html
@@ -3463,12 +3673,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI8" s="4" t="inlineStr">
+      <c r="AJ8" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -3573,66 +3783,78 @@
           <t>THE2027: 401–450</t>
         </is>
       </c>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="n">
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr"/>
       <c r="Y9" s="4" t="inlineStr"/>
-      <c r="Z9" s="4" t="inlineStr">
+      <c r="Z9" s="4" t="inlineStr"/>
+      <c r="AA9" s="4" t="inlineStr">
         <is>
           <t>Space Research Center (listed among PMU research centers)</t>
         </is>
       </c>
-      <c r="AA9" s="4" t="inlineStr">
+      <c r="AB9" s="4" t="inlineStr">
         <is>
           <t>• ICESCO (strategic partnership incl. space sciences
 • Proposed CanSat training workshop, Sept 2025)</t>
         </is>
       </c>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="n">
+      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AD9" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="AD9" s="7" t="inlineStr">
+      <c r="AE9" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AE9" s="4" t="inlineStr">
+      <c r="AF9" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF9" s="4" t="inlineStr">
+      <c r="AG9" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG9" s="4" t="inlineStr">
+      <c r="AH9" s="4" t="inlineStr">
         <is>
           <t>• E-mail международного отдела (Department of International Affairs) не опубликован; использован адрес офиса президента President@pmu.edu.sa (также есть Info@pmu.edu.sa)
 • На старой оргсхеме директором International Affairs указана Mrs. Rania Sinno, но в текущем справочнике она числится директором Institutional Planning and Research — не использовано
 • В университете есть Space Research Center; спутников в nanosats.csv нет; в 2025 г. подписано партнёрство с ICESCO в т.ч. по космическим наукам (CanSat)
-• Рейтинг QS2027: 421 по одному источнику, 422 по другому</t>
-        </is>
-      </c>
-      <c r="AH9" s="4" t="inlineStr">
+• Рейтинг QS2027: 421 по одному источнику, 422 по другому
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI9" s="4" t="inlineStr">
         <is>
           <t>• Https://www.pmu.edu.sa/About/Contact_Us.aspx
 • Https://www.pmu.edu.sa/global-engagement/
 • Https://www.pmu.edu.sa/global-engagement/about/organizational-chart.aspx
 • Https://icesco.org/en/2025/09/10/strategic-partnership-between-icesco-and-prince-mohammad-bin-fahd-university-in-saudi-arabia/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI9" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AK9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -3740,62 +3962,75 @@
           <t>THE2027: 401–450</t>
         </is>
       </c>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="n">
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr"/>
       <c r="Y10" s="4" t="inlineStr"/>
-      <c r="Z10" s="4" t="inlineStr">
+      <c r="Z10" s="4" t="inlineStr"/>
+      <c r="AA10" s="4" t="inlineStr">
         <is>
           <t>Astronomy programme (Faculty of Science) — KAU offers astronomy, meteorology and marine science courses</t>
         </is>
       </c>
-      <c r="AA10" s="4" t="inlineStr"/>
       <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="n">
+      <c r="AC10" s="4" t="inlineStr"/>
+      <c r="AD10" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="AD10" s="8" t="inlineStr">
+      <c r="AE10" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE10" s="4" t="inlineStr">
+      <c r="AF10" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF10" s="4" t="inlineStr">
+      <c r="AG10" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG10" s="4" t="inlineStr">
+      <c r="AH10" s="4" t="inlineStr">
         <is>
           <t>• Ректор (с февраля 2024) подтверждён по Википедии; на официальном сайте страница ректора не найдена (сайт на JS)
 • Ic@kau.edu.sa — Управление глобального и внешнего взаимодействия (Department of International Cooperation Agreements, подчиняется ректору); руководитель не указан
 • Бесплатный номер: 800 116 9528; основной +966 12 640 0000 (WIPO TISC, сайт КАУ)
-• Спутников, построенных КАУ, не найдено</t>
-        </is>
-      </c>
-      <c r="AH10" s="4" t="inlineStr">
+• Спутников, построенных КАУ, не найдено
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI10" s="4" t="inlineStr">
         <is>
           <t>• Https://kau.edu.sa/en/page/contact-us
 • Https://kau.edu.sa/en/page/global-and-external-engagement
 • Https://kau.edu.sa/en/page/important-links
 • Https://www.wipo.int/tisc/en/search/details.jsp?id=11353
 • Https://en.wikipedia.org/wiki/Tareef_bin_Yousuf_Alaama
-• Https://en.wikipedia.org/wiki/King_Abdulaziz_University</t>
-        </is>
-      </c>
-      <c r="AI10" s="4" t="inlineStr">
+• Https://en.wikipedia.org/wiki/King_Abdulaziz_University
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ10" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ10" s="4" t="inlineStr"/>
+      <c r="AK10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -3900,54 +4135,56 @@
         </is>
       </c>
       <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="n">
+      <c r="V11" s="4" t="inlineStr"/>
+      <c r="W11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W11" s="4" t="inlineStr"/>
       <c r="X11" s="4" t="inlineStr"/>
       <c r="Y11" s="4" t="inlineStr"/>
       <c r="Z11" s="4" t="inlineStr"/>
       <c r="AA11" s="4" t="inlineStr"/>
       <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="n">
+      <c r="AC11" s="4" t="inlineStr"/>
+      <c r="AD11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD11" s="8" t="inlineStr">
+      <c r="AE11" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE11" s="4" t="inlineStr">
+      <c r="AF11" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF11" s="4" t="inlineStr">
+      <c r="AG11" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG11" s="4" t="inlineStr">
+      <c r="AH11" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт iau.edu.sa недоступен из-за геоблокировки (HTTP 503 / сброс соединения); контакты — из справочника WIPO TISC
 • Ректор проф. Фахад аль-Харби назначен королевским указом (новость IAU, июль 2025); в Википедии также упоминается прежний ректор Абдулла ар-Рубаиш — использовать аль-Харби
 • Cm.dir@iau.edu.sa — Управление коммуникаций центральной администрации; по поисковой выдаче также info@iau.edu.sa и тел. +966 13 333 0000 (не подтверждено)
-• E-mail международного отдела не найден; космических проектов не найдено</t>
-        </is>
-      </c>
-      <c r="AH11" s="4" t="inlineStr">
+• E-mail международного отдела не найден; космических проектов не найдено
+• Ручная проверка: Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI11" s="4" t="inlineStr">
         <is>
           <t>• Https://www.wipo.int/tisc/en/search/details.jsp?id=11748
 • Https://en.wikipedia.org/wiki/Imam_Abdulrahman_Bin_Faisal_University
 • Https://www.iau.edu.sa/en/news/professor-dr-fahd-al-harbi-president-of-imam-abdulrahman-bin-faisal-university</t>
         </is>
       </c>
-      <c r="AI11" s="4" t="inlineStr">
+      <c r="AJ11" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AK11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -4056,43 +4293,53 @@
           <t>THE2027: 301–325</t>
         </is>
       </c>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="n">
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W12" s="4" t="inlineStr"/>
       <c r="X12" s="4" t="inlineStr"/>
       <c r="Y12" s="4" t="inlineStr"/>
       <c r="Z12" s="4" t="inlineStr"/>
       <c r="AA12" s="4" t="inlineStr"/>
       <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="n">
+      <c r="AC12" s="4" t="inlineStr"/>
+      <c r="AD12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD12" s="8" t="inlineStr">
+      <c r="AE12" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE12" s="4" t="inlineStr">
+      <c r="AF12" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF12" s="4" t="inlineStr">
+      <c r="AG12" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG12" s="4" t="inlineStr">
+      <c r="AH12" s="4" t="inlineStr">
         <is>
           <t>• Ректор занимает пост с июня 2016 г.; официальная страница (обновлена 2026) указывает «June 2016 – Present»
 • Спутников не найдено (nanosats.csv и один поиск)
 • Общий e-mail kkurector@kku.edu.sa — офис ректора; отдельного общего адреса отдела международного сотрудничества на сайте нет — указан личный e-mail руководителя отдела (msalshehri@kku.edu.sa)
-• QS2027 по таблице qianmu.org (вторичный источник)</t>
-        </is>
-      </c>
-      <c r="AH12" s="4" t="inlineStr">
+• QS2027 по таблице qianmu.org (вторичный источник)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI12" s="4" t="inlineStr">
         <is>
           <t>• Https://www.kku.edu.sa/en
 • Https://www.kku.edu.sa/en/portfolio/The-university-president
@@ -4100,15 +4347,18 @@
 • Https://www.kku.edu.sa/en/portfolio/local-and-international-cooperation
 • Https://www.kku.edu.sa/en/contact
 • Https://www.qianmu.org/2027QS世界大学排名
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI12" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ12" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ12" s="4" t="inlineStr"/>
+      <c r="AK12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -4205,7 +4455,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 677</t>
+          <t>QS2027: =677</t>
         </is>
       </c>
       <c r="T13" s="4" t="inlineStr">
@@ -4213,42 +4463,52 @@
           <t>THE2027: 401–450</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr"/>
-      <c r="V13" s="4" t="n">
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W13" s="4" t="inlineStr"/>
       <c r="X13" s="4" t="inlineStr"/>
       <c r="Y13" s="4" t="inlineStr"/>
       <c r="Z13" s="4" t="inlineStr"/>
       <c r="AA13" s="4" t="inlineStr"/>
       <c r="AB13" s="4" t="inlineStr"/>
-      <c r="AC13" s="4" t="n">
+      <c r="AC13" s="4" t="inlineStr"/>
+      <c r="AD13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD13" s="8" t="inlineStr">
+      <c r="AE13" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE13" s="4" t="inlineStr">
+      <c r="AF13" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF13" s="4" t="inlineStr">
+      <c r="AG13" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG13" s="4" t="inlineStr">
+      <c r="AH13" s="4" t="inlineStr">
         <is>
           <t>• Общий номер телефона на сайте не найден (только телефонный справочник/добавочные); добавочный директора отдела — 4460
 • Спутников не найдено (nanosats.csv и один поиск)
-• Отдел международного сотрудничества: DICCR@psau.edu.sa; директор — s.alabdulaziz@psau.edu.sa (страница обновлена 24.08.2026)</t>
-        </is>
-      </c>
-      <c r="AH13" s="4" t="inlineStr">
+• Отдел международного сотрудничества: DICCR@psau.edu.sa; директор — s.alabdulaziz@psau.edu.sa (страница обновлена 24.08.2026)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI13" s="4" t="inlineStr">
         <is>
           <t>• Https://www.psau.edu.sa/en
 • Https://www.psau.edu.sa/en/presidents-message
@@ -4256,15 +4516,18 @@
 • Https://psau.edu.sa/dicss/en/contact-directory
 • Https://psau.edu.sa/dicss/en/directors-message
 • Https://www.qianmu.org/2027QS世界大学排名
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI13" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ13" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ13" s="4" t="inlineStr"/>
+      <c r="AK13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -4364,57 +4627,70 @@
           <t>THE2027: 451–500</t>
         </is>
       </c>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="n">
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W14" s="4" t="inlineStr"/>
       <c r="X14" s="4" t="inlineStr"/>
       <c r="Y14" s="4" t="inlineStr"/>
       <c r="Z14" s="4" t="inlineStr"/>
       <c r="AA14" s="4" t="inlineStr"/>
       <c r="AB14" s="4" t="inlineStr"/>
-      <c r="AC14" s="4" t="n">
+      <c r="AC14" s="4" t="inlineStr"/>
+      <c r="AD14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD14" s="8" t="inlineStr">
+      <c r="AE14" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE14" s="4" t="inlineStr">
+      <c r="AF14" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF14" s="4" t="inlineStr">
+      <c r="AG14" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG14" s="4" t="inlineStr">
+      <c r="AH14" s="4" t="inlineStr">
         <is>
           <t>• Женский университет (крупнейший женский университет страны) — учитывать при приглашении
 • E-mail международного отдела не найден на сайте; используется общий info@pnu.edu.sa (также pnu-tawasul@pnu.edu.sa — канал обращений)
 • Почтовый адрес на сайте не опубликован в текстовом виде — не заполнен
-• Спутников в nanosats.csv и в быстрой проверке не найдено</t>
-        </is>
-      </c>
-      <c r="AH14" s="4" t="inlineStr">
+• Спутников в nanosats.csv и в быстрой проверке не найдено
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI14" s="4" t="inlineStr">
         <is>
           <t>• Https://www.pnu.edu.sa/en/Pages/ContactUsForm.aspx
 • Https://pnu.edu.sa/en/AboutUniversity/pages/home.aspx
 • Https://pnu.edu.sa/en/MediaCenter/News/Pages/NewsDetails.aspx?RequestID=399
 • Http://www.qianmu.org/2027QS世界大学排名
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI14" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ14" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ14" s="4" t="inlineStr"/>
+      <c r="AK14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -4508,61 +4784,76 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S15" s="4" t="inlineStr"/>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T15" s="4" t="inlineStr">
         <is>
           <t>THE2027: 701–800</t>
         </is>
       </c>
-      <c r="U15" s="4" t="inlineStr"/>
-      <c r="V15" s="4" t="n">
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W15" s="4" t="inlineStr"/>
       <c r="X15" s="4" t="inlineStr"/>
       <c r="Y15" s="4" t="inlineStr"/>
       <c r="Z15" s="4" t="inlineStr"/>
       <c r="AA15" s="4" t="inlineStr"/>
       <c r="AB15" s="4" t="inlineStr"/>
-      <c r="AC15" s="4" t="n">
+      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AD15" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD15" s="8" t="inlineStr">
+      <c r="AE15" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE15" s="4" t="inlineStr">
+      <c r="AF15" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF15" s="4" t="inlineStr">
+      <c r="AG15" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG15" s="4" t="inlineStr">
+      <c r="AH15" s="4" t="inlineStr">
         <is>
           <t>• Частный университет медицинского профиля — низкая релевантность для спутниковой программы
 • E-mail международного отдела не найден; общий info@um.edu.sa; единый номер 920011909
 • Страница президента не датирована — актуальность ФИО подтверждена только текущим сайтом
-• Спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH15" s="4" t="inlineStr">
+• Спутников не найдено
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI15" s="4" t="inlineStr">
         <is>
           <t>• Https://www.um.edu.sa/en
 • Https://www.um.edu.sa/en/%D9%83%D9%84%D9%85%D8%A9-%D9%85%D8%B9%D8%A7%D9%84%D9%8A-%D8%B1%D8%A6%D9%8A%D8%B3-%D8%A7%D9%84%D8%AC%D8%A7%D9%85%D8%B9%D8%A9-2/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI15" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ15" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ15" s="4" t="inlineStr"/>
+      <c r="AK15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -4671,57 +4962,69 @@
           <t>THE2027: 501–550</t>
         </is>
       </c>
-      <c r="U16" s="4" t="inlineStr"/>
-      <c r="V16" s="4" t="n">
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W16" s="4" t="inlineStr"/>
       <c r="X16" s="4" t="inlineStr"/>
       <c r="Y16" s="4" t="inlineStr"/>
       <c r="Z16" s="4" t="inlineStr"/>
       <c r="AA16" s="4" t="inlineStr"/>
       <c r="AB16" s="4" t="inlineStr"/>
-      <c r="AC16" s="4" t="n">
+      <c r="AC16" s="4" t="inlineStr"/>
+      <c r="AD16" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD16" s="8" t="inlineStr">
+      <c r="AE16" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE16" s="4" t="inlineStr">
+      <c r="AF16" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF16" s="4" t="inlineStr">
+      <c r="AG16" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG16" s="4" t="inlineStr">
+      <c r="AH16" s="4" t="inlineStr">
         <is>
           <t>• Частный некоммерческий университет (основан фондом короля Фейсала)
 • Космической программы и спутников не найдено (одна проверка)
 • Партнёрствами занимается Department of External Relations and Advancement (advancement@alfaisal.edu, +966 11 215 7985); курирует вице-президент Dr. Maha bint Mishari AlSaud; имя директора департамента на сайте не указано
-• Office of International Students &amp; Exchange (oise.alfaisal.edu) ориентирован на студентов</t>
-        </is>
-      </c>
-      <c r="AH16" s="4" t="inlineStr">
+• Office of International Students &amp; Exchange (oise.alfaisal.edu) ориентирован на студентов
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI16" s="4" t="inlineStr">
         <is>
           <t>• Https://www.alfaisal.edu
 • Https://www.alfaisal.edu/en/contact
 • Https://advancement.alfaisal.edu
 • Https://advancement.alfaisal.edu/contact
-• Https://oise.alfaisal.edu/</t>
-        </is>
-      </c>
-      <c r="AI16" s="4" t="inlineStr">
+• Https://oise.alfaisal.edu/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ16" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ16" s="4" t="inlineStr"/>
+      <c r="AK16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -4801,58 +5104,74 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S17" s="4" t="inlineStr"/>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: 901–950</t>
+        </is>
+      </c>
       <c r="T17" s="4" t="inlineStr">
         <is>
           <t>THE2027: 601–650</t>
         </is>
       </c>
-      <c r="U17" s="4" t="inlineStr"/>
-      <c r="V17" s="4" t="n">
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W17" s="4" t="inlineStr"/>
       <c r="X17" s="4" t="inlineStr"/>
       <c r="Y17" s="4" t="inlineStr"/>
       <c r="Z17" s="4" t="inlineStr"/>
       <c r="AA17" s="4" t="inlineStr"/>
       <c r="AB17" s="4" t="inlineStr"/>
-      <c r="AC17" s="4" t="n">
+      <c r="AC17" s="4" t="inlineStr"/>
+      <c r="AD17" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD17" s="8" t="inlineStr">
+      <c r="AE17" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE17" s="4" t="inlineStr"/>
-      <c r="AF17" s="4" t="inlineStr">
+      <c r="AF17" s="4" t="inlineStr"/>
+      <c r="AG17" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG17" s="4" t="inlineStr">
+      <c r="AH17" s="4" t="inlineStr">
         <is>
           <t>• Частный женский университет (учредитель — King Faisal Foundation)
 • Общий e-mail и e-mail международного отдела на сайте не опубликованы (есть только Effat.PACCE@effatuniversity.edu.sa — непрерывное образование); связь через форму Tawasul или единый номер 920003331
-• Спутников не найдено; студенты участвовали в космическом лагере в Нью-Йорке (2024)</t>
-        </is>
-      </c>
-      <c r="AH17" s="4" t="inlineStr">
+• Спутников не найдено; студенты участвовали в космическом лагере в Нью-Йорке (2024)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI17" s="4" t="inlineStr">
         <is>
           <t>• Https://www.effatuniversity.edu.sa/English/Pages/default.aspx
 • Https://www.effatuniversity.edu.sa/English/About/Contact-Us/Pages/default.aspx
 • Https://www.effatuniversity.edu.sa/English/About/Governance/President/Pages/default.aspx
 • Https://www.effatuniversity.edu.sa/English/About/Impact/Pages/contact-us.aspx
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI17" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ17" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ17" s="4" t="inlineStr"/>
+      <c r="AK17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -4957,60 +5276,73 @@
           <t>THE2027: 601–650</t>
         </is>
       </c>
-      <c r="U18" s="4" t="inlineStr"/>
-      <c r="V18" s="4" t="n">
+      <c r="U18" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+      <c r="W18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W18" s="4" t="inlineStr"/>
       <c r="X18" s="4" t="inlineStr"/>
       <c r="Y18" s="4" t="inlineStr"/>
       <c r="Z18" s="4" t="inlineStr"/>
       <c r="AA18" s="4" t="inlineStr"/>
       <c r="AB18" s="4" t="inlineStr"/>
-      <c r="AC18" s="4" t="n">
+      <c r="AC18" s="4" t="inlineStr"/>
+      <c r="AD18" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD18" s="8" t="inlineStr">
+      <c r="AE18" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE18" s="4" t="inlineStr">
+      <c r="AF18" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF18" s="4" t="inlineStr">
+      <c r="AG18" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG18" s="4" t="inlineStr">
+      <c r="AH18" s="4" t="inlineStr">
         <is>
           <t>• Президент подтверждён по новости SPA (июль 2026 г.); учёное звание в источнике не указано
 • Op@imamu.edu.sa — e-mail для записи на приём к президенту (офис президента); телефоны офиса: 011 259 8762, 011 258 5214
 • Сайт в основном на JavaScript, часть страниц (contact-us) блокируется WAF; почтовый адрес (P.O. Box) на открытых страницах не найден
 • Есть Генеральное управление международного сотрудничества и коммуникаций (الإدارة العامة للتعاون والتواصل الدولي), но e-mail и руководитель на странице не отображаются
 • Спутников не найдено; в поиске упоминается проект KN-Sat1 (ResearchGate), связь с IMSIU и запуск не подтверждены
-• Перепроверка: Повторный доступ к imamu.edu.sa блокируется WAF (страница «IMAMU Support», 04.10.2026) — обход не выполнялся; уровень повышен до medium на основании ранее подтверждённых данных (президент — SPA, июль 2026; e-mail офиса президента — официальный сайт), данные не изменены</t>
-        </is>
-      </c>
-      <c r="AH18" s="4" t="inlineStr">
+• Перепроверка: Повторный доступ к imamu.edu.sa блокируется WAF (страница «IMAMU Support», 04.10.2026) — обход не выполнялся; уровень повышен до medium на основании ранее подтверждённых данных (президент — SPA, июль 2026; e-mail офиса президента — официальный сайт), данные не изменены
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI18" s="4" t="inlineStr">
         <is>
           <t>• Https://imamu.edu.sa/en
 • Https://imamu.edu.sa/en/about-university/president-office
 • Https://www.spa.gov.sa/en/N2625933
 • Https://units.imamu.edu.sa/administrations/International_Cooperation/Pages/default.aspx
 • Https://www.qianmu.org/2027QS世界大学排名
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI18" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ18" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ18" s="4" t="inlineStr"/>
+      <c r="AK18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -5115,58 +5447,70 @@
           <t>THE2027: 701–800</t>
         </is>
       </c>
-      <c r="U19" s="4" t="inlineStr"/>
-      <c r="V19" s="4" t="n">
+      <c r="U19" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W19" s="4" t="inlineStr"/>
       <c r="X19" s="4" t="inlineStr"/>
       <c r="Y19" s="4" t="inlineStr"/>
       <c r="Z19" s="4" t="inlineStr"/>
       <c r="AA19" s="4" t="inlineStr"/>
       <c r="AB19" s="4" t="inlineStr"/>
-      <c r="AC19" s="4" t="n">
+      <c r="AC19" s="4" t="inlineStr"/>
+      <c r="AD19" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD19" s="8" t="inlineStr">
+      <c r="AE19" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE19" s="4" t="inlineStr">
+      <c r="AF19" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF19" s="4" t="inlineStr">
+      <c r="AG19" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG19" s="4" t="inlineStr">
+      <c r="AH19" s="4" t="inlineStr">
         <is>
           <t>• Президент с мая 2024 г. (официальная CV на сайте); латинская транслитерация фамилии (العقلا) — наша, на сайте только по-арабски
 • Care@iu.edu.sa — служба по работе с обращениями (единственный опубликованный общий e-mail); телефон 920022042 — единый номер внутри КСА
 • Партнёрствами занимается Центр партнёрств и обмена знаниями (مركز الشراكات والتبادل المعرفي); e-mail и руководитель не опубликованы
-• Профиль преимущественно исламские/гуманитарные науки; спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH19" s="4" t="inlineStr">
+• Профиль преимущественно исламские/гуманитарные науки; спутников не найдено
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI19" s="4" t="inlineStr">
         <is>
           <t>• Https://iu.edu.sa
 • Https://iu.edu.sa/university
 • Https://iu.edu.sa/university/CVofPresident
 • Https://iu.edu.sa/Departments/CorporateKnowledgeExchangeCenter
 • Https://www.qianmu.org/2027QS世界大学排名
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI19" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ19" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ19" s="4" t="inlineStr"/>
+      <c r="AK19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -5261,50 +5605,56 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S20" s="4" t="inlineStr"/>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T20" s="4" t="inlineStr">
         <is>
           <t>THE2027: 701–800</t>
         </is>
       </c>
       <c r="U20" s="4" t="inlineStr"/>
-      <c r="V20" s="4" t="n">
+      <c r="V20" s="4" t="inlineStr"/>
+      <c r="W20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W20" s="4" t="inlineStr"/>
       <c r="X20" s="4" t="inlineStr"/>
       <c r="Y20" s="4" t="inlineStr"/>
       <c r="Z20" s="4" t="inlineStr"/>
       <c r="AA20" s="4" t="inlineStr"/>
       <c r="AB20" s="4" t="inlineStr"/>
-      <c r="AC20" s="4" t="n">
+      <c r="AC20" s="4" t="inlineStr"/>
+      <c r="AD20" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD20" s="8" t="inlineStr">
+      <c r="AE20" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE20" s="4" t="inlineStr">
+      <c r="AF20" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF20" s="4" t="inlineStr">
+      <c r="AG20" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG20" s="4" t="inlineStr">
+      <c r="AH20" s="4" t="inlineStr">
         <is>
           <t>• Сайт jazanu.edu.sa недоступен из нашей сети (HTTP 403 / сброс соединения) — e-mail president@jazanu.edu.sa, телефон и адрес взяты из поисковой выдачи по официальным страницам, НЕ открытым напрямую; обязательно перепроверить
 • Президент исправлен: Dr. Mohammad AbuRasain (Mohammed bin Hassan AbuRasain), с 17.05.2024 — подтверждено Saudi Press Agency 21.04.2026; ранее в строке ошибочно был указан Prof. Mar'ei bin Hussein Al-Qahtani (бывший президент)
 • E-mail международного отдела не найден; используется адрес офиса президента president@jazanu.edu.sa (в письме требуется указать полное имя и мобильный номер)
 • Спутников в nanosats.csv не найдено; отдельная проверка по космосу не проводилась из-за блокировки сайта
-• Перепроверка: ИСПРАВЛЕНО: президент — д-р Мохаммад Абурасаин (SPA, 21.04.2026; в должности с 17.05.2024), а не Al-Qahtani; контакты по-прежнему не открыты (сайт 403)</t>
-        </is>
-      </c>
-      <c r="AH20" s="4" t="inlineStr">
+• Перепроверка: ИСПРАВЛЕНО: президент — д-р Мохаммад Абурасаин (SPA, 21.04.2026; в должности с 17.05.2024), а не Al-Qahtani; контакты по-прежнему не открыты (сайт 403)
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026. Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI20" s="4" t="inlineStr">
         <is>
           <t>• Https://www.jazanu.edu.sa/en/administration/departments/jupresident/contactinfo (via search index
 • Site blocked)
@@ -5313,12 +5663,12 @@
 • Https://spa.gov.sa/en/N2566500</t>
         </is>
       </c>
-      <c r="AI20" s="4" t="inlineStr">
+      <c r="AJ20" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ20" s="4" t="inlineStr"/>
+      <c r="AK20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -5422,56 +5772,69 @@
           <t>THE2027: 651–700</t>
         </is>
       </c>
-      <c r="U21" s="4" t="inlineStr"/>
-      <c r="V21" s="4" t="n">
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W21" s="4" t="inlineStr"/>
       <c r="X21" s="4" t="inlineStr"/>
       <c r="Y21" s="4" t="inlineStr"/>
       <c r="Z21" s="4" t="inlineStr"/>
       <c r="AA21" s="4" t="inlineStr"/>
       <c r="AB21" s="4" t="inlineStr"/>
-      <c r="AC21" s="4" t="n">
+      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AD21" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD21" s="8" t="inlineStr">
+      <c r="AE21" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE21" s="4" t="inlineStr">
+      <c r="AF21" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF21" s="4" t="inlineStr">
+      <c r="AG21" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG21" s="4" t="inlineStr">
+      <c r="AH21" s="4" t="inlineStr">
         <is>
           <t>• E-mail международного отдела не найден; используется общий contact@ju.edu.sa (колл-центр 014 654 4444)
 • Почтовый индекс/а/я не опубликованы на главной странице — адрес неполный
-• Спутников не найдено (nanosats.csv, сайт)</t>
-        </is>
-      </c>
-      <c r="AH21" s="4" t="inlineStr">
+• Спутников не найдено (nanosats.csv, сайт)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI21" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ju.edu.sa/en
 • Https://www.ju.edu.sa/en/He-President-Jouf-University-launches-ai-course
 • Https://www.ju.edu.sa/en/president-meets-partnerships-agreements-team
 • Http://www.qianmu.org/2027QS世界大学排名
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI21" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ21" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ21" s="4" t="inlineStr"/>
+      <c r="AK21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -5580,59 +5943,72 @@
           <t>THE2027: 551–600</t>
         </is>
       </c>
-      <c r="U22" s="4" t="inlineStr"/>
-      <c r="V22" s="4" t="n">
+      <c r="U22" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="W22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W22" s="4" t="inlineStr"/>
       <c r="X22" s="4" t="inlineStr"/>
       <c r="Y22" s="4" t="inlineStr"/>
       <c r="Z22" s="4" t="inlineStr"/>
       <c r="AA22" s="4" t="inlineStr"/>
       <c r="AB22" s="4" t="inlineStr"/>
-      <c r="AC22" s="4" t="n">
+      <c r="AC22" s="4" t="inlineStr"/>
+      <c r="AD22" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD22" s="8" t="inlineStr">
+      <c r="AE22" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE22" s="4" t="inlineStr">
+      <c r="AF22" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF22" s="4" t="inlineStr">
+      <c r="AG22" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG22" s="4" t="inlineStr">
+      <c r="AH22" s="4" t="inlineStr">
         <is>
           <t>• Президент (с октября 2024 г.) подтверждён по газете Al-Jazirah от 21.09.2026, на сайте университета страница ректора не открылась (меню на JavaScript)
 • Телефон 920002366 — единый номер (внутри КСА); отдел международного сотрудничества: +966 13 589 5298
 • Спутников не найдено (nanosats.csv и один поиск)
 • Имя руководителя отдела международного сотрудничества на сайте не указано
-• Профиль: исторически аграрно-ветеринарный университет, ныне многопрофильный</t>
-        </is>
-      </c>
-      <c r="AH22" s="4" t="inlineStr">
+• Профиль: исторически аграрно-ветеринарный университет, ныне многопрофильный
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI22" s="4" t="inlineStr">
         <is>
           <t>• Https://www.kfu.edu.sa/en
 • Https://www.kfu.edu.sa/en/Departments/knowledgeExchange/Pages/Home-new.aspx
 • Https://www.al-jazirahonline.com/2026/09/21/536508/
 • Https://x.com/KFUniversity/status/2026752115150840169
 • Https://www.qianmu.org/2027QS世界大学排名
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI22" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ22" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ22" s="4" t="inlineStr"/>
+      <c r="AK22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -5727,51 +6103,57 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S23" s="4" t="inlineStr"/>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T23" s="4" t="inlineStr">
         <is>
           <t>THE2027: 701–800</t>
         </is>
       </c>
       <c r="U23" s="4" t="inlineStr"/>
-      <c r="V23" s="4" t="n">
+      <c r="V23" s="4" t="inlineStr"/>
+      <c r="W23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W23" s="4" t="inlineStr"/>
       <c r="X23" s="4" t="inlineStr"/>
       <c r="Y23" s="4" t="inlineStr"/>
       <c r="Z23" s="4" t="inlineStr"/>
       <c r="AA23" s="4" t="inlineStr"/>
       <c r="AB23" s="4" t="inlineStr"/>
-      <c r="AC23" s="4" t="n">
+      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AD23" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD23" s="8" t="inlineStr">
+      <c r="AE23" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE23" s="4" t="inlineStr">
+      <c r="AF23" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF23" s="4" t="inlineStr">
+      <c r="AG23" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG23" s="4" t="inlineStr">
+      <c r="AH23" s="4" t="inlineStr">
         <is>
           <t>• Сайт ksau-hs.edu.sa не открывается (устаревший TLS — unsafe legacy renegotiation); адрес, телефон и e-mail взяты из поисковой выдачи официальной страницы контактов, не проверены вручную
 • Ask_dar@ksau-hs.edu.sa — e-mail деканата приёма и регистрации (другого общего адреса не найдено)
 • Университет подчиняется Министерству национальной гвардии (не Минобразования); президент одновременно CEO медицинских служб нацгвардии (MNGHA); подтверждён по программе BIO 2026
 • Медицинский профиль; спутников не найдено (проверка только по nanosats.csv)
 • Имя руководителя по международным партнёрствам не найдено; есть портал соглашений и стратегических партнёрств
-• Перепроверка: Сайт ksau-hs.edu.sa по-прежнему не открывается (устаревший TLS и неполная цепочка сертификатов); данные не изменены</t>
-        </is>
-      </c>
-      <c r="AH23" s="4" t="inlineStr">
+• Перепроверка: Сайт ksau-hs.edu.sa по-прежнему не открывается (устаревший TLS и неполная цепочка сертификатов); данные не изменены
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026. Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI23" s="4" t="inlineStr">
         <is>
           <t>• Https://convention.bio.org/2026-sessions-and-courses/king-saud-bin-abdulaziz-university-for-health-sciences
 • Https://www.ksau-hs.edu.sa/English/About-Us/Pages/ContactKSAU.aspx
@@ -5779,12 +6161,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI23" s="4" t="inlineStr">
+      <c r="AJ23" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ23" s="4" t="inlineStr"/>
+      <c r="AK23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -5860,57 +6242,63 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S24" s="4" t="inlineStr"/>
+      <c r="S24" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T24" s="4" t="inlineStr">
         <is>
           <t>THE2027: 701–800</t>
         </is>
       </c>
       <c r="U24" s="4" t="inlineStr"/>
-      <c r="V24" s="4" t="n">
+      <c r="V24" s="4" t="inlineStr"/>
+      <c r="W24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W24" s="4" t="inlineStr"/>
       <c r="X24" s="4" t="inlineStr"/>
       <c r="Y24" s="4" t="inlineStr"/>
       <c r="Z24" s="4" t="inlineStr"/>
       <c r="AA24" s="4" t="inlineStr"/>
       <c r="AB24" s="4" t="inlineStr"/>
-      <c r="AC24" s="4" t="n">
+      <c r="AC24" s="4" t="inlineStr"/>
+      <c r="AD24" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD24" s="8" t="inlineStr">
+      <c r="AE24" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE24" s="4" t="inlineStr"/>
-      <c r="AF24" s="4" t="inlineStr">
+      <c r="AF24" s="4" t="inlineStr"/>
+      <c r="AG24" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG24" s="4" t="inlineStr">
+      <c r="AH24" s="4" t="inlineStr">
         <is>
           <t>• Сайт mu.edu.sa (и m.mu.edu.sa) недоступен из нашей сети (HTTP 403) — e-mail и адрес не проверены, не заполнены
 • ФИО президента — по Википедии (данные 2026 г.); учёное звание «Prof.» не подтверждено официальным сайтом; телефон — по поисковой выдаче (my.gov.sa), перепроверить
 • Спутников в nanosats.csv не найдено
-• Перепроверка: 04.10.2026: mu.edu.sa (в т.ч. /en через WebFetch) и каталог my.gov.sa по-прежнему отдают 403; данные не изменены</t>
-        </is>
-      </c>
-      <c r="AH24" s="4" t="inlineStr">
+• Перепроверка: 04.10.2026: mu.edu.sa (в т.ч. /en через WebFetch) и каталог my.gov.sa по-прежнему отдают 403; данные не изменены
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026. Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI24" s="4" t="inlineStr">
         <is>
           <t>• Https://en.wikipedia.org/wiki/Majmaah_University
 • Https://my.gov.sa/en/agencies/17441 (via search index)
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI24" s="4" t="inlineStr">
+      <c r="AJ24" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ24" s="4" t="inlineStr"/>
+      <c r="AK24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -6005,64 +6393,79 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S25" s="4" t="inlineStr"/>
+      <c r="S25" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T25" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="U25" s="4" t="inlineStr"/>
-      <c r="V25" s="4" t="n">
+      <c r="U25" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V25" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W25" s="4" t="inlineStr"/>
       <c r="X25" s="4" t="inlineStr"/>
       <c r="Y25" s="4" t="inlineStr"/>
       <c r="Z25" s="4" t="inlineStr"/>
       <c r="AA25" s="4" t="inlineStr"/>
       <c r="AB25" s="4" t="inlineStr"/>
-      <c r="AC25" s="4" t="n">
+      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AD25" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD25" s="8" t="inlineStr">
+      <c r="AE25" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE25" s="4" t="inlineStr">
+      <c r="AF25" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF25" s="4" t="inlineStr">
+      <c r="AG25" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG25" s="4" t="inlineStr">
+      <c r="AH25" s="4" t="inlineStr">
         <is>
           <t>• Президент подтверждён новостью сайта к Нацдню (сентябрь 2026)
 • Care@nu.edu.sa — центр обслуживания обращений (официальная страница «Связаться с нами»); info@nu.edu.sa, адрес и телефон — из вторичного каталога LabOasis
 • Noip@nu.edu.sa (каталог WIPO TISC) относится к офису интеллектуальной собственности, не к международному отделу
-• Международный отдел и его руководитель на сайте не найдены; спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH25" s="4" t="inlineStr">
+• Международный отдел и его руководитель на сайте не найдены; спутников не найдено
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI25" s="4" t="inlineStr">
         <is>
           <t>• Https://www.nu.edu.sa/en
 • Https://portal.nu.edu.sa/contact-us
 • Https://portal.nu.edu.sa:443/en/home/-/asset_publisher/vzkp/content/president-of-najran-university-congratulates-the-supreme-leadership-on-the-occasion-of-national-day/maximized
 • Https://www.laboasis.org/organization/nu-najran-university/
 • Https://www.wipo.int/tisc/en/search/details.jsp?id=12374
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI25" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ25" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ25" s="4" t="inlineStr"/>
+      <c r="AK25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -6167,56 +6570,68 @@
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="U26" s="4" t="inlineStr"/>
-      <c r="V26" s="4" t="n">
+      <c r="U26" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W26" s="4" t="inlineStr"/>
       <c r="X26" s="4" t="inlineStr"/>
       <c r="Y26" s="4" t="inlineStr"/>
       <c r="Z26" s="4" t="inlineStr"/>
       <c r="AA26" s="4" t="inlineStr"/>
       <c r="AB26" s="4" t="inlineStr"/>
-      <c r="AC26" s="4" t="n">
+      <c r="AC26" s="4" t="inlineStr"/>
+      <c r="AD26" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD26" s="8" t="inlineStr">
+      <c r="AE26" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE26" s="4" t="inlineStr">
+      <c r="AF26" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF26" s="4" t="inlineStr">
+      <c r="AG26" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG26" s="4" t="inlineStr">
+      <c r="AH26" s="4" t="inlineStr">
         <is>
           <t>• ФИО президента на сайте только по-арабски (الأستاذ الدكتور أحمد بن علي الرميح) — латинская транслитерация наша
 • E-mail международного отдела не найден; используется адрес офиса президента opu@nbu.edu.sa (факс +966 14 662 0771)
-• Спутников не найдено (nanosats.csv, сайт)</t>
-        </is>
-      </c>
-      <c r="AH26" s="4" t="inlineStr">
+• Спутников не найдено (nanosats.csv, сайт)
+• Рейтинги: QS: в таблице как «Northern Borders University»; Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI26" s="4" t="inlineStr">
         <is>
           <t>• Https://www.nbu.edu.sa/
 • Https://www.nbu.edu.sa/university-administration/university-manager
 • Https://www.nbu.edu.sa/university-administration/president-office/contact-us
 • Http://www.qianmu.org/2027QS世界大学排名
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI26" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ26" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ26" s="4" t="inlineStr"/>
+      <c r="AK26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -6325,57 +6740,70 @@
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="U27" s="4" t="inlineStr"/>
-      <c r="V27" s="4" t="n">
+      <c r="U27" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="inlineStr">
+        <is>
+          <t>1143</t>
+        </is>
+      </c>
+      <c r="W27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W27" s="4" t="inlineStr"/>
       <c r="X27" s="4" t="inlineStr"/>
       <c r="Y27" s="4" t="inlineStr"/>
       <c r="Z27" s="4" t="inlineStr"/>
       <c r="AA27" s="4" t="inlineStr"/>
       <c r="AB27" s="4" t="inlineStr"/>
-      <c r="AC27" s="4" t="n">
+      <c r="AC27" s="4" t="inlineStr"/>
+      <c r="AD27" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD27" s="8" t="inlineStr">
+      <c r="AE27" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE27" s="4" t="inlineStr">
+      <c r="AF27" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF27" s="4" t="inlineStr">
+      <c r="AG27" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG27" s="4" t="inlineStr">
+      <c r="AH27" s="4" t="inlineStr">
         <is>
           <t>• Президент — профессор электротехники (PhD, Ohio University); страница CV на официальном сайте, дата назначения не указана
 • Cir@qu.edu.sa (тел. +966 16 302 0768) в официальном справочнике значится за «Управлением обмена знаниями и научных мероприятий» (إدارة التبادل المعرفي والفعاليات العلمية); по поисковой выдаче — Центр международного сотрудничества и обмена знаниями; имя руководителя не найдено
-• Спутников не найдено (nanosats.csv и один поиск)</t>
-        </is>
-      </c>
-      <c r="AH27" s="4" t="inlineStr">
+• Спутников не найдено (nanosats.csv и один поиск)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI27" s="4" t="inlineStr">
         <is>
           <t>• Https://qu.edu.sa/en
 • Https://www.qu.edu.sa/en/university-president/cv/
 • Https://www.qu.edu.sa/en/contact-us/
 • Https://www.qu.edu.sa/contact?lang=en
 • Https://www.qianmu.org/2027QS世界大学排名
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI27" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ27" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ27" s="4" t="inlineStr"/>
+      <c r="AK27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -6469,62 +6897,77 @@
           <t>Acting President</t>
         </is>
       </c>
-      <c r="S28" s="4" t="inlineStr"/>
+      <c r="S28" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T28" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="U28" s="4" t="inlineStr"/>
-      <c r="V28" s="4" t="n">
+      <c r="U28" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W28" s="4" t="inlineStr"/>
       <c r="X28" s="4" t="inlineStr"/>
       <c r="Y28" s="4" t="inlineStr"/>
       <c r="Z28" s="4" t="inlineStr"/>
       <c r="AA28" s="4" t="inlineStr"/>
       <c r="AB28" s="4" t="inlineStr"/>
-      <c r="AC28" s="4" t="n">
+      <c r="AC28" s="4" t="inlineStr"/>
+      <c r="AD28" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD28" s="8" t="inlineStr">
+      <c r="AE28" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE28" s="4" t="inlineStr">
+      <c r="AF28" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF28" s="4" t="inlineStr">
+      <c r="AG28" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG28" s="4" t="inlineStr">
+      <c r="AH28" s="4" t="inlineStr">
         <is>
           <t>• Руководитель — исполняющий обязанности президента (Acting President) — должность может смениться
 • E-mail международного отдела не найден; общий info@su.edu.sa (факс +966 11 647 7762)
 • Полный почтовый адрес на сайте не указан — только «Шакра»
-• Спутников не найдено (nanosats.csv, сайт)</t>
-        </is>
-      </c>
-      <c r="AH28" s="4" t="inlineStr">
+• Спутников не найдено (nanosats.csv, сайт)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI28" s="4" t="inlineStr">
         <is>
           <t>• Https://www.su.edu.sa/en
 • Https://www.su.edu.sa/en/contact/form
 • Https://www.su.edu.sa/en/news/su-times-ranking-2027
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI28" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ28" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ28" s="4" t="inlineStr"/>
+      <c r="AK28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -6629,43 +7072,53 @@
           <t>THE2027: 701–800</t>
         </is>
       </c>
-      <c r="U29" s="4" t="inlineStr"/>
-      <c r="V29" s="4" t="n">
+      <c r="U29" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="inlineStr">
+        <is>
+          <t>919</t>
+        </is>
+      </c>
+      <c r="W29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W29" s="4" t="inlineStr"/>
       <c r="X29" s="4" t="inlineStr"/>
       <c r="Y29" s="4" t="inlineStr"/>
       <c r="Z29" s="4" t="inlineStr"/>
       <c r="AA29" s="4" t="inlineStr"/>
       <c r="AB29" s="4" t="inlineStr"/>
-      <c r="AC29" s="4" t="n">
+      <c r="AC29" s="4" t="inlineStr"/>
+      <c r="AD29" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD29" s="8" t="inlineStr">
+      <c r="AE29" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE29" s="4" t="inlineStr">
+      <c r="AF29" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF29" s="4" t="inlineStr">
+      <c r="AG29" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG29" s="4" t="inlineStr">
+      <c r="AH29" s="4" t="inlineStr">
         <is>
           <t>• Президент подтверждён новостью сайта от 20.09.2026
 • Единственный опубликованный e-mail — websupport@tu.edu.sa (техподдержка сайта); лучше использовать платформу партнёрств webapps1.tu.edu.sa/partnership
 • Есть Управление контрактов и международного сотрудничества и Отдел стратегических партнёрств и инициатив (руководитель Dr. Abdullah bin Hasan Al-Shahri; e-mail не опубликован)
-• Спутников не найдено; кафедра компьютерной инженерии вела работы по CubeSat-прототипу для управления толпой (испытание на высоте 15 м, 2022)</t>
-        </is>
-      </c>
-      <c r="AH29" s="4" t="inlineStr">
+• Спутников не найдено; кафедра компьютерной инженерии вела работы по CubeSat-прототипу для управления толпой (испытание на высоте 15 м, 2022)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI29" s="4" t="inlineStr">
         <is>
           <t>• Https://www.tu.edu.sa/En
 • Https://www.tu.edu.sa/En/University/Pages/20291/Contact-Us
@@ -6674,15 +7127,18 @@
 • Https://www.tu.edu.sa/En/Administrations/262/Contracting-and-international-cooperation-management
 • Https://www.astesj.com/v07/i06/p12/
 • Https://www.qianmu.org/2027QS世界大学排名
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI29" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ29" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ29" s="4" t="inlineStr"/>
+      <c r="AK29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -6786,57 +7242,69 @@
           <t>THE2027: 701–800</t>
         </is>
       </c>
-      <c r="U30" s="4" t="inlineStr"/>
-      <c r="V30" s="4" t="n">
+      <c r="U30" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="4" t="inlineStr"/>
       <c r="X30" s="4" t="inlineStr"/>
       <c r="Y30" s="4" t="inlineStr"/>
       <c r="Z30" s="4" t="inlineStr"/>
       <c r="AA30" s="4" t="inlineStr"/>
       <c r="AB30" s="4" t="inlineStr"/>
-      <c r="AC30" s="4" t="n">
+      <c r="AC30" s="4" t="inlineStr"/>
+      <c r="AD30" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD30" s="8" t="inlineStr">
+      <c r="AE30" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE30" s="4" t="inlineStr">
+      <c r="AF30" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF30" s="4" t="inlineStr">
+      <c r="AG30" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG30" s="4" t="inlineStr">
+      <c r="AH30" s="4" t="inlineStr">
         <is>
           <t>• E-mail международного отдела не найден; общий info@uoh.edu.sa
 • На сайте телефон указан с опечаткой «+996 165109200» — исправлено на +966
 • Почтовый адрес на сайте только «Хаиль — Университетский городок», без индекса
-• Спутников не найдено (nanosats.csv, сайт)</t>
-        </is>
-      </c>
-      <c r="AH30" s="4" t="inlineStr">
+• Спутников не найдено (nanosats.csv, сайт)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI30" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uoh.edu.sa/
 • Https://www.uoh.edu.sa/Ar/Pages/Contacts.aspx
 • Https://www.uoh.edu.sa/Ar/About/Pages/President.aspx
 • Http://www.qianmu.org/2027QS世界大学排名
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI30" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ30" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ30" s="4" t="inlineStr"/>
+      <c r="AK30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -6941,57 +7409,69 @@
           <t>THE2027: 651–700</t>
         </is>
       </c>
-      <c r="U31" s="4" t="inlineStr"/>
-      <c r="V31" s="4" t="n">
+      <c r="U31" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W31" s="4" t="inlineStr"/>
       <c r="X31" s="4" t="inlineStr"/>
       <c r="Y31" s="4" t="inlineStr"/>
       <c r="Z31" s="4" t="inlineStr"/>
       <c r="AA31" s="4" t="inlineStr"/>
       <c r="AB31" s="4" t="inlineStr"/>
-      <c r="AC31" s="4" t="n">
+      <c r="AC31" s="4" t="inlineStr"/>
+      <c r="AD31" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD31" s="8" t="inlineStr">
+      <c r="AE31" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE31" s="4" t="inlineStr">
+      <c r="AF31" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF31" s="4" t="inlineStr">
+      <c r="AG31" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG31" s="4" t="inlineStr">
+      <c r="AH31" s="4" t="inlineStr">
         <is>
           <t>• Почтовый адрес (P.O. Box) на сайте не указан — только «Kingdom of Saudi Arabia - Tabuk»
 • Есть International Partnerships and Cooperation Unit (при проректорате по аспирантуре и науке), но контакты и руководитель на странице не опубликованы — письмо направлять на ut@ut.edu.sa
-• Спутников не найдено; сотрудники кафедры электротехники публикуют работы по системам питания CubeSat (Scientific Reports, 2026)</t>
-        </is>
-      </c>
-      <c r="AH31" s="4" t="inlineStr">
+• Спутников не найдено; сотрудники кафедры электротехники публикуют работы по системам питания CubeSat (Scientific Reports, 2026)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI31" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ut.edu.sa/en
 • Https://www.ut.edu.sa/en/contact-us/contact-university
 • Https://www.ut.edu.sa/en/about-ut/who-we-are/university-leaders
 • Https://www.ut.edu.sa/en/graduate-studies-and-scientific-research/international-partnerships-and-cooperation-unit
 • Https://www.qianmu.org/2027QS世界大学排名
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI31" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ31" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ31" s="4" t="inlineStr"/>
+      <c r="AK31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -7081,50 +7561,56 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S32" s="4" t="inlineStr"/>
+      <c r="S32" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T32" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr"/>
-      <c r="V32" s="4" t="n">
+      <c r="V32" s="4" t="inlineStr"/>
+      <c r="W32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W32" s="4" t="inlineStr"/>
       <c r="X32" s="4" t="inlineStr"/>
       <c r="Y32" s="4" t="inlineStr"/>
       <c r="Z32" s="4" t="inlineStr"/>
       <c r="AA32" s="4" t="inlineStr"/>
       <c r="AB32" s="4" t="inlineStr"/>
-      <c r="AC32" s="4" t="n">
+      <c r="AC32" s="4" t="inlineStr"/>
+      <c r="AD32" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD32" s="8" t="inlineStr">
+      <c r="AE32" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE32" s="4" t="inlineStr">
+      <c r="AF32" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF32" s="4" t="inlineStr">
+      <c r="AG32" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG32" s="4" t="inlineStr">
+      <c r="AH32" s="4" t="inlineStr">
         <is>
           <t>• Сайт bu.edu.sa недоступен из нашей сети (HTTP 503/обрыв соединения) — e-mail contact@bu.edu.sa, телефон (+966 17 725 7700, доб. 15005; факс +966 17 725 7777) и ФИО взяты из поисковой выдачи по странице офиса президента и Википедии; перепроверить
 • По той же выдаче директор офиса президента — Mr. Abdullah Alzahrani
 • Главный кампус — в Аль-Акике (~25 км от г. Эль-Баха); почтовый адрес не проверен
 • Спутников в nanosats.csv не найдено
-• Перепроверка: Сайт bu.edu.sa по-прежнему недоступен (04.10.2026: сброс соединения, WebFetch — 503); данные не изменены</t>
-        </is>
-      </c>
-      <c r="AH32" s="4" t="inlineStr">
+• Перепроверка: Сайт bu.edu.sa по-прежнему недоступен (04.10.2026: сброс соединения, WebFetch — 503); данные не изменены
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026. Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI32" s="4" t="inlineStr">
         <is>
           <t>• Https://bu.edu.sa/en/web/office-of-the-president (via search index
 • Site blocked)
@@ -7132,12 +7618,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI32" s="4" t="inlineStr">
+      <c r="AJ32" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ32" s="4" t="inlineStr"/>
+      <c r="AK32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -7236,63 +7722,78 @@
           <t>Dean</t>
         </is>
       </c>
-      <c r="S33" s="4" t="inlineStr"/>
+      <c r="S33" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T33" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="U33" s="4" t="inlineStr"/>
-      <c r="V33" s="4" t="n">
+      <c r="U33" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W33" s="4" t="inlineStr"/>
       <c r="X33" s="4" t="inlineStr"/>
       <c r="Y33" s="4" t="inlineStr"/>
       <c r="Z33" s="4" t="inlineStr"/>
       <c r="AA33" s="4" t="inlineStr"/>
       <c r="AB33" s="4" t="inlineStr"/>
-      <c r="AC33" s="4" t="n">
+      <c r="AC33" s="4" t="inlineStr"/>
+      <c r="AD33" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD33" s="8" t="inlineStr">
+      <c r="AE33" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE33" s="4" t="inlineStr">
+      <c r="AF33" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF33" s="4" t="inlineStr">
+      <c r="AG33" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG33" s="4" t="inlineStr">
+      <c r="AH33" s="4" t="inlineStr">
         <is>
           <t>• Частный медицинский колледж (кампусы в Джидде, Асире и Даммаме); руководитель — декан (Dean), а не президент
 • Bd@bmc.edu.sa — отдел развития бизнеса/партнёрств; International Student Office ориентирован на студентов
 • Телефон 920033923 — единый номер (на сайте также в формате +966 920033923)
-• Медицинский профиль; спутников не найдено (проверка только по nanosats.csv)</t>
-        </is>
-      </c>
-      <c r="AH33" s="4" t="inlineStr">
+• Медицинский профиль; спутников не найдено (проверка только по nanosats.csv)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI33" s="4" t="inlineStr">
         <is>
           <t>• Https://bmc.edu.sa/en/
 • Https://bmc.edu.sa/en/About-BMC/Message-from-the-Dean
 • Https://bmc.edu.sa/en/Business-Development/Contact-Us
 • Https://bmc.edu.sa/en/International-Student-Office
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI33" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ33" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ33" s="4" t="inlineStr"/>
+      <c r="AK33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -7371,60 +7872,75 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S34" s="4" t="inlineStr"/>
+      <c r="S34" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T34" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="U34" s="4" t="inlineStr"/>
-      <c r="V34" s="4" t="n">
+      <c r="U34" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W34" s="4" t="inlineStr"/>
       <c r="X34" s="4" t="inlineStr"/>
       <c r="Y34" s="4" t="inlineStr"/>
       <c r="Z34" s="4" t="inlineStr"/>
       <c r="AA34" s="4" t="inlineStr"/>
       <c r="AB34" s="4" t="inlineStr"/>
-      <c r="AC34" s="4" t="n">
+      <c r="AC34" s="4" t="inlineStr"/>
+      <c r="AD34" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD34" s="8" t="inlineStr">
+      <c r="AE34" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE34" s="4" t="inlineStr"/>
-      <c r="AF34" s="4" t="inlineStr">
+      <c r="AF34" s="4" t="inlineStr"/>
+      <c r="AG34" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG34" s="4" t="inlineStr">
+      <c r="AH34" s="4" t="inlineStr">
         <is>
           <t>• Электронный (дистанционно-смешанный) университет с филиалами в 17 городах; инженерного/космического профиля нет
 • Общий e-mail на сайте не опубликован — обращения через форму «Contact Us» (seu.edu.sa/external) и X @SEU_Care
 • Есть Управление партнёрств и международного сотрудничества (при проректорате по аспирантуре и науке), но контакты и руководитель не указаны
-• Спутников не найдено (проверка только по nanosats.csv — лимит веб-поиска исчерпан)</t>
-        </is>
-      </c>
-      <c r="AH34" s="4" t="inlineStr">
+• Спутников не найдено (проверка только по nanosats.csv — лимит веб-поиска исчерпан)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI34" s="4" t="inlineStr">
         <is>
           <t>• Https://seu.edu.sa/en/
 • Https://seu.edu.sa/en/university-presidency/
 • Https://seu.edu.sa/en/about/location/
 • Https://seu.edu.sa/external/
 • Https://seu.edu.sa/en/administrations/partnerships-and-international-cooperation-administration/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI34" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ34" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ34" s="4" t="inlineStr"/>
+      <c r="AK34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -7529,59 +8045,72 @@
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="U35" s="4" t="inlineStr"/>
-      <c r="V35" s="4" t="n">
+      <c r="U35" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V35" s="4" t="inlineStr">
+        <is>
+          <t>1432</t>
+        </is>
+      </c>
+      <c r="W35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W35" s="4" t="inlineStr"/>
       <c r="X35" s="4" t="inlineStr"/>
       <c r="Y35" s="4" t="inlineStr"/>
       <c r="Z35" s="4" t="inlineStr"/>
       <c r="AA35" s="4" t="inlineStr"/>
       <c r="AB35" s="4" t="inlineStr"/>
-      <c r="AC35" s="4" t="n">
+      <c r="AC35" s="4" t="inlineStr"/>
+      <c r="AD35" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD35" s="8" t="inlineStr">
+      <c r="AE35" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE35" s="4" t="inlineStr">
+      <c r="AF35" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF35" s="4" t="inlineStr">
+      <c r="AG35" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG35" s="4" t="inlineStr">
+      <c r="AH35" s="4" t="inlineStr">
         <is>
           <t>• Президент — первая женщина-ректор саудовского университета (с ноября 2023 г.); подтверждена новостью сайта от 07.04.2026
 • Tu@taibahu.edu.sa — официальный адрес для официальной переписки; tawasul@taibahu.edu.sa — общие запросы
 • Сайт с curl недоступен (таймаут/503), данные получены через WebFetch
 • Отдельный международный отдел и его руководитель на сайте не указаны (есть программа стратегических партнёрств)
-• Спутников не найдено (проверка только по nanosats.csv — лимит веб-поиска исчерпан)</t>
-        </is>
-      </c>
-      <c r="AH35" s="4" t="inlineStr">
+• Спутников не найдено (проверка только по nanosats.csv — лимит веб-поиска исчерпан)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI35" s="4" t="inlineStr">
         <is>
           <t>• Https://www.taibahu.edu.sa/en/contact-us
 • Https://www.taibahu.edu.sa/en/administration-of-media-and-communication/media-center/news-53
 • Https://www.taibahu.edu.sa/en/the-university/resources-and-information/partnerships
 • Https://saudigazette.com.sa/article/637292
 • Https://www.qianmu.org/2027QS世界大学排名
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI35" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ35" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ35" s="4" t="inlineStr"/>
+      <c r="AK35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -7672,63 +8201,78 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S36" s="4" t="inlineStr"/>
+      <c r="S36" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T36" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="U36" s="4" t="inlineStr"/>
-      <c r="V36" s="4" t="n">
+      <c r="U36" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V36" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W36" s="4" t="inlineStr"/>
       <c r="X36" s="4" t="inlineStr"/>
       <c r="Y36" s="4" t="inlineStr"/>
       <c r="Z36" s="4" t="inlineStr"/>
       <c r="AA36" s="4" t="inlineStr"/>
       <c r="AB36" s="4" t="inlineStr"/>
-      <c r="AC36" s="4" t="n">
+      <c r="AC36" s="4" t="inlineStr"/>
+      <c r="AD36" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD36" s="8" t="inlineStr">
+      <c r="AE36" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE36" s="4" t="inlineStr">
+      <c r="AF36" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF36" s="4" t="inlineStr">
+      <c r="AG36" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG36" s="4" t="inlineStr">
+      <c r="AH36" s="4" t="inlineStr">
         <is>
           <t>• Новый сайт ub.edu.sa — SPA; e-mail president_office@ub.edu.sa и телефон +966 17 623 8093 заданы в коде официальной страницы «Президент университета» (проверено 04.10.2026); ccm@ub.edu.sa — общий ящик из подвала сайта
 • Президент подтверждён новостью официального сайта за октябрь 2026 (أ.د. محمد بن محسن صفحي)
 • Почтовый адрес не найден (страница контактов подгружает данные динамически); e-mail международного отдела не найден
 • Спутников не найдено (nanosats.csv, новости сайта)
-• Перепроверка: Добавлены e-mail и телефон офиса президента с официальной страницы президента (04.10.2026); президент подтверждён новостями сайта 10.2026</t>
-        </is>
-      </c>
-      <c r="AH36" s="4" t="inlineStr">
+• Перепроверка: Добавлены e-mail и телефон офиса президента с официальной страницы президента (04.10.2026); президент подтверждён новостями сайта 10.2026
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI36" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ub.edu.sa/
 • Https://www.ub.edu.sa/university-president (assets/university-president-Du7USWOi.js)
 • Https://ubapi.ub.edu.sa/api/cms/news
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI36" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ36" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ36" s="4" t="inlineStr"/>
+      <c r="AK36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -7822,61 +8366,76 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S37" s="4" t="inlineStr"/>
+      <c r="S37" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T37" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="U37" s="4" t="inlineStr"/>
-      <c r="V37" s="4" t="n">
+      <c r="U37" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V37" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W37" s="4" t="inlineStr"/>
       <c r="X37" s="4" t="inlineStr"/>
       <c r="Y37" s="4" t="inlineStr"/>
       <c r="Z37" s="4" t="inlineStr"/>
       <c r="AA37" s="4" t="inlineStr"/>
       <c r="AB37" s="4" t="inlineStr"/>
-      <c r="AC37" s="4" t="n">
+      <c r="AC37" s="4" t="inlineStr"/>
+      <c r="AD37" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD37" s="8" t="inlineStr">
+      <c r="AE37" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE37" s="4" t="inlineStr">
+      <c r="AF37" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF37" s="4" t="inlineStr">
+      <c r="AG37" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG37" s="4" t="inlineStr">
+      <c r="AH37" s="4" t="inlineStr">
         <is>
           <t>• ФИО президента взято из новости на арабской главной странице (أ.د. خالد بن باني الحربي, начало 1448 г.х. / 2026) — латиница наша
 • E-mail международного отдела не найден; общий info@uhb.edu.sa (факс +966 13 720 4931)
-• Спутников не найдено (nanosats.csv, сайт)</t>
-        </is>
-      </c>
-      <c r="AH37" s="4" t="inlineStr">
+• Спутников не найдено (nanosats.csv, сайт)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI37" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uhb.edu.sa/en
 • Https://www.uhb.edu.sa/ar
 • Https://www.uhb.edu.sa/en/contact/form
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI37" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ37" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ37" s="4" t="inlineStr"/>
+      <c r="AK37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -7975,63 +8534,78 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S38" s="4" t="inlineStr"/>
+      <c r="S38" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T38" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="U38" s="4" t="inlineStr"/>
-      <c r="V38" s="4" t="n">
+      <c r="U38" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W38" s="4" t="inlineStr"/>
       <c r="X38" s="4" t="inlineStr"/>
       <c r="Y38" s="4" t="inlineStr"/>
       <c r="Z38" s="4" t="inlineStr"/>
       <c r="AA38" s="4" t="inlineStr"/>
       <c r="AB38" s="4" t="inlineStr"/>
-      <c r="AC38" s="4" t="n">
+      <c r="AC38" s="4" t="inlineStr"/>
+      <c r="AD38" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD38" s="8" t="inlineStr">
+      <c r="AE38" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE38" s="4" t="inlineStr">
+      <c r="AF38" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF38" s="4" t="inlineStr">
+      <c r="AG38" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG38" s="4" t="inlineStr">
+      <c r="AH38" s="4" t="inlineStr">
         <is>
           <t>• Международное сотрудничество ведёт Деканат аспирантуры и международного сотрудничества (dgs@uj.edu.sa); есть также вице-декан по стипендиям/обучению dgs-vdean.sic@uj.edu.sa
 • Декан — Dr. Faten bint Mohammed Ali Zainalabdeen Zaini (по новости на сайте деканата, дата публикации не указана); вице-декан женского отделения и межд. сотрудничества — Dr. Samar Al-Jahdali
-• Спутников не найдено (проверка только по nanosats.csv — лимит веб-поиска исчерпан)</t>
-        </is>
-      </c>
-      <c r="AH38" s="4" t="inlineStr">
+• Спутников не найдено (проверка только по nanosats.csv — лимит веб-поиска исчерпан)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI38" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uj.edu.sa/en
 • Https://www.uj.edu.sa/en/senior-leadership
 • Https://www.uj.edu.sa/en/contact-us
 • Https://www.uj.edu.sa/en/global-partnerships
 • Https://dgs.uj.edu.sa/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI38" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ38" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ38" s="4" t="inlineStr"/>
+      <c r="AK38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -8129,45 +8703,63 @@
           <t>Acting President</t>
         </is>
       </c>
-      <c r="S39" s="4" t="inlineStr"/>
-      <c r="T39" s="4" t="inlineStr"/>
-      <c r="U39" s="4" t="inlineStr"/>
-      <c r="V39" s="4" t="n">
+      <c r="S39" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T39" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U39" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V39" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W39" s="4" t="inlineStr"/>
       <c r="X39" s="4" t="inlineStr"/>
       <c r="Y39" s="4" t="inlineStr"/>
       <c r="Z39" s="4" t="inlineStr"/>
       <c r="AA39" s="4" t="inlineStr"/>
       <c r="AB39" s="4" t="inlineStr"/>
-      <c r="AC39" s="4" t="n">
+      <c r="AC39" s="4" t="inlineStr"/>
+      <c r="AD39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD39" s="8" t="inlineStr">
+      <c r="AE39" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE39" s="4" t="inlineStr">
+      <c r="AF39" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF39" s="4" t="inlineStr">
+      <c r="AG39" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG39" s="4" t="inlineStr">
+      <c r="AH39" s="4" t="inlineStr">
         <is>
           <t>• Частный университет (бизнес, инженерия, право); есть кампус в Эль-Хобаре
 • Global Engagement Office: директор Dr. Mashhour Mourad (m_mourad@yu.edu.sa, доб. 3001); менеджер по международным партнёрствам Ms. Raghad Balkhi (r_balkhi@yu.edu.sa, доб. 3043)
 • Руководитель — исполняющий обязанности президента (Acting President), данные мая 2026
-• Не входит в THE2027/QS2027; спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH39" s="4" t="inlineStr">
+• Не входит в THE2027/QS2027; спутников не найдено
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI39" s="4" t="inlineStr">
         <is>
           <t>• Https://yu.edu.sa/global-engagement-office/
 • Https://yu.edu.sa/about/about-yu/locate-us/
@@ -8175,12 +8767,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI39" s="4" t="inlineStr">
+      <c r="AJ39" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ39" s="4" t="inlineStr"/>
+      <c r="AK39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -8274,47 +8866,65 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S40" s="4" t="inlineStr"/>
-      <c r="T40" s="4" t="inlineStr"/>
-      <c r="U40" s="4" t="inlineStr"/>
-      <c r="V40" s="4" t="n">
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T40" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U40" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V40" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W40" s="4" t="inlineStr"/>
       <c r="X40" s="4" t="inlineStr"/>
       <c r="Y40" s="4" t="inlineStr"/>
       <c r="Z40" s="4" t="inlineStr"/>
       <c r="AA40" s="4" t="inlineStr"/>
       <c r="AB40" s="4" t="inlineStr"/>
-      <c r="AC40" s="4" t="n">
+      <c r="AC40" s="4" t="inlineStr"/>
+      <c r="AD40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD40" s="8" t="inlineStr">
+      <c r="AE40" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE40" s="4" t="inlineStr">
+      <c r="AF40" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF40" s="4" t="inlineStr">
+      <c r="AG40" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG40" s="4" t="inlineStr">
+      <c r="AH40" s="4" t="inlineStr">
         <is>
           <t>• Саудовское отделение некоммерческого Арабского открытого университета (штаб-квартира в Кувейте), смешанное/дистанционное обучение; партнёр Open University (UK)
 • Есть раздел Local and International Relations, но отдельного e-mail/руководителя нет — использовать info@arabou.edu.sa; второй телефон +966 11 274 2696
 • Филиалы: Даммам/Эль-Хаса (Dr. Mohammad Alsaif), Джидда (Dr. Osamah Alzaid), Медина (Dr. Abdullah AlGhamdi)
 • Инженерного/космического профиля нет; спутников не найдено (проверка только по nanosats.csv)
 • 04.10.2026: страница About (сайт активно обновляется, новости до 30.09.2026) по-прежнему называет президентом Prof. Dr. Ali bin Mohammed Al-Shahrani; адрес, info@arabou.edu.sa и телефоны подтверждены. В новостях 2026 г. («رئيس الجامعة…», 26.08.2026) имя президента не указано — дата назначения не подтверждена
-• Перепроверка: Президент, адрес, e-mail и телефоны подтверждены на сайте arabou.edu.sa 04.10.2026 (страница без даты, сайт обновляется в 2026)</t>
-        </is>
-      </c>
-      <c r="AH40" s="4" t="inlineStr">
+• Перепроверка: Президент, адрес, e-mail и телефоны подтверждены на сайте arabou.edu.sa 04.10.2026 (страница без даты, сайт обновляется в 2026)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI40" s="4" t="inlineStr">
         <is>
           <t>• Https://www.arabou.edu.sa/
 • Https://www.arabou.edu.sa/about
@@ -8323,12 +8933,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI40" s="4" t="inlineStr">
+      <c r="AJ40" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ40" s="4" t="inlineStr"/>
+      <c r="AK40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -8422,45 +9032,63 @@
           <t>Acting President</t>
         </is>
       </c>
-      <c r="S41" s="4" t="inlineStr"/>
-      <c r="T41" s="4" t="inlineStr"/>
-      <c r="U41" s="4" t="inlineStr"/>
-      <c r="V41" s="4" t="n">
+      <c r="S41" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T41" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U41" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V41" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W41" s="4" t="inlineStr"/>
       <c r="X41" s="4" t="inlineStr"/>
       <c r="Y41" s="4" t="inlineStr"/>
       <c r="Z41" s="4" t="inlineStr"/>
       <c r="AA41" s="4" t="inlineStr"/>
       <c r="AB41" s="4" t="inlineStr"/>
-      <c r="AC41" s="4" t="n">
+      <c r="AC41" s="4" t="inlineStr"/>
+      <c r="AD41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD41" s="8" t="inlineStr">
+      <c r="AE41" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE41" s="4" t="inlineStr">
+      <c r="AF41" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF41" s="4" t="inlineStr">
+      <c r="AG41" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG41" s="4" t="inlineStr">
+      <c r="AH41" s="4" t="inlineStr">
         <is>
           <t>• Частный университет (медицина, стоматология, инженерия, право, бизнес)
 • Руководитель — исполняющий обязанности президента (رئيس الجامعة المكلف) с сентября 2026: أ.د. حسام بن محمد رمضان (латиница наша); до этого президентом был Prof. Dr. Khalid bin Abdulrahman Al-Hamoudi
 • E-mail международного отдела не найден; общий info@dau.edu.sa, факс +966 11 494 9490; почтовый индекс/а-я не найдены
-• Спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH41" s="4" t="inlineStr">
+• Спутников не найдено
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI41" s="4" t="inlineStr">
         <is>
           <t>• Https://dau.edu.sa/
 • Https://dau.edu.sa/عن-الجامعة/اتصل-بنا-2/
@@ -8468,12 +9096,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI41" s="4" t="inlineStr">
+      <c r="AJ41" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ41" s="4" t="inlineStr"/>
+      <c r="AK41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -8572,45 +9200,63 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S42" s="4" t="inlineStr"/>
-      <c r="T42" s="4" t="inlineStr"/>
-      <c r="U42" s="4" t="inlineStr"/>
-      <c r="V42" s="4" t="n">
+      <c r="S42" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T42" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U42" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V42" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W42" s="4" t="inlineStr"/>
       <c r="X42" s="4" t="inlineStr"/>
       <c r="Y42" s="4" t="inlineStr"/>
       <c r="Z42" s="4" t="inlineStr"/>
       <c r="AA42" s="4" t="inlineStr"/>
       <c r="AB42" s="4" t="inlineStr"/>
-      <c r="AC42" s="4" t="n">
+      <c r="AC42" s="4" t="inlineStr"/>
+      <c r="AD42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD42" s="8" t="inlineStr">
+      <c r="AE42" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE42" s="4" t="inlineStr">
+      <c r="AF42" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF42" s="4" t="inlineStr">
+      <c r="AG42" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG42" s="4" t="inlineStr">
+      <c r="AH42" s="4" t="inlineStr">
         <is>
           <t>• Частный некоммерческий женский университет (Джидда)
 • Communications@dah.edu.sa — отдел маркетинга и коммуникаций (отдельного общего/ректорского адреса нет); единый номер +966 9200 16965
 • Партнёрствами (местными и международными) занимается Collaboration Unit при президенте — директор Dr. Ahlam Alaki, e-mail отдела не опубликован; BusinessDevelopment@dah.edu.sa — Business Development &amp; Consultancy
-• Космического профиля нет; спутников не найдено (проверка только по nanosats.csv)</t>
-        </is>
-      </c>
-      <c r="AH42" s="4" t="inlineStr">
+• Космического профиля нет; спутников не найдено (проверка только по nanosats.csv)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI42" s="4" t="inlineStr">
         <is>
           <t>• Https://www.dah.edu.sa/en
 • Https://www.dah.edu.sa/en/about/Pages/President.aspx
@@ -8619,12 +9265,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI42" s="4" t="inlineStr">
+      <c r="AJ42" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ42" s="4" t="inlineStr"/>
+      <c r="AK42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -8717,45 +9363,63 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S43" s="4" t="inlineStr"/>
-      <c r="T43" s="4" t="inlineStr"/>
-      <c r="U43" s="4" t="inlineStr"/>
-      <c r="V43" s="4" t="n">
+      <c r="S43" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T43" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U43" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V43" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W43" s="4" t="inlineStr"/>
       <c r="X43" s="4" t="inlineStr"/>
       <c r="Y43" s="4" t="inlineStr"/>
       <c r="Z43" s="4" t="inlineStr"/>
       <c r="AA43" s="4" t="inlineStr"/>
       <c r="AB43" s="4" t="inlineStr"/>
-      <c r="AC43" s="4" t="n">
+      <c r="AC43" s="4" t="inlineStr"/>
+      <c r="AD43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD43" s="8" t="inlineStr">
+      <c r="AE43" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE43" s="4" t="inlineStr">
+      <c r="AF43" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF43" s="4" t="inlineStr">
+      <c r="AG43" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG43" s="4" t="inlineStr">
+      <c r="AH43" s="4" t="inlineStr">
         <is>
           <t>• Частный университет в Табуке (с 2004 г.); 4 инженерные программы аккредитованы ABET
 • E-mail международного отдела не найден; общий info@fbsu.edu.sa
 • Страница президента не датирована — актуальность ФИО подтверждена только текущим сайтом
-• Спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH43" s="4" t="inlineStr">
+• Спутников не найдено
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI43" s="4" t="inlineStr">
         <is>
           <t>• Https://www.fbsu.edu.sa/
 • Https://fbsu.edu.sa/Contacts
@@ -8763,12 +9427,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI43" s="4" t="inlineStr">
+      <c r="AJ43" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ43" s="4" t="inlineStr"/>
+      <c r="AK43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -8835,52 +9499,62 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="S44" s="4" t="inlineStr"/>
-      <c r="T44" s="4" t="inlineStr"/>
+      <c r="S44" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T44" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="U44" s="4" t="inlineStr"/>
-      <c r="V44" s="4" t="n">
+      <c r="V44" s="4" t="inlineStr"/>
+      <c r="W44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W44" s="4" t="inlineStr"/>
       <c r="X44" s="4" t="inlineStr"/>
       <c r="Y44" s="4" t="inlineStr"/>
       <c r="Z44" s="4" t="inlineStr"/>
       <c r="AA44" s="4" t="inlineStr"/>
       <c r="AB44" s="4" t="inlineStr"/>
-      <c r="AC44" s="4" t="n">
+      <c r="AC44" s="4" t="inlineStr"/>
+      <c r="AD44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD44" s="8" t="inlineStr">
+      <c r="AE44" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE44" s="4" t="inlineStr"/>
-      <c r="AF44" s="4" t="inlineStr">
+      <c r="AF44" s="4" t="inlineStr"/>
+      <c r="AG44" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG44" s="4" t="inlineStr">
+      <c r="AH44" s="4" t="inlineStr">
         <is>
           <t>• Сайт www.jic.edu.sa недоступен (DNS не разрешается/прокси отклоняет соединение), портал Королевской комиссии rcjy.edu.sa отвечает 503; лимит веб-поиска исчерпан — контакты и руководитель НЕ проверены
 • Колледж Королевской комиссии по Джубайлю и Янбу (не Минобразования); прикладной инженерно-технологический профиль; должность руководителя (Managing Director) не подтверждена
 • Спутников не найдено (проверка только по nanosats.csv)
 • Требуется ручная доработка перед рассылкой
-• Перепроверка: Домен www.jic.edu.sa не разрешается, jic.edu.sa и rcjy.gov.sa недоступны (502 / сброс соединения) — данные не изменены (04.10.2026)</t>
-        </is>
-      </c>
-      <c r="AH44" s="4" t="inlineStr">
+• Перепроверка: Домен www.jic.edu.sa не разрешается, jic.edu.sa и rcjy.gov.sa недоступны (502 / сброс соединения) — данные не изменены (04.10.2026)
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI44" s="4" t="inlineStr">
         <is>
           <t>Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI44" s="4" t="inlineStr">
+      <c r="AJ44" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ44" s="4" t="inlineStr"/>
+      <c r="AK44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -8933,42 +9607,52 @@
       </c>
       <c r="Q45" s="4" t="inlineStr"/>
       <c r="R45" s="4" t="inlineStr"/>
-      <c r="S45" s="4" t="inlineStr"/>
-      <c r="T45" s="4" t="inlineStr"/>
+      <c r="S45" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T45" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="U45" s="4" t="inlineStr"/>
-      <c r="V45" s="4" t="n">
+      <c r="V45" s="4" t="inlineStr"/>
+      <c r="W45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W45" s="4" t="inlineStr"/>
       <c r="X45" s="4" t="inlineStr"/>
       <c r="Y45" s="4" t="inlineStr"/>
       <c r="Z45" s="4" t="inlineStr"/>
       <c r="AA45" s="4" t="inlineStr"/>
       <c r="AB45" s="4" t="inlineStr"/>
-      <c r="AC45" s="4" t="n">
+      <c r="AC45" s="4" t="inlineStr"/>
+      <c r="AD45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD45" s="8" t="inlineStr">
+      <c r="AE45" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE45" s="4" t="inlineStr"/>
-      <c r="AF45" s="4" t="inlineStr">
+      <c r="AF45" s="4" t="inlineStr"/>
+      <c r="AG45" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG45" s="4" t="inlineStr">
+      <c r="AH45" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт — https://psaa.com.sa (одностраничное приложение, в основном портал записи на курсы); psaa.edu.sa не резолвится
 • Сайт указывает расположение академии в Джидде и отдельную регистрацию для сотрудников Saudia — подтверждает принадлежность к группе Saudia
 • Руководитель, e-mail, телефон, почтовый адрес НЕ найдены на официальных страницах — требуется ручная доработка
 • Профиль main_fields — общий для авиационной академии, не проверен; спутников в nanosats.csv нет
-• Перепроверка: Официальный сайт psaa.com.sa (SPA) открыт 04.10.2026: из его кода подтверждены расположение в Джидде и связь с Saudia (отдельная регистрация для сотрудников Saudia); руководитель, e-mail, телефон и адрес на сайте не опубликованы</t>
-        </is>
-      </c>
-      <c r="AH45" s="4" t="inlineStr">
+• Перепроверка: Официальный сайт psaa.com.sa (SPA) открыт 04.10.2026: из его кода подтверждены расположение в Джидде и связь с Saudia (отдельная регистрация для сотрудников Saudia); руководитель, e-mail, телефон и адрес на сайте не опубликованы
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI45" s="4" t="inlineStr">
         <is>
           <t>• Https://psaa.com.sa/ (SPA
 • Текст из официального JS-бандла /static/js/main.ca029ecb.js)
@@ -8976,12 +9660,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI45" s="4" t="inlineStr">
+      <c r="AJ45" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ45" s="4" t="inlineStr"/>
+      <c r="AK45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -9076,45 +9760,63 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S46" s="4" t="inlineStr"/>
-      <c r="T46" s="4" t="inlineStr"/>
-      <c r="U46" s="4" t="inlineStr"/>
-      <c r="V46" s="4" t="n">
+      <c r="S46" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T46" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U46" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V46" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W46" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W46" s="4" t="inlineStr"/>
       <c r="X46" s="4" t="inlineStr"/>
       <c r="Y46" s="4" t="inlineStr"/>
       <c r="Z46" s="4" t="inlineStr"/>
       <c r="AA46" s="4" t="inlineStr"/>
       <c r="AB46" s="4" t="inlineStr"/>
-      <c r="AC46" s="4" t="n">
+      <c r="AC46" s="4" t="inlineStr"/>
+      <c r="AD46" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD46" s="8" t="inlineStr">
+      <c r="AE46" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE46" s="4" t="inlineStr">
+      <c r="AF46" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF46" s="4" t="inlineStr">
+      <c r="AG46" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG46" s="4" t="inlineStr">
+      <c r="AH46" s="4" t="inlineStr">
         <is>
           <t>• Частный университет медико-стоматологического профиля (бывш. Riyadh Colleges of Dentistry and Pharmacy)
 • Президент указан на сайте по-арабски (фото загружено 29.10.2025); латинская транслитерация — наша
 • Международного отдела/контактов на сайте нет (только раздел для иностранных студентов) — использовать info@riyadh.edu.sa
-• Космического профиля нет; спутников не найдено (проверка только по nanosats.csv)</t>
-        </is>
-      </c>
-      <c r="AH46" s="4" t="inlineStr">
+• Космического профиля нет; спутников не найдено (проверка только по nanosats.csv)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI46" s="4" t="inlineStr">
         <is>
           <t>• Https://www.riyadh.edu.sa/en
 • Https://www.riyadh.edu.sa/about
@@ -9122,12 +9824,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI46" s="4" t="inlineStr">
+      <c r="AJ46" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ46" s="4" t="inlineStr"/>
+      <c r="AK46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -9220,62 +9922,77 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S47" s="4" t="inlineStr"/>
+      <c r="S47" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T47" s="4" t="inlineStr">
         <is>
-          <t>THE2027: Reporter (unranked)</t>
-        </is>
-      </c>
-      <c r="U47" s="4" t="inlineStr"/>
-      <c r="V47" s="4" t="n">
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U47" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V47" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W47" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W47" s="4" t="inlineStr"/>
       <c r="X47" s="4" t="inlineStr"/>
       <c r="Y47" s="4" t="inlineStr"/>
       <c r="Z47" s="4" t="inlineStr"/>
       <c r="AA47" s="4" t="inlineStr"/>
       <c r="AB47" s="4" t="inlineStr"/>
-      <c r="AC47" s="4" t="n">
+      <c r="AC47" s="4" t="inlineStr"/>
+      <c r="AD47" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD47" s="8" t="inlineStr">
+      <c r="AE47" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE47" s="4" t="inlineStr">
+      <c r="AF47" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF47" s="4" t="inlineStr">
+      <c r="AG47" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG47" s="4" t="inlineStr">
+      <c r="AH47" s="4" t="inlineStr">
         <is>
           <t>• Частный университет бизнес-профиля (есть инженерный колледж и программы ИИ); низкая релевантность для спутниковой программы
 • В вузе есть подразделение International Partnership Affairs, но его e-mail/руководитель не опубликованы; используется общий info@ubt.edu.sa
 • Президент — Dr. Weam Husni Tunsi (по данным API официального сайта; учёное звание — доцент/Associate Professor)
-• В THE 2027 — только статус Reporter (без места); спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH47" s="4" t="inlineStr">
+• В THE 2027 — только статус Reporter (без места); спутников не найдено
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI47" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ubt.edu.sa/
 • Https://www.ubt.edu.sa/about/ubtpresident
 • Https://mobileapp.ubt.edu.sa/UBTWebsiteAPI/api/Faculty/get/president
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI47" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ47" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ47" s="4" t="inlineStr"/>
+      <c r="AK47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -9372,46 +10089,64 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S48" s="4" t="inlineStr"/>
-      <c r="T48" s="4" t="inlineStr"/>
-      <c r="U48" s="4" t="inlineStr"/>
-      <c r="V48" s="4" t="n">
+      <c r="S48" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T48" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U48" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V48" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W48" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W48" s="4" t="inlineStr"/>
       <c r="X48" s="4" t="inlineStr"/>
       <c r="Y48" s="4" t="inlineStr"/>
       <c r="Z48" s="4" t="inlineStr"/>
       <c r="AA48" s="4" t="inlineStr"/>
       <c r="AB48" s="4" t="inlineStr"/>
-      <c r="AC48" s="4" t="n">
+      <c r="AC48" s="4" t="inlineStr"/>
+      <c r="AD48" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD48" s="8" t="inlineStr">
+      <c r="AE48" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE48" s="4" t="inlineStr">
+      <c r="AF48" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF48" s="4" t="inlineStr">
+      <c r="AG48" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG48" s="4" t="inlineStr">
+      <c r="AH48" s="4" t="inlineStr">
         <is>
           <t>• Частный некоммерческий университет (Медина); президент назначен 18/1/1444 г.х. (август 2022); упоминается как президент в новости о TEDxUPM от 12.02.2026
 • Профиль — компьютерные науки, кибербезопасность, инженерия (выбран technical, не аэрокосмический в узком смысле)
 • Отдельного международного отдела нет; vrbd@upm.edu.sa — Проректорат по развитию бизнеса (партнёрства); исследования/партнёрства в науке — srgs@upm.edu.sa
 • Телефон 920000238 — единый номер (на сайте в формате +966920000238)
-• Спутников не найдено (проверка только по nanosats.csv)</t>
-        </is>
-      </c>
-      <c r="AH48" s="4" t="inlineStr">
+• Спутников не найдено (проверка только по nanosats.csv)
+• Рейтинги: Есть только национальная классификация ETEC «Saqr» (صقر), 1-я редакция 2023/24 (итоги 02.2025): 4 уровня (Excellence/Progress/Launch/Preparation), без мест; результаты рассылались вузам индивидуально, публичного списка нет</t>
+        </is>
+      </c>
+      <c r="AI48" s="4" t="inlineStr">
         <is>
           <t>• Https://www.upm.edu.sa/en
 • Https://www.upm.edu.sa/en/about-upm#president-corner
@@ -9420,12 +10155,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI48" s="4" t="inlineStr">
+      <c r="AJ48" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ48" s="4" t="inlineStr"/>
+      <c r="AK48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -9493,33 +10228,42 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="S49" s="4" t="inlineStr"/>
-      <c r="T49" s="4" t="inlineStr"/>
+      <c r="S49" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T49" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="U49" s="4" t="inlineStr"/>
-      <c r="V49" s="4" t="n">
+      <c r="V49" s="4" t="inlineStr"/>
+      <c r="W49" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W49" s="4" t="inlineStr"/>
       <c r="X49" s="4" t="inlineStr"/>
       <c r="Y49" s="4" t="inlineStr"/>
       <c r="Z49" s="4" t="inlineStr"/>
       <c r="AA49" s="4" t="inlineStr"/>
       <c r="AB49" s="4" t="inlineStr"/>
-      <c r="AC49" s="4" t="n">
+      <c r="AC49" s="4" t="inlineStr"/>
+      <c r="AD49" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD49" s="8" t="inlineStr">
+      <c r="AE49" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE49" s="4" t="inlineStr"/>
-      <c r="AF49" s="4" t="inlineStr">
+      <c r="AF49" s="4" t="inlineStr"/>
+      <c r="AG49" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG49" s="4" t="inlineStr">
+      <c r="AH49" s="4" t="inlineStr">
         <is>
           <t>• Колледж Королевской комиссии по Джубайлю и Янбу (Royal Commission), основан в 1989 г., расположен в промышленном городе Янбу
 • В Википедии руководителем указан Dr. Fahad Aloufi (без даты, вероятно устарело) — в head_name не внесено
@@ -9527,10 +10271,11 @@
 • Актуальный официальный сайт — раздел портала Royal Commission Education (rcjy.edu.sa); yic.edu.sa и rcyci.edu.sa не открываются
 • Руководитель — Managing Director (по оргструктуре на rcjy.edu.sa), имя на открытых страницах не указано; по поиску — Dr. Ahmed Al-Ghamdi (не подтверждено)
 • Опубликованного e-mail нет: обращения через веб-форму https://rcjy.edu.sa/en/contact-us/ (выбор «Yanbu Industrial College»)
-• Перепроверка: 04.10.2026: найден официальный раздел колледжа на rcjy.edu.sa (сайт обновлён); имя руководителя и e-mail там не опубликованы — остаётся low</t>
-        </is>
-      </c>
-      <c r="AH49" s="4" t="inlineStr">
+• Перепроверка: 04.10.2026: найден официальный раздел колледжа на rcjy.edu.sa (сайт обновлён); имя руководителя и e-mail там не опубликованы — остаётся low
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI49" s="4" t="inlineStr">
         <is>
           <t>• Https://rcjy.edu.sa/en/colleges-and-institutes-in-yanbu/yanbu-industrial-college/home-yanbu-industrial-college/
 • Https://rcjy.edu.sa/en/colleges-and-institutes-in-yanbu/yanbu-industrial-college/about-yanbu-industrial-college/organizational-structure-yanbu-industrial-college/
@@ -9539,15 +10284,15 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI49" s="4" t="inlineStr">
+      <c r="AJ49" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ49" s="4" t="inlineStr"/>
+      <c r="AK49" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ49"/>
+  <autoFilter ref="A1:AK49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>